--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,15 +427,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
@@ -577,20 +577,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>4197</t>
-        </is>
+      <c r="C2" t="n">
+        <v>4197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>ibrar gul</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>117116</t>
-        </is>
+      <c r="E2" t="n">
+        <v>117116</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -599,7 +595,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-01 08:44:48</t>
+          <t>2026-10-01 8:44:48</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -609,7 +605,7 @@
         <v>67.03396480000001</v>
       </c>
       <c r="J2" t="n">
-        <v>24.89999961853027</v>
+        <v>24.89999962</v>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -634,8 +630,140 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VIS-20261001090417-FC6691</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>5073</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Syed Talha Qamar</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>120293</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>KISWA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-01 9:04:17</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>24.8369652</v>
+      </c>
+      <c r="I3" t="n">
+        <v>67.03389</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12.3039999</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>16247</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>VIS-20261001092533-3DCA5B</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4757</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Aisha ulfat</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>101660</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SADIQ GASOLINE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-01 09:25:33</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>24.8370641</v>
+      </c>
+      <c r="I4" t="n">
+        <v>67.0338747</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.13500022888184</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
+        <v>11768.3</v>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V2"/>
+  <autoFilter ref="A1:V4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -705,20 +705,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4757</t>
-        </is>
+      <c r="C4" t="n">
+        <v>4757</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Aisha ulfat</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>101660</t>
-        </is>
+      <c r="E4" t="n">
+        <v>101660</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -727,7 +723,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-01 09:25:33</t>
+          <t>2026-10-01 9:25:33</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -737,7 +733,7 @@
         <v>67.0338747</v>
       </c>
       <c r="J4" t="n">
-        <v>16.13500022888184</v>
+        <v>16.13500023</v>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -762,8 +758,76 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VIS-20261001100032-56BD0B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3473</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Yasir Hameed</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>118099</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DHA MULTAN F/S</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:00:32</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>30.2928934</v>
+      </c>
+      <c r="I5" t="n">
+        <v>71.50366560000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14.8129997253418</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V4"/>
+  <autoFilter ref="A1:V5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,19 +427,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -769,20 +769,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3473</t>
-        </is>
+      <c r="C5" t="n">
+        <v>3473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Yasir Hameed</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>118099</t>
-        </is>
+      <c r="E5" t="n">
+        <v>118099</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -801,7 +797,7 @@
         <v>71.50366560000001</v>
       </c>
       <c r="J5" t="n">
-        <v>14.8129997253418</v>
+        <v>14.81299973</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -826,8 +822,76 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>VIS-20261001101513-4D7EED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4483</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Muhammad Hassnain Zia</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>104241</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CAPRI FLNG AND SER STN</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:15:13</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>33.7213993</v>
+      </c>
+      <c r="I6" t="n">
+        <v>73.0597118</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.673000335693359</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V5"/>
+  <autoFilter ref="A1:V6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -435,11 +435,11 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -833,20 +833,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4483</t>
-        </is>
+      <c r="C6" t="n">
+        <v>4483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Muhammad Hassnain Zia</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>104241</t>
-        </is>
+      <c r="E6" t="n">
+        <v>104241</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -865,7 +861,7 @@
         <v>73.0597118</v>
       </c>
       <c r="J6" t="n">
-        <v>8.673000335693359</v>
+        <v>8.673000335999999</v>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
@@ -890,8 +886,140 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>VIS-20261001101655-F1F80A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4667</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fahad Shakir</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>104241</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CAPRI FLNG AND SER STN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:16:55</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>33.7214927</v>
+      </c>
+      <c r="I7" t="n">
+        <v>73.0597863</v>
+      </c>
+      <c r="J7" t="n">
+        <v>13.90299988</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>VIS-20261001102335-DF37FC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Adnan Afzaal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>116674</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>PSO S/S -03 (CLIFF PETROLEUM SERVIC</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:23:35</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>24.8338565826416</v>
+      </c>
+      <c r="I8" t="n">
+        <v>67.03367614746094</v>
+      </c>
+      <c r="J8" t="n">
+        <v>200</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V6"/>
+  <autoFilter ref="A1:V8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,15 +437,15 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -961,20 +961,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4970</t>
-        </is>
+      <c r="C8" t="n">
+        <v>4970</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Adnan Afzaal</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>116674</t>
-        </is>
+      <c r="E8" t="n">
+        <v>116674</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -987,39 +983,451 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.8338565826416</v>
+        <v>24.83385658</v>
       </c>
       <c r="I8" t="n">
-        <v>67.03367614746094</v>
+        <v>67.03367615000001</v>
       </c>
       <c r="J8" t="n">
         <v>200</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:24:36</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>24.83385658</v>
+      </c>
+      <c r="M8" t="n">
+        <v>67.03367615000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>200</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0:01:01</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.0169</v>
+      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T8" t="n">
         <v>213.4</v>
       </c>
-      <c r="U8" t="inlineStr"/>
+      <c r="U8" t="n">
+        <v>213.4</v>
+      </c>
       <c r="V8" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>VIS-20261001102642-4738A1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>5261</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Naseer Mangi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>101719</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>M/S POONAM F/S</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:26:42</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>25.3875427</v>
+      </c>
+      <c r="I9" t="n">
+        <v>68.3412319</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>VIS-20261001102703-6E5380</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3936</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Muhammad Ali</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>116442</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SAMCO POL F/S</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:27:03</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>33.6340757</v>
+      </c>
+      <c r="I10" t="n">
+        <v>73.0763683</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.35499954223633</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>VIS-20261001102718-C034DD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4814</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Hassan Ahmed</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>119062</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>POLICE WELFARE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:27:18</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>32.9322274</v>
+      </c>
+      <c r="I11" t="n">
+        <v>73.7286802</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19.7810001373291</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:27:31</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>32.9322338</v>
+      </c>
+      <c r="M11" t="n">
+        <v>73.7287374</v>
+      </c>
+      <c r="N11" t="n">
+        <v>33.86299896240234</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>00:00:13</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>VIS-20261001102823-26D732</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4172</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Syed Ali Azhar Rizvi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>104671</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PSO S/S2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:28:23</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>33.7180269</v>
+      </c>
+      <c r="I12" t="n">
+        <v>73.1047011</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15.21100044250488</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VIS-20261001102829-8A7C92</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4814</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Hassan Ahmed</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>119062</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>POLICE WELFARE</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:28:29</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>32.9322682</v>
+      </c>
+      <c r="I13" t="n">
+        <v>73.72883760000001</v>
+      </c>
+      <c r="J13" t="n">
+        <v>39.83100128173828</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:28:37</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>32.9322039</v>
+      </c>
+      <c r="M13" t="n">
+        <v>73.7288266</v>
+      </c>
+      <c r="N13" t="n">
+        <v>25.79500007629395</v>
+      </c>
+      <c r="O13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>00:00:08</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V8"/>
+  <autoFilter ref="A1:V13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1049,20 +1049,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
+      <c r="C9" t="n">
+        <v>5261</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Naseer Mangi</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>101719</t>
-        </is>
+      <c r="E9" t="n">
+        <v>101719</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1117,20 +1113,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3936</t>
-        </is>
+      <c r="C10" t="n">
+        <v>3936</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Muhammad Ali</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>116442</t>
-        </is>
+      <c r="E10" t="n">
+        <v>116442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1149,7 +1141,7 @@
         <v>73.0763683</v>
       </c>
       <c r="J10" t="n">
-        <v>18.35499954223633</v>
+        <v>18.35499954</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1185,20 +1177,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
+      <c r="C11" t="n">
+        <v>4814</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Hassan Ahmed</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>119062</t>
-        </is>
+      <c r="E11" t="n">
+        <v>119062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1217,7 +1205,7 @@
         <v>73.7286802</v>
       </c>
       <c r="J11" t="n">
-        <v>19.7810001373291</v>
+        <v>19.78100014</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1231,7 +1219,7 @@
         <v>73.7287374</v>
       </c>
       <c r="N11" t="n">
-        <v>33.86299896240234</v>
+        <v>33.86299896</v>
       </c>
       <c r="O11" t="n">
         <v>5.4</v>
@@ -1243,7 +1231,7 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>00:00:13</t>
+          <t>0:00:13</t>
         </is>
       </c>
       <c r="R11" t="n">
@@ -1277,20 +1265,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4172</t>
-        </is>
+      <c r="C12" t="n">
+        <v>4172</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Syed Ali Azhar Rizvi</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>104671</t>
-        </is>
+      <c r="E12" t="n">
+        <v>104671</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1309,25 +1293,49 @@
         <v>73.1047011</v>
       </c>
       <c r="J12" t="n">
-        <v>15.21100044250488</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
+        <v>15.21100044</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:28:44</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>33.7182216</v>
+      </c>
+      <c r="M12" t="n">
+        <v>73.1047233</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8.329000473000001</v>
+      </c>
+      <c r="O12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0:00:21</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.0058</v>
+      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T12" t="n">
         <v>36.1</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>14.4</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -1345,20 +1353,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4814</t>
-        </is>
+      <c r="C13" t="n">
+        <v>4814</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>Hassan Ahmed</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>119062</t>
-        </is>
+      <c r="E13" t="n">
+        <v>119062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1377,7 +1381,7 @@
         <v>73.72883760000001</v>
       </c>
       <c r="J13" t="n">
-        <v>39.83100128173828</v>
+        <v>39.83100128</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1391,7 +1395,7 @@
         <v>73.7288266</v>
       </c>
       <c r="N13" t="n">
-        <v>25.79500007629395</v>
+        <v>25.79500008</v>
       </c>
       <c r="O13" t="n">
         <v>7.2</v>
@@ -1403,7 +1407,7 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>00:00:08</t>
+          <t>0:00:08</t>
         </is>
       </c>
       <c r="R13" t="n">
@@ -1426,8 +1430,532 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VIS-20261001103013-1A3796</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4996</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Tahseen ullah khan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>120071</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>GULBERG GREENS FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:30:13</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>33.6109473</v>
+      </c>
+      <c r="I14" t="n">
+        <v>73.1763869</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7.657999992370605</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VIS-20261001103053-E5C429</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Muhammad Ibrahim</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>104238</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>INAYAT GAS AND SER STN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:30:53</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>33.6556823</v>
+      </c>
+      <c r="I15" t="n">
+        <v>73.08191309999999</v>
+      </c>
+      <c r="J15" t="n">
+        <v>20.46100044250488</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:33:51</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>33.6556656</v>
+      </c>
+      <c r="M15" t="n">
+        <v>73.08191600000001</v>
+      </c>
+      <c r="N15" t="n">
+        <v>15.42000007629395</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>00:02:58</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>0.0494</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T15" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>VIS-20261001103121-2F3514</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2367</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Malik Amir Abbas</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>111737</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AL-WAHID F/S</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:31:21</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>33.6453751</v>
+      </c>
+      <c r="I16" t="n">
+        <v>72.97584620000001</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.299999952316284</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T16" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>VIS-20261001103206-9AB10F</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2699</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Haseeb Alam Khsn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>119026</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ABID PETROLEUM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:32:06</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>33.6689586</v>
+      </c>
+      <c r="I17" t="n">
+        <v>73.1502151</v>
+      </c>
+      <c r="J17" t="n">
+        <v>11.56599998474121</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:33:00</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>33.668959</v>
+      </c>
+      <c r="M17" t="n">
+        <v>73.150218</v>
+      </c>
+      <c r="N17" t="n">
+        <v>20</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>00:00:54</t>
+        </is>
+      </c>
+      <c r="R17" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>2454.7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2454.5</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>VIS-20261001103252-30C791</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4798</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Salman Waleed</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>115291</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>PSO SERVICE STATION 13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:32:52</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>33.7100303</v>
+      </c>
+      <c r="I18" t="n">
+        <v>73.0391218</v>
+      </c>
+      <c r="J18" t="n">
+        <v>11.98600006103516</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>23</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>VIS-20261001103255-BB21B5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4957</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Muhammad Saad Durrani</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>102505</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SUPER SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:32:55</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>27.6931649</v>
+      </c>
+      <c r="I19" t="n">
+        <v>68.8466861</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.875999927520752</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>VIS-20261001103320-7C2E38</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2096</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Taimur Yaqoob</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>113672</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>HABIB FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:33:20</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>33.4917851</v>
+      </c>
+      <c r="I20" t="n">
+        <v>73.0958199</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.045000076293945</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V13"/>
+  <autoFilter ref="A1:V20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,18 +427,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -1954,8 +1954,1484 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>VIS-20261001103401-C2837D</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3659</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Muhammad Omar Khan</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>120130</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>MEHAR ASHIQ AND COMPANY, ISLAMABAD</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:34:01</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>33.71961524428054</v>
+      </c>
+      <c r="I21" t="n">
+        <v>73.07347450741493</v>
+      </c>
+      <c r="J21" t="n">
+        <v>13.18800957520656</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>VIS-20261001103404-0F359A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4974</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Muhammad Sohail</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>101737</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>AL-MADINA T/S</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:34:04</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>25.6459935</v>
+      </c>
+      <c r="I22" t="n">
+        <v>68.300264</v>
+      </c>
+      <c r="J22" t="n">
+        <v>11.73499965667725</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>VIS-20261001103405-FCDF0D</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4973</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ejaz Ahmad</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>119961</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>HASSAN FS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:34:05</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>31.8244242</v>
+      </c>
+      <c r="I23" t="n">
+        <v>70.8527359</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>VIS-20261001103409-67C663</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Umair Ahmed Abbasi</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>115291</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>PSO SERVICE STATION 13</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:34:09</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>33.710037</v>
+      </c>
+      <c r="I24" t="n">
+        <v>73.0391228</v>
+      </c>
+      <c r="J24" t="n">
+        <v>12.74100017547607</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>VIS-20261001103422-F2E1BC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3387</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ARIF RIAZ KHAN</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>116183</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>MUSA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:34:22</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>33.6436439</v>
+      </c>
+      <c r="I25" t="n">
+        <v>73.06106560000001</v>
+      </c>
+      <c r="J25" t="n">
+        <v>14.18099975585938</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>VIS-20261001103439-366CBA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3619</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Muhammad Faizan</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>120130</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>MEHAR ASHIQ AND COMPANY, ISLAMABAD</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:34:39</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>33.7198033</v>
+      </c>
+      <c r="I26" t="n">
+        <v>73.07342180000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T26" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>VIS-20261001103454-578044</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2699</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Haseeb Alam Khsn</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>119026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ABID PETROLEUM</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:34:54</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>33.6689587</v>
+      </c>
+      <c r="I27" t="n">
+        <v>73.1502167</v>
+      </c>
+      <c r="J27" t="n">
+        <v>11.60700035095215</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:36:36</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>33.6689592</v>
+      </c>
+      <c r="M27" t="n">
+        <v>73.15021779999999</v>
+      </c>
+      <c r="N27" t="n">
+        <v>11.5959997177124</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>00:01:42</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>0.0283</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
+        <v>2454.6</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2454.5</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>VIS-20261001103459-D61088</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2097</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mian Zubairuddin</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>104286</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>PEARL FILL STATION</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:34:59</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>33.660286</v>
+      </c>
+      <c r="I28" t="n">
+        <v>73.0631692</v>
+      </c>
+      <c r="J28" t="n">
+        <v>36.52700042724609</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VIS-20261001103501-01912F</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2953</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sohaib Lodhi</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>120071</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>GULBERG GREENS FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:35:01</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>33.610959</v>
+      </c>
+      <c r="I29" t="n">
+        <v>73.1764053</v>
+      </c>
+      <c r="J29" t="n">
+        <v>13.26200008392334</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VIS-20261001103510-340A1C</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Zafarjamil</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>117439</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>GARDEN PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:35:10</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>24.8745883</v>
+      </c>
+      <c r="I30" t="n">
+        <v>67.019972</v>
+      </c>
+      <c r="J30" t="n">
+        <v>15.81599998474121</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>VIS-20261001103536-09CA44</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4556</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Mudasar javed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>115582</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>TRI STAR PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:35:36</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>33.6435446</v>
+      </c>
+      <c r="I31" t="n">
+        <v>73.0307117</v>
+      </c>
+      <c r="J31" t="n">
+        <v>12.39900016784668</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>VIS-20261001103605-BEE679</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Nisar Ahmed Jan Sarhandi</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>101719</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>M/S POONAM F/S</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:36:05</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>25.3875421</v>
+      </c>
+      <c r="I32" t="n">
+        <v>68.3412301</v>
+      </c>
+      <c r="J32" t="n">
+        <v>20</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>VIS-20261001103622-7E49D5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sajid Abbasi</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>101864</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>PLATINUM PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:36:22</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>25.4066225</v>
+      </c>
+      <c r="I33" t="n">
+        <v>68.3630129</v>
+      </c>
+      <c r="J33" t="n">
+        <v>11.89900016784668</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>VIS-20261001103729-7BF72E</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4495</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Mirza Amjid Baig</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>116183</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>MUSA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:37:29</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>33.6436502</v>
+      </c>
+      <c r="I34" t="n">
+        <v>73.0610652</v>
+      </c>
+      <c r="J34" t="n">
+        <v>12.44200038909912</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>VIS-20261001103738-62840E</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4412</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Ch Arshad Hussain</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>115853</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>AWAN ASSOCIATES</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:37:38</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>33.7282938</v>
+      </c>
+      <c r="I35" t="n">
+        <v>73.0781049</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10.61600017547607</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>VIS-20261001103743-BDB018</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Raham Ali</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>115853</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>AWAN ASSOCIATES</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:37:43</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>33.728288</v>
+      </c>
+      <c r="I36" t="n">
+        <v>73.0781073</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7.386000156402588</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:38:53</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>33.7282127</v>
+      </c>
+      <c r="M36" t="n">
+        <v>73.07816769999999</v>
+      </c>
+      <c r="N36" t="n">
+        <v>7.026999950408936</v>
+      </c>
+      <c r="O36" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>00:01:10</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>VIS-20261001103743-D6B260</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5091</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Abdullah</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>104459</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>FREINDS FILL STATION</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:37:43</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>33.7580499</v>
+      </c>
+      <c r="I37" t="n">
+        <v>72.8070341</v>
+      </c>
+      <c r="J37" t="n">
+        <v>20.89999961853027</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>VIS-20261001103752-223DFA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2830</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Nazar Muhammad Kharal</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>118099</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DHA MULTAN F/S</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:37:52</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>30.2928487</v>
+      </c>
+      <c r="I38" t="n">
+        <v>71.50364759999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>20</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
+        <v>77.7</v>
+      </c>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>VIS-20261001103801-9543DC</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4474</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Abdul Razique</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>102014</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>QASIMABAD PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:38:01</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>25.4013694</v>
+      </c>
+      <c r="I39" t="n">
+        <v>68.3396235</v>
+      </c>
+      <c r="J39" t="n">
+        <v>45.44499969482422</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VIS-20261001103833-365D48</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4925</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Usama Tasif</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>119468</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>MARWAT FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:38:33</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>33.6685149</v>
+      </c>
+      <c r="I40" t="n">
+        <v>73.0772733</v>
+      </c>
+      <c r="J40" t="n">
+        <v>41.46099853515625</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T40" t="n">
+        <v>52</v>
+      </c>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>VIS-20261001103900-3B862D</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4909</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Victor Bashir</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>110951</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>NLC PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:39:00</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>25.4115209</v>
+      </c>
+      <c r="I41" t="n">
+        <v>68.3541412</v>
+      </c>
+      <c r="J41" t="n">
+        <v>42.34199905395508</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T41" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V20"/>
+  <autoFilter ref="A1:V41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V41"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,8 +437,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -1441,20 +1441,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4996</t>
-        </is>
+      <c r="C14" t="n">
+        <v>4996</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Tahseen ullah khan</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>120071</t>
-        </is>
+      <c r="E14" t="n">
+        <v>120071</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1473,7 +1469,7 @@
         <v>73.1763869</v>
       </c>
       <c r="J14" t="n">
-        <v>7.657999992370605</v>
+        <v>7.657999992</v>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
@@ -1509,20 +1505,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2313</t>
-        </is>
+      <c r="C15" t="n">
+        <v>2313</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Muhammad Ibrahim</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>104238</t>
-        </is>
+      <c r="E15" t="n">
+        <v>104238</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1541,7 +1533,7 @@
         <v>73.08191309999999</v>
       </c>
       <c r="J15" t="n">
-        <v>20.46100044250488</v>
+        <v>20.46100044</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1555,7 +1547,7 @@
         <v>73.08191600000001</v>
       </c>
       <c r="N15" t="n">
-        <v>15.42000007629395</v>
+        <v>15.42000008</v>
       </c>
       <c r="O15" t="n">
         <v>1.9</v>
@@ -1567,7 +1559,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>00:02:58</t>
+          <t>0:02:58</t>
         </is>
       </c>
       <c r="R15" t="n">
@@ -1601,20 +1593,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2367</t>
-        </is>
+      <c r="C16" t="n">
+        <v>2367</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Malik Amir Abbas</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>111737</t>
-        </is>
+      <c r="E16" t="n">
+        <v>111737</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1633,7 +1621,7 @@
         <v>72.97584620000001</v>
       </c>
       <c r="J16" t="n">
-        <v>3.299999952316284</v>
+        <v>3.299999952</v>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
@@ -1669,20 +1657,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2699</t>
-        </is>
+      <c r="C17" t="n">
+        <v>2699</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Haseeb Alam Khsn</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>119026</t>
-        </is>
+      <c r="E17" t="n">
+        <v>119026</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1701,7 +1685,7 @@
         <v>73.1502151</v>
       </c>
       <c r="J17" t="n">
-        <v>11.56599998474121</v>
+        <v>11.56599998</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1727,7 +1711,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>00:00:54</t>
+          <t>0:00:54</t>
         </is>
       </c>
       <c r="R17" t="n">
@@ -1761,20 +1745,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4798</t>
-        </is>
+      <c r="C18" t="n">
+        <v>4798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>Salman Waleed</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>115291</t>
-        </is>
+      <c r="E18" t="n">
+        <v>115291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1793,7 +1773,7 @@
         <v>73.0391218</v>
       </c>
       <c r="J18" t="n">
-        <v>11.98600006103516</v>
+        <v>11.98600006</v>
       </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
@@ -1829,20 +1809,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>4957</t>
-        </is>
+      <c r="C19" t="n">
+        <v>4957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Muhammad Saad Durrani</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>102505</t>
-        </is>
+      <c r="E19" t="n">
+        <v>102505</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1861,7 +1837,7 @@
         <v>68.8466861</v>
       </c>
       <c r="J19" t="n">
-        <v>4.875999927520752</v>
+        <v>4.875999928</v>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
@@ -1897,20 +1873,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2096</t>
-        </is>
+      <c r="C20" t="n">
+        <v>2096</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>Taimur Yaqoob</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>113672</t>
-        </is>
+      <c r="E20" t="n">
+        <v>113672</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1929,7 +1901,7 @@
         <v>73.0958199</v>
       </c>
       <c r="J20" t="n">
-        <v>4.045000076293945</v>
+        <v>4.045000076</v>
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
@@ -1965,20 +1937,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>3659</t>
-        </is>
+      <c r="C21" t="n">
+        <v>3659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>Muhammad Omar Khan</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>120130</t>
-        </is>
+      <c r="E21" t="n">
+        <v>120130</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1991,13 +1959,13 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>33.71961524428054</v>
+        <v>33.71961524</v>
       </c>
       <c r="I21" t="n">
-        <v>73.07347450741493</v>
+        <v>73.07347451</v>
       </c>
       <c r="J21" t="n">
-        <v>13.18800957520656</v>
+        <v>13.18800958</v>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -2033,20 +2001,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>4974</t>
-        </is>
+      <c r="C22" t="n">
+        <v>4974</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Muhammad Sohail</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>101737</t>
-        </is>
+      <c r="E22" t="n">
+        <v>101737</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2065,7 +2029,7 @@
         <v>68.300264</v>
       </c>
       <c r="J22" t="n">
-        <v>11.73499965667725</v>
+        <v>11.73499966</v>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
@@ -2101,20 +2065,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>4973</t>
-        </is>
+      <c r="C23" t="n">
+        <v>4973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Ejaz Ahmad</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>119961</t>
-        </is>
+      <c r="E23" t="n">
+        <v>119961</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2169,20 +2129,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>4573</t>
-        </is>
+      <c r="C24" t="n">
+        <v>4573</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Umair Ahmed Abbasi</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>115291</t>
-        </is>
+      <c r="E24" t="n">
+        <v>115291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2201,7 +2157,7 @@
         <v>73.0391228</v>
       </c>
       <c r="J24" t="n">
-        <v>12.74100017547607</v>
+        <v>12.74100018</v>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
@@ -2237,20 +2193,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>3387</t>
-        </is>
+      <c r="C25" t="n">
+        <v>3387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>ARIF RIAZ KHAN</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>116183</t>
-        </is>
+      <c r="E25" t="n">
+        <v>116183</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2269,7 +2221,7 @@
         <v>73.06106560000001</v>
       </c>
       <c r="J25" t="n">
-        <v>14.18099975585938</v>
+        <v>14.18099976</v>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
@@ -2305,20 +2257,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>3619</t>
-        </is>
+      <c r="C26" t="n">
+        <v>3619</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>Muhammad Faizan</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>120130</t>
-        </is>
+      <c r="E26" t="n">
+        <v>120130</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2373,20 +2321,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2699</t>
-        </is>
+      <c r="C27" t="n">
+        <v>2699</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>Haseeb Alam Khsn</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>119026</t>
-        </is>
+      <c r="E27" t="n">
+        <v>119026</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2405,7 +2349,7 @@
         <v>73.1502167</v>
       </c>
       <c r="J27" t="n">
-        <v>11.60700035095215</v>
+        <v>11.60700035</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2419,7 +2363,7 @@
         <v>73.15021779999999</v>
       </c>
       <c r="N27" t="n">
-        <v>11.5959997177124</v>
+        <v>11.59599972</v>
       </c>
       <c r="O27" t="n">
         <v>0.1</v>
@@ -2431,7 +2375,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>00:01:42</t>
+          <t>0:01:42</t>
         </is>
       </c>
       <c r="R27" t="n">
@@ -2465,20 +2409,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>2097</t>
-        </is>
+      <c r="C28" t="n">
+        <v>2097</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>Mian Zubairuddin</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>104286</t>
-        </is>
+      <c r="E28" t="n">
+        <v>104286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2497,7 +2437,7 @@
         <v>73.0631692</v>
       </c>
       <c r="J28" t="n">
-        <v>36.52700042724609</v>
+        <v>36.52700043</v>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
@@ -2533,20 +2473,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>2953</t>
-        </is>
+      <c r="C29" t="n">
+        <v>2953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>Sohaib Lodhi</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>120071</t>
-        </is>
+      <c r="E29" t="n">
+        <v>120071</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2565,7 +2501,7 @@
         <v>73.1764053</v>
       </c>
       <c r="J29" t="n">
-        <v>13.26200008392334</v>
+        <v>13.26200008</v>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
@@ -2601,20 +2537,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1494</t>
-        </is>
+      <c r="C30" t="n">
+        <v>1494</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>Zafarjamil</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>117439</t>
-        </is>
+      <c r="E30" t="n">
+        <v>117439</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2633,7 +2565,7 @@
         <v>67.019972</v>
       </c>
       <c r="J30" t="n">
-        <v>15.81599998474121</v>
+        <v>15.81599998</v>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -2669,20 +2601,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>4556</t>
-        </is>
+      <c r="C31" t="n">
+        <v>4556</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>Mudasar javed</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>115582</t>
-        </is>
+      <c r="E31" t="n">
+        <v>115582</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2701,7 +2629,7 @@
         <v>73.0307117</v>
       </c>
       <c r="J31" t="n">
-        <v>12.39900016784668</v>
+        <v>12.39900017</v>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
@@ -2737,20 +2665,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2214</t>
-        </is>
+      <c r="C32" t="n">
+        <v>2214</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>Nisar Ahmed Jan Sarhandi</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>101719</t>
-        </is>
+      <c r="E32" t="n">
+        <v>101719</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2805,20 +2729,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2319</t>
-        </is>
+      <c r="C33" t="n">
+        <v>2319</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>Sajid Abbasi</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>101864</t>
-        </is>
+      <c r="E33" t="n">
+        <v>101864</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2837,7 +2757,7 @@
         <v>68.3630129</v>
       </c>
       <c r="J33" t="n">
-        <v>11.89900016784668</v>
+        <v>11.89900017</v>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -2873,20 +2793,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>4495</t>
-        </is>
+      <c r="C34" t="n">
+        <v>4495</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>Mirza Amjid Baig</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>116183</t>
-        </is>
+      <c r="E34" t="n">
+        <v>116183</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2905,7 +2821,7 @@
         <v>73.0610652</v>
       </c>
       <c r="J34" t="n">
-        <v>12.44200038909912</v>
+        <v>12.44200039</v>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
@@ -2941,20 +2857,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>4412</t>
-        </is>
+      <c r="C35" t="n">
+        <v>4412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>Ch Arshad Hussain</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>115853</t>
-        </is>
+      <c r="E35" t="n">
+        <v>115853</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2973,7 +2885,7 @@
         <v>73.0781049</v>
       </c>
       <c r="J35" t="n">
-        <v>10.61600017547607</v>
+        <v>10.61600018</v>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
@@ -3009,20 +2921,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
+      <c r="C36" t="n">
+        <v>3269</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>Raham Ali</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>115853</t>
-        </is>
+      <c r="E36" t="n">
+        <v>115853</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3041,7 +2949,7 @@
         <v>73.0781073</v>
       </c>
       <c r="J36" t="n">
-        <v>7.386000156402588</v>
+        <v>7.386000156</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3055,7 +2963,7 @@
         <v>73.07816769999999</v>
       </c>
       <c r="N36" t="n">
-        <v>7.026999950408936</v>
+        <v>7.02699995</v>
       </c>
       <c r="O36" t="n">
         <v>10.1</v>
@@ -3067,7 +2975,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>00:01:10</t>
+          <t>0:01:10</t>
         </is>
       </c>
       <c r="R36" t="n">
@@ -3101,20 +3009,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>5091</t>
-        </is>
+      <c r="C37" t="n">
+        <v>5091</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>Abdullah</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>104459</t>
-        </is>
+      <c r="E37" t="n">
+        <v>104459</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3133,7 +3037,7 @@
         <v>72.8070341</v>
       </c>
       <c r="J37" t="n">
-        <v>20.89999961853027</v>
+        <v>20.89999962</v>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
@@ -3169,20 +3073,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="C38" t="n">
+        <v>2830</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>Nazar Muhammad Kharal</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>118099</t>
-        </is>
+      <c r="E38" t="n">
+        <v>118099</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3237,20 +3137,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>4474</t>
-        </is>
+      <c r="C39" t="n">
+        <v>4474</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>Abdul Razique</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>102014</t>
-        </is>
+      <c r="E39" t="n">
+        <v>102014</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3269,7 +3165,7 @@
         <v>68.3396235</v>
       </c>
       <c r="J39" t="n">
-        <v>45.44499969482422</v>
+        <v>45.44499969</v>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
@@ -3305,20 +3201,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
+      <c r="C40" t="n">
+        <v>4925</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>Usama Tasif</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>119468</t>
-        </is>
+      <c r="E40" t="n">
+        <v>119468</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3337,25 +3229,49 @@
         <v>73.0772733</v>
       </c>
       <c r="J40" t="n">
-        <v>41.46099853515625</v>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
+        <v>41.46099854</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:40:01</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>33.6681196</v>
+      </c>
+      <c r="M40" t="n">
+        <v>73.07715469999999</v>
+      </c>
+      <c r="N40" t="n">
+        <v>33.3769989</v>
+      </c>
+      <c r="O40" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>0:01:28</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>0.0244</v>
+      </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T40" t="n">
         <v>52</v>
       </c>
-      <c r="U40" t="inlineStr"/>
+      <c r="U40" t="n">
+        <v>16.3</v>
+      </c>
       <c r="V40" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -3373,20 +3289,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>4909</t>
-        </is>
+      <c r="C41" t="n">
+        <v>4909</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>Victor Bashir</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>110951</t>
-        </is>
+      <c r="E41" t="n">
+        <v>110951</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3405,33 +3317,1161 @@
         <v>68.3541412</v>
       </c>
       <c r="J41" t="n">
-        <v>42.34199905395508</v>
-      </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
+        <v>42.34199905</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:39:30</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>25.41139</v>
+      </c>
+      <c r="M41" t="n">
+        <v>68.3537833</v>
+      </c>
+      <c r="N41" t="n">
+        <v>7</v>
+      </c>
+      <c r="O41" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>0:00:30</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>0.0083</v>
+      </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T41" t="n">
         <v>27.1</v>
       </c>
-      <c r="U41" t="inlineStr"/>
+      <c r="U41" t="n">
+        <v>12.4</v>
+      </c>
       <c r="V41" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>VIS-20261001103946-F07C03</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>5145</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Iftikhar Ali</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>119547</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PSO S/S 88 (D-12 F/S)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:39:46</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>33.7017142</v>
+      </c>
+      <c r="I42" t="n">
+        <v>72.9466297</v>
+      </c>
+      <c r="J42" t="n">
+        <v>23.12400055</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>VIS-20261001103958-042413</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3613</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Zain Ali</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>119209</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MALIK BASHIR &amp; SONS FS</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:39:58</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>33.5867831</v>
+      </c>
+      <c r="I43" t="n">
+        <v>73.142825</v>
+      </c>
+      <c r="J43" t="n">
+        <v>9.199999808999999</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>VIS-20261001104000-0CC07B</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>4995</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Adnan Arif</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>119209</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>MALIK BASHIR &amp; SONS FS</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:40:00</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>33.56756757</v>
+      </c>
+      <c r="I44" t="n">
+        <v>73.15463472</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>2346</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>VIS-20261001104040-C458DA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Amin Qayyum</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>119468</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>MARWAT FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:40:40</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>33.6682029</v>
+      </c>
+      <c r="I45" t="n">
+        <v>73.07722819999999</v>
+      </c>
+      <c r="J45" t="n">
+        <v>20</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>VIS-20261001104046-B625DA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3024</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Javaid Kamal</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>117538</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>REHMAN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:40:46</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>31.6001003</v>
+      </c>
+      <c r="I46" t="n">
+        <v>74.2996119</v>
+      </c>
+      <c r="J46" t="n">
+        <v>20</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T46" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>VIS-20261001104055-DABFE6</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>5028</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Muhammad Hasnain</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>104241</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>CAPRI FLNG AND SER STN</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:40:55</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>33.7215338</v>
+      </c>
+      <c r="I47" t="n">
+        <v>73.0598349</v>
+      </c>
+      <c r="J47" t="n">
+        <v>14.25399971</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T47" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>VIS-20261001104126-CE5677</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>5017</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sheikh Adnan Atta</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>104241</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CAPRI FLNG AND SER STN</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:41:26</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>33.7215059</v>
+      </c>
+      <c r="I48" t="n">
+        <v>73.05993789999999</v>
+      </c>
+      <c r="J48" t="n">
+        <v>11.07400036</v>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T48" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>VIS-20261001104127-333C18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3598</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Zarak Khan</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>115582</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>TRI STAR PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:41:27</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>33.6435472</v>
+      </c>
+      <c r="I49" t="n">
+        <v>73.03070820000001</v>
+      </c>
+      <c r="J49" t="n">
+        <v>11.70400047</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>VIS-20261001104242-30C6D0</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4533</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Abdul Majid Shaikh</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>120248</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PSO S/S 92 (LANSDOWNE SS)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:42:42</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>27.7130396</v>
+      </c>
+      <c r="I50" t="n">
+        <v>68.84141459999999</v>
+      </c>
+      <c r="J50" t="n">
+        <v>10.48999977111816</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:43:21</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>27.7130091</v>
+      </c>
+      <c r="M50" t="n">
+        <v>68.8413657</v>
+      </c>
+      <c r="N50" t="n">
+        <v>10.37100028991699</v>
+      </c>
+      <c r="O50" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>00:00:39</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
+        <v>21</v>
+      </c>
+      <c r="U50" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>VIS-20261001104305-90FEEA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1647</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Habib Rehman</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>101719</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>M/S POONAM F/S</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:43:05</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>25.3875421</v>
+      </c>
+      <c r="I51" t="n">
+        <v>68.3412222</v>
+      </c>
+      <c r="J51" t="n">
+        <v>20</v>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>VIS-20261001104306-1D3D26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2348</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Shahjahan</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>120248</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PSO S/S 92 (LANSDOWNE SS)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:43:06</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>27.7130219</v>
+      </c>
+      <c r="I52" t="n">
+        <v>68.8413881</v>
+      </c>
+      <c r="J52" t="n">
+        <v>28.10000038146973</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:43:16</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>27.7130303</v>
+      </c>
+      <c r="M52" t="n">
+        <v>68.8413869</v>
+      </c>
+      <c r="N52" t="n">
+        <v>45.6879997253418</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>00:00:10</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T52" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>19</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>VIS-20261001104316-C7DEC5</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2703</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Abdul Khalique Khan</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>101864</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>PLATINUM PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:43:16</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>25.4067108</v>
+      </c>
+      <c r="I53" t="n">
+        <v>68.3629579</v>
+      </c>
+      <c r="J53" t="n">
+        <v>21.85300064086914</v>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>VIS-20261001104331-17C0AE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Raham Ali</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>115853</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>AWAN ASSOCIATES</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:43:31</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>33.7282098</v>
+      </c>
+      <c r="I54" t="n">
+        <v>73.07825149999999</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7.206999778747559</v>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>VIS-20261001104344-7FE52E</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>4594</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Waqas Mustafa Ghouri</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>102505</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>SUPER SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:43:44</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>27.693201</v>
+      </c>
+      <c r="I55" t="n">
+        <v>68.8466837</v>
+      </c>
+      <c r="J55" t="n">
+        <v>24.63699913024902</v>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T55" t="n">
+        <v>25</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>VIS-20261001104348-80B755</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Zain Ahmad</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>120054</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ALI PAK PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:43:48</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>27.6914794</v>
+      </c>
+      <c r="I56" t="n">
+        <v>68.8558573</v>
+      </c>
+      <c r="J56" t="n">
+        <v>22.51000022888184</v>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T56" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>VIS-20261001104425-91BD81</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Muhammad Afzal Arain</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>101611</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>NEW GARDEN SER STN</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:44:25</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>24.8726892</v>
+      </c>
+      <c r="I57" t="n">
+        <v>67.02210239999999</v>
+      </c>
+      <c r="J57" t="n">
+        <v>20</v>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T57" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V41"/>
+  <autoFilter ref="A1:V57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,8 +437,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -2439,23 +2439,47 @@
       <c r="J28" t="n">
         <v>36.52700043</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:44:36</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>33.660425</v>
+      </c>
+      <c r="M28" t="n">
+        <v>73.06313830000001</v>
+      </c>
+      <c r="N28" t="n">
+        <v>39.95800018310547</v>
+      </c>
+      <c r="O28" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>00:09:37</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1603</v>
+      </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T28" t="n">
         <v>33.9</v>
       </c>
-      <c r="U28" t="inlineStr"/>
+      <c r="U28" t="n">
+        <v>18.3</v>
+      </c>
       <c r="V28" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -4447,31 +4471,2215 @@
       <c r="J57" t="n">
         <v>20</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:44:41</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>24.8726912</v>
+      </c>
+      <c r="M57" t="n">
+        <v>67.022102</v>
+      </c>
+      <c r="N57" t="n">
+        <v>20</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>00:00:16</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>0.0044</v>
+      </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T57" t="n">
         <v>22.4</v>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="U57" t="n">
+        <v>22.4</v>
+      </c>
       <c r="V57" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>VIS-20261001104428-910C07</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>4909</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Victor Bashir</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>110951</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>NLC PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:44:28</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>25.4114813</v>
+      </c>
+      <c r="I58" t="n">
+        <v>68.3539834</v>
+      </c>
+      <c r="J58" t="n">
+        <v>38.22499847412109</v>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T58" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>VIS-20261001104436-D2606E</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>4925</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Usama Tasif</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>119468</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>MARWAT FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:44:36</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>33.6681719</v>
+      </c>
+      <c r="I59" t="n">
+        <v>73.0772047</v>
+      </c>
+      <c r="J59" t="n">
+        <v>28.26199913024902</v>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T59" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>VIS-20261001104448-F8AB8C</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4988</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>SYEDA KHADIJA FATIMA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>101664</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>MADINA SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:44:48</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>24.8786544426191</v>
+      </c>
+      <c r="I60" t="n">
+        <v>67.0459278413461</v>
+      </c>
+      <c r="J60" t="n">
+        <v>30.92412171635922</v>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T60" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>VIS-20261001104506-DE9A3D</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3433</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Mansoor ur Rehman</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>118519</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SALEEMI FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:45:06</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>30.1721893</v>
+      </c>
+      <c r="I61" t="n">
+        <v>71.50785329999999</v>
+      </c>
+      <c r="J61" t="n">
+        <v>20</v>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>VIS-20261001104515-5874E9</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Muhammad Afzal Arain</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>101611</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>NEW GARDEN SER STN</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:45:15</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>24.8727028</v>
+      </c>
+      <c r="I62" t="n">
+        <v>67.02208539999999</v>
+      </c>
+      <c r="J62" t="n">
+        <v>20.66799926757812</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:45:50</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>24.8727015</v>
+      </c>
+      <c r="M62" t="n">
+        <v>67.0220905</v>
+      </c>
+      <c r="N62" t="n">
+        <v>16.63100051879883</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>00:00:35</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T62" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="U62" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VIS-20261001104517-4D1E9F</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>4424</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Dhaniyal Petroleum</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>115228</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DHANIYAL PETROLEUM</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:45:17</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>33.6470007</v>
+      </c>
+      <c r="I63" t="n">
+        <v>73.2178428</v>
+      </c>
+      <c r="J63" t="n">
+        <v>12.99199962615967</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:45:48</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>33.6471483</v>
+      </c>
+      <c r="M63" t="n">
+        <v>73.21805000000001</v>
+      </c>
+      <c r="N63" t="n">
+        <v>5.599999904632568</v>
+      </c>
+      <c r="O63" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>00:00:31</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T63" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="U63" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>VIS-20261001104523-A145C6</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2379</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Mashkoor A Shamim</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>115228</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>DHANIYAL PETROLEUM</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:45:23</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>33.6470606</v>
+      </c>
+      <c r="I64" t="n">
+        <v>73.2178771</v>
+      </c>
+      <c r="J64" t="n">
+        <v>16.52899932861328</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:13</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>33.6471213</v>
+      </c>
+      <c r="M64" t="n">
+        <v>73.2179258</v>
+      </c>
+      <c r="N64" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="O64" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>00:00:50</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>20</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VIS-20261001104547-2845E4</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>3726</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Saba irfan</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>101664</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>MADINA SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:45:47</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>24.8787574</v>
+      </c>
+      <c r="I65" t="n">
+        <v>67.0456707</v>
+      </c>
+      <c r="J65" t="n">
+        <v>20.92399978637695</v>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T65" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>VIS-20261001104554-B401B6</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>5212</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Syed Muhammad Umair</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>101664</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>MADINA SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:45:54</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>24.8786695</v>
+      </c>
+      <c r="I66" t="n">
+        <v>67.0456286</v>
+      </c>
+      <c r="J66" t="n">
+        <v>23.92900085449219</v>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T66" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>VIS-20261001104626-260F41</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Hira Fatima</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>115764</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>NOOR FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:26</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>32.9716409</v>
+      </c>
+      <c r="I67" t="n">
+        <v>73.69087829999999</v>
+      </c>
+      <c r="J67" t="n">
+        <v>20</v>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T67" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>VIS-20261001104627-E0046B</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>3118</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Mehar afroze</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>117793</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Q.STAR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:27</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>24.85308776499481</v>
+      </c>
+      <c r="I68" t="n">
+        <v>67.0525579841546</v>
+      </c>
+      <c r="J68" t="n">
+        <v>27.75169213503676</v>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T68" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>VIS-20261001104627-DFB60B</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>4627</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Atif Waqar Toor</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>119649</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>AA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:27</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>33.5159852</v>
+      </c>
+      <c r="I69" t="n">
+        <v>73.0479249</v>
+      </c>
+      <c r="J69" t="n">
+        <v>20</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:44</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>33.5159871</v>
+      </c>
+      <c r="M69" t="n">
+        <v>73.04791950000001</v>
+      </c>
+      <c r="N69" t="n">
+        <v>20</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>00:00:17</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
+        <v>37</v>
+      </c>
+      <c r="U69" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>VIS-20261001104631-86C0E3</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Waqas Ahmad Shah</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>115610</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ALI F/S</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:31</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>31.8445215</v>
+      </c>
+      <c r="I70" t="n">
+        <v>70.9110376</v>
+      </c>
+      <c r="J70" t="n">
+        <v>13.9980001449585</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:45</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>31.8445154</v>
+      </c>
+      <c r="M70" t="n">
+        <v>70.9110506</v>
+      </c>
+      <c r="N70" t="n">
+        <v>20</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>00:00:14</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T70" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>VIS-20261001104645-DC11A8</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>5115</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Hammad Tariq Mirza</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>104263</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>GOLDEN RAYS FILL STN</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:45</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>33.6789538</v>
+      </c>
+      <c r="I71" t="n">
+        <v>72.85060420000001</v>
+      </c>
+      <c r="J71" t="n">
+        <v>33.70399856567383</v>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T71" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>VIS-20261001104650-21D7DD</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Muhammad shariq khan</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>115282</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>RAHEEL SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:50</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>24.8683073</v>
+      </c>
+      <c r="I72" t="n">
+        <v>67.0113163</v>
+      </c>
+      <c r="J72" t="n">
+        <v>13.15299987792969</v>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T72" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>VIS-20261001104653-38E0BF</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>5110</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Syed Kamran Haider</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>102987</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>AMER MAHMOOD FILL STN</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:53</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>30.1918817</v>
+      </c>
+      <c r="I73" t="n">
+        <v>71.4592933</v>
+      </c>
+      <c r="J73" t="n">
+        <v>7.300000190734863</v>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T73" t="n">
+        <v>42.7</v>
+      </c>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>VIS-20261001104657-89673E</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>4664</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Ayesha Khan</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>115569</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>MIAN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:46:57</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>33.7640058</v>
+      </c>
+      <c r="I74" t="n">
+        <v>72.7251741</v>
+      </c>
+      <c r="J74" t="n">
+        <v>14.38599967956543</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T74" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VIS-20261001104702-88991B</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>4627</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Atif Waqar Toor</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>119649</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>AA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:47:02</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>33.5159862</v>
+      </c>
+      <c r="I75" t="n">
+        <v>73.04792019999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>20</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T75" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>VIS-20261001104703-40C4F4</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2877</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Aftab ur rehman</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>115569</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>MIAN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:47:03</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>33.7639874</v>
+      </c>
+      <c r="I76" t="n">
+        <v>72.725165</v>
+      </c>
+      <c r="J76" t="n">
+        <v>14.03699970245361</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T76" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>VIS-20261001104718-E1CB57</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>3337</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Mudassir Altag</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>115764</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NOOR FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:47:18</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>32.9716406</v>
+      </c>
+      <c r="I77" t="n">
+        <v>73.6908055</v>
+      </c>
+      <c r="J77" t="n">
+        <v>5.407000064849854</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T77" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>VIS-20261001104744-EA1D5C</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>4563</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Waqas Ahmad Shah</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>115610</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ALI F/S</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:47:44</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>31.8445109</v>
+      </c>
+      <c r="I78" t="n">
+        <v>70.91106449999999</v>
+      </c>
+      <c r="J78" t="n">
+        <v>20</v>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T78" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>VIS-20261001104816-6F8979</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2803</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Saima aftab</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>115582</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>TRI STAR PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:48:16</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>33.6434987</v>
+      </c>
+      <c r="I79" t="n">
+        <v>73.0307949</v>
+      </c>
+      <c r="J79" t="n">
+        <v>15.92199993133545</v>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T79" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>VIS-20261001104828-74B94A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2441</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Muhammad Faisal Shahzad</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>119649</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>AA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:48:28</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>33.515984</v>
+      </c>
+      <c r="I80" t="n">
+        <v>73.0479237</v>
+      </c>
+      <c r="J80" t="n">
+        <v>20</v>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T80" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>VIS-20261001104838-0FD21F</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Rubbia Moten</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>115569</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>MIAN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:48:38</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>33.76396322193338</v>
+      </c>
+      <c r="I81" t="n">
+        <v>72.72512793827059</v>
+      </c>
+      <c r="J81" t="n">
+        <v>20.65444269134041</v>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T81" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>VIS-20261001104847-2E1C7D</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>4023</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Waqas</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>101781</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>UNEEK SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:48:47</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>25.3761859</v>
+      </c>
+      <c r="I82" t="n">
+        <v>68.35887150000001</v>
+      </c>
+      <c r="J82" t="n">
+        <v>43.55599975585938</v>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T82" t="n">
+        <v>215.4</v>
+      </c>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>VIS-20261001104851-F94B5A</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ilsa Nidal</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>119440</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>PSO S/S 86 (JINNAH)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:48:51</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>24.86738921146792</v>
+      </c>
+      <c r="I83" t="n">
+        <v>67.02498770978858</v>
+      </c>
+      <c r="J83" t="n">
+        <v>39.99802691234568</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T83" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>VIS-20261001104913-7A1B28</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2840</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Saba Ahmed</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>120542</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Al-Asad III</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:49:13</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>24.84804295872743</v>
+      </c>
+      <c r="I84" t="n">
+        <v>67.04645151997653</v>
+      </c>
+      <c r="J84" t="n">
+        <v>7.874778465949883</v>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T84" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>VIS-20261001104918-85B8DE</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2602</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Fahad murtaza</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>117078</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>MODERN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:49:18</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>24.9022105</v>
+      </c>
+      <c r="I85" t="n">
+        <v>67.0294251</v>
+      </c>
+      <c r="J85" t="n">
+        <v>23.11199951171875</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T85" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>VIS-20261001104919-66882F</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2590</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Altaf Khattak</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>119649</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>AA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:49:19</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>33.5159883</v>
+      </c>
+      <c r="I86" t="n">
+        <v>73.04792019999999</v>
+      </c>
+      <c r="J86" t="n">
+        <v>20</v>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T86" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>VIS-20261001104936-41574C</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Shamim Abbas Tarar</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>119062</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>POLICE WELFARE</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:49:36</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>32.9321362</v>
+      </c>
+      <c r="I87" t="n">
+        <v>73.72893209999999</v>
+      </c>
+      <c r="J87" t="n">
+        <v>27.61899948120117</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T87" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V57"/>
+  <autoFilter ref="A1:V87"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V87"/>
+  <dimension ref="A1:V121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -445,7 +445,7 @@
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
@@ -5635,23 +5635,47 @@
       <c r="J72" t="n">
         <v>13.15299987792969</v>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:53</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>24.8683242</v>
+      </c>
+      <c r="M72" t="n">
+        <v>67.01133299999999</v>
+      </c>
+      <c r="N72" t="n">
+        <v>12.42599964141846</v>
+      </c>
+      <c r="O72" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>00:04:03</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>0.0675</v>
+      </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T72" t="n">
         <v>39.3</v>
       </c>
-      <c r="U72" t="inlineStr"/>
+      <c r="U72" t="n">
+        <v>37.1</v>
+      </c>
       <c r="V72" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -6655,31 +6679,2391 @@
       <c r="J87" t="n">
         <v>27.61899948120117</v>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:49:55</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>32.9303542</v>
+      </c>
+      <c r="M87" t="n">
+        <v>73.72902240000001</v>
+      </c>
+      <c r="N87" t="n">
+        <v>15</v>
+      </c>
+      <c r="O87" t="n">
+        <v>198.3</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Some Difference</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>00:00:19</t>
+        </is>
+      </c>
+      <c r="R87" t="n">
+        <v>0.0053</v>
+      </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T87" t="n">
         <v>7.1</v>
       </c>
-      <c r="U87" t="inlineStr"/>
+      <c r="U87" t="n">
+        <v>194.6</v>
+      </c>
       <c r="V87" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>VIS-20261001104950-41B68B</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>1670</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Muhammad Shoaib</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>117078</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>MODERN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:49:50</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>24.9022829</v>
+      </c>
+      <c r="I88" t="n">
+        <v>67.0294418</v>
+      </c>
+      <c r="J88" t="n">
+        <v>20.95000076293945</v>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T88" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>VIS-20261001105021-48B5FA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2179</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Saira shoaib</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>117793</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Q.STAR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:21</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>24.85292598809838</v>
+      </c>
+      <c r="I89" t="n">
+        <v>67.05300793917331</v>
+      </c>
+      <c r="J89" t="n">
+        <v>39.5574247269759</v>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T89" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>VIS-20261001105030-A6707F</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>4031</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Muhammad Zulfiqar Ali</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>102987</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>AMER MAHMOOD FILL STN</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:30</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>30.1920025</v>
+      </c>
+      <c r="I90" t="n">
+        <v>71.45936020000001</v>
+      </c>
+      <c r="J90" t="n">
+        <v>17.0939998626709</v>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T90" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>VIS-20261001105041-FCA636</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>720010</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Adeena Yawer</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>116674</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>PSO S/S -03 (CLIFF PETROLEUM SERVIC</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:41</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>24.8358416</v>
+      </c>
+      <c r="I91" t="n">
+        <v>67.0339041</v>
+      </c>
+      <c r="J91" t="n">
+        <v>33.13600158691406</v>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T91" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>VIS-20261001105042-5BE539</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2185</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Allah Dino Mirani</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>101781</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>UNEEK SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:42</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>25.3757226</v>
+      </c>
+      <c r="I92" t="n">
+        <v>68.3593697</v>
+      </c>
+      <c r="J92" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T92" t="n">
+        <v>223.2</v>
+      </c>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>VIS-20261001105045-0786D6</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Farooq Asghar</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>119290</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>HAIDER JAMAL FS</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:45</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>33.6507583</v>
+      </c>
+      <c r="I93" t="n">
+        <v>73.0624783</v>
+      </c>
+      <c r="J93" t="n">
+        <v>11</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T93" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>VIS-20261001105046-263EFB</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>3597</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Rimsha Iqbal</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>104279</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>TARNAUL FILL STN</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:46</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>33.64683497431298</v>
+      </c>
+      <c r="I94" t="n">
+        <v>72.91575492656544</v>
+      </c>
+      <c r="J94" t="n">
+        <v>39.97399397343361</v>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T94" t="n">
+        <v>46</v>
+      </c>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>VIS-20261001105047-D745C9</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2769</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Rabia yasir Afridi</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>104279</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>TARNAUL FILL STN</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:47</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>33.6467056</v>
+      </c>
+      <c r="I95" t="n">
+        <v>72.915862</v>
+      </c>
+      <c r="J95" t="n">
+        <v>14.9689998626709</v>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T95" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>VIS-20261001105050-F7067F</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>4288</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sana Durrani</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>120542</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Al-Asad III</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:50:50</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>24.8491697</v>
+      </c>
+      <c r="I96" t="n">
+        <v>67.0460279</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5.10200023651123</v>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T96" t="n">
+        <v>122</v>
+      </c>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>VIS-20261001105102-D15202</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>4640</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Waqar Haider</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>120542</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Al-Asad III</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:51:02</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>24.8480536</v>
+      </c>
+      <c r="I97" t="n">
+        <v>67.0466418</v>
+      </c>
+      <c r="J97" t="n">
+        <v>20</v>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T97" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>VIS-20261001105116-83A428</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Aqsa Mumtaz</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>114529</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>NEW STERLING SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:51:16</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>24.84995280796351</v>
+      </c>
+      <c r="I98" t="n">
+        <v>67.020035421549</v>
+      </c>
+      <c r="J98" t="n">
+        <v>16.50806252351778</v>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T98" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>VIS-20261001105117-0CD0A7</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Muhammad shariq khan</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>115282</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>RAHEEL SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:51:17</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>24.868322</v>
+      </c>
+      <c r="I99" t="n">
+        <v>67.0113329</v>
+      </c>
+      <c r="J99" t="n">
+        <v>13.37600040435791</v>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T99" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>VIS-20261001105119-2805FF</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Zainab amir</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>104279</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>TARNAUL FILL STN</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:51:19</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>33.6467155</v>
+      </c>
+      <c r="I100" t="n">
+        <v>72.9158621</v>
+      </c>
+      <c r="J100" t="n">
+        <v>15.24400043487549</v>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T100" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>VIS-20261001105122-4A3011</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>4590</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Muhammad Shahzad Ahmed</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>114529</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>NEW STERLING SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:51:22</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>24.8498061</v>
+      </c>
+      <c r="I101" t="n">
+        <v>67.0200624</v>
+      </c>
+      <c r="J101" t="n">
+        <v>46.70800018310547</v>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T101" t="n">
+        <v>74.3</v>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>VIS-20261001105155-BC3EBC</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2979</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>FAISAL MEHMOOD</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>114662</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SAFA SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:51:55</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>24.8775479</v>
+      </c>
+      <c r="I102" t="n">
+        <v>67.03870499999999</v>
+      </c>
+      <c r="J102" t="n">
+        <v>12.83600044250488</v>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T102" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>VIS-20261001105157-CBB17A</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>4969</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Waqar Ahmed</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>101760</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>HAFEEZ PET.SERVICE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:51:57</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>27.4391835</v>
+      </c>
+      <c r="I103" t="n">
+        <v>68.3903942</v>
+      </c>
+      <c r="J103" t="n">
+        <v>20</v>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T103" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>VIS-20261001105157-2F6F3B</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>4779</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Shaista Faisal</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>114529</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>NEW STERLING SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:51:57</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>24.849752</v>
+      </c>
+      <c r="I104" t="n">
+        <v>67.0200816</v>
+      </c>
+      <c r="J104" t="n">
+        <v>4.099999904632568</v>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T104" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>VIS-20261001105206-1A612D</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>5022</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Ahsan Anwar</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>119440</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>PSO S/S 86 (JINNAH)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:06</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>24.8674145</v>
+      </c>
+      <c r="I105" t="n">
+        <v>67.02487530000001</v>
+      </c>
+      <c r="J105" t="n">
+        <v>11.61800003051758</v>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T105" t="n">
+        <v>27</v>
+      </c>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>VIS-20261001105214-C7BBDE</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Nissa Yasir</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>114662</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SAFA SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:14</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>24.87753756126155</v>
+      </c>
+      <c r="I106" t="n">
+        <v>67.03874965404376</v>
+      </c>
+      <c r="J106" t="n">
+        <v>14.16613577768025</v>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T106" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>VIS-20261001105220-7B3B80</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Raj Kumar</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>101781</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>UNEEK SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:20</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>25.3759748</v>
+      </c>
+      <c r="I107" t="n">
+        <v>68.35921380000001</v>
+      </c>
+      <c r="J107" t="n">
+        <v>4.598999977111816</v>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T107" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>VIS-20261001105221-6A3F8C</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>4930</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>WALEED AHMED</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>116118</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>MEHR BROTHERS</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:21</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>33.6672356</v>
+      </c>
+      <c r="I108" t="n">
+        <v>72.9958242</v>
+      </c>
+      <c r="J108" t="n">
+        <v>12.02400016784668</v>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T108" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>VIS-20261001105226-EC7F25</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>5229</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Muhammad Zain</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>117078</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>MODERN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:26</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>24.9022145</v>
+      </c>
+      <c r="I109" t="n">
+        <v>67.029387</v>
+      </c>
+      <c r="J109" t="n">
+        <v>24.38199996948242</v>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T109" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>VIS-20261001105239-7D43D3</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>5015</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Hassan Shahid</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>115029</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>RIZWAN P/S</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:39</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>30.24163731911212</v>
+      </c>
+      <c r="I110" t="n">
+        <v>71.5022891512978</v>
+      </c>
+      <c r="J110" t="n">
+        <v>39.99172002685452</v>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T110" t="n">
+        <v>676.5</v>
+      </c>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>VIS-20261001105242-7CA521</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>4831</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Saad Aamer</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ZAHOOR FILL STATION</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:42</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>31.3978084</v>
+      </c>
+      <c r="I111" t="n">
+        <v>74.230581</v>
+      </c>
+      <c r="J111" t="n">
+        <v>22.18099975585938</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:57</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>31.3978094</v>
+      </c>
+      <c r="M111" t="n">
+        <v>74.2302263</v>
+      </c>
+      <c r="N111" t="n">
+        <v>22.9109992980957</v>
+      </c>
+      <c r="O111" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>00:00:15</t>
+        </is>
+      </c>
+      <c r="R111" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T111" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="U111" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>VIS-20261001105251-EC52A6</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Inam Ullah</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>117963</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>DHA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:51</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>33.5516627</v>
+      </c>
+      <c r="I112" t="n">
+        <v>73.0923124</v>
+      </c>
+      <c r="J112" t="n">
+        <v>9.975000381469727</v>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T112" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>VIS-20261001105253-B80DCA</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>5173</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>kazim jamil</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>116118</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>MEHR BROTHERS</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:52:53</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>33.6671842</v>
+      </c>
+      <c r="I113" t="n">
+        <v>72.9956275</v>
+      </c>
+      <c r="J113" t="n">
+        <v>15.58199977874756</v>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T113" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>VIS-20261001105308-730C9D</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>5123</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Affan Saleem</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>119547</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>PSO S/S 88 (D-12 F/S)</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:53:08</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>33.7014682</v>
+      </c>
+      <c r="I114" t="n">
+        <v>72.94676010000001</v>
+      </c>
+      <c r="J114" t="n">
+        <v>20.44300079345703</v>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T114" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>VIS-20261001105405-2F4375</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Kashif Alu</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>102604</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>MOONRAYS MODERN</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:54:05</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>30.1852742</v>
+      </c>
+      <c r="I115" t="n">
+        <v>71.4450255</v>
+      </c>
+      <c r="J115" t="n">
+        <v>16.32699966430664</v>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T115" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>VIS-20261001105406-46F2DC</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Muhammad Ilyas Soomro</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>102014</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>QASIMABAD PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:54:06</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>25.4015614</v>
+      </c>
+      <c r="I116" t="n">
+        <v>68.3396561</v>
+      </c>
+      <c r="J116" t="n">
+        <v>14.64599990844727</v>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T116" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>VIS-20261001105419-C1CBBF</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>3165</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Imran Siddique Minhas</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>104263</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>GOLDEN RAYS FILL STN</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:54:19</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>33.6787983</v>
+      </c>
+      <c r="I117" t="n">
+        <v>72.8505183</v>
+      </c>
+      <c r="J117" t="n">
+        <v>5.199999809265137</v>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T117" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>VIS-20261001105429-7D186F</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>4547</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Kamil Iqbal</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>118293</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>PSO S/S 78 (DHA F/S)</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:54:29</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>34.0420036</v>
+      </c>
+      <c r="I118" t="n">
+        <v>71.4306241</v>
+      </c>
+      <c r="J118" t="n">
+        <v>13.51099967956543</v>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T118" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>VIS-20261001105431-1D43C1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>5004</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Mahesh kumar</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>115998</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>GALAXY SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:54:31</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>24.8406871</v>
+      </c>
+      <c r="I119" t="n">
+        <v>67.1335639</v>
+      </c>
+      <c r="J119" t="n">
+        <v>20</v>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T119" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>VIS-20261001105436-4C6C0A</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>4922</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Kanwar Yousuf Ali Khan</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>114662</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>SAFA SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:54:36</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>24.877549</v>
+      </c>
+      <c r="I120" t="n">
+        <v>67.0387083</v>
+      </c>
+      <c r="J120" t="n">
+        <v>11.61800003051758</v>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T120" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>VIS-20261001105454-BD0DE0</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>4976</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Malik Zeshan Khalid</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>120209</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>PSO S/S 91 (GULBERG)</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:54:54</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>24.9386599</v>
+      </c>
+      <c r="I121" t="n">
+        <v>67.0745711</v>
+      </c>
+      <c r="J121" t="n">
+        <v>300</v>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T121" t="n">
+        <v>211.9</v>
+      </c>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V87"/>
+  <autoFilter ref="A1:V121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V121"/>
+  <dimension ref="A1:V166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -9062,8 +9062,3116 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>VIS-20261001105502-59D1C3</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>4681</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Zainab Nawaz</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>120650</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>IFTIKHAR NADEEM &amp; CO.</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:55:02</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>33.57376939470232</v>
+      </c>
+      <c r="I122" t="n">
+        <v>73.03956177176075</v>
+      </c>
+      <c r="J122" t="n">
+        <v>40.31179310774912</v>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T122" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>VIS-20261001105504-C04177</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>5019</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Ghazi Sanaullah</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>112305</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>MOTOCARE F/S</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:55:04</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>33.7041783</v>
+      </c>
+      <c r="I123" t="n">
+        <v>73.07174670000001</v>
+      </c>
+      <c r="J123" t="n">
+        <v>4</v>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T123" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>VIS-20261001105513-E557A2</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Sania tabbasum</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>120650</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>IFTIKHAR NADEEM &amp; CO.</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:55:13</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>33.5738242</v>
+      </c>
+      <c r="I124" t="n">
+        <v>73.0394088</v>
+      </c>
+      <c r="J124" t="n">
+        <v>22.07500076293945</v>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T124" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>VIS-20261001105518-877492</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>4793</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Abdul Bari</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>117753</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>GOLDEN</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:55:18</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>25.3767443</v>
+      </c>
+      <c r="I125" t="n">
+        <v>68.37423149999999</v>
+      </c>
+      <c r="J125" t="n">
+        <v>15.66800022125244</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:55:35</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>25.3768152</v>
+      </c>
+      <c r="M125" t="n">
+        <v>68.3742182</v>
+      </c>
+      <c r="N125" t="n">
+        <v>4.25600004196167</v>
+      </c>
+      <c r="O125" t="n">
+        <v>8</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>00:00:17</t>
+        </is>
+      </c>
+      <c r="R125" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T125" t="n">
+        <v>72</v>
+      </c>
+      <c r="U125" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>VIS-20261001105535-DC625E</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2792</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Abdur Rehman</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>115029</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>RIZWAN P/S</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:55:35</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>30.2414715</v>
+      </c>
+      <c r="I126" t="n">
+        <v>71.5023087</v>
+      </c>
+      <c r="J126" t="n">
+        <v>23.20599937438965</v>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T126" t="n">
+        <v>668</v>
+      </c>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>VIS-20261001105540-CF789A</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2853</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Hina Shakil</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>101703</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>SONY PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:55:40</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>24.8747643</v>
+      </c>
+      <c r="I127" t="n">
+        <v>67.0459053</v>
+      </c>
+      <c r="J127" t="n">
+        <v>10</v>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T127" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>VIS-20261001105547-96CE2D</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Jamal Elahi</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>119290</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>HAIDER JAMAL FS</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:55:47</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>33.6509149</v>
+      </c>
+      <c r="I128" t="n">
+        <v>73.0629636</v>
+      </c>
+      <c r="J128" t="n">
+        <v>18.38699913024902</v>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T128" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>VIS-20261001105550-3A1740</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>4793</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Abdul Bari</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>117753</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>GOLDEN</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:55:50</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>25.3768064</v>
+      </c>
+      <c r="I129" t="n">
+        <v>68.3742211</v>
+      </c>
+      <c r="J129" t="n">
+        <v>7.848999977111816</v>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T129" t="n">
+        <v>76</v>
+      </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>VIS-20261001105602-64AD68</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Zulfiqar Ali</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>114529</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>NEW STERLING SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:02</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>24.8498306</v>
+      </c>
+      <c r="I130" t="n">
+        <v>67.0201023</v>
+      </c>
+      <c r="J130" t="n">
+        <v>20</v>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T130" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>VIS-20261001105606-656BAF</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>5041</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Bushra Taufique</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>101703</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>SONY PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:06</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>24.855112</v>
+      </c>
+      <c r="I131" t="n">
+        <v>67.0079286</v>
+      </c>
+      <c r="J131" t="n">
+        <v>13207.75677138323</v>
+      </c>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T131" t="n">
+        <v>4407.1</v>
+      </c>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>VIS-20261001105609-785929</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>4588</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Raheel Syed</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>117753</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>GOLDEN</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:09</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>25.3769671</v>
+      </c>
+      <c r="I132" t="n">
+        <v>68.3741114</v>
+      </c>
+      <c r="J132" t="n">
+        <v>9.133999824523926</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:36</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>25.3766965</v>
+      </c>
+      <c r="M132" t="n">
+        <v>68.3742604</v>
+      </c>
+      <c r="N132" t="n">
+        <v>17.09600067138672</v>
+      </c>
+      <c r="O132" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>00:00:27</t>
+        </is>
+      </c>
+      <c r="R132" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T132" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="U132" t="n">
+        <v>71</v>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>VIS-20261001105611-B5FE97</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Izhar Ahmed</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>101703</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SONY PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:11</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>24.87503691539372</v>
+      </c>
+      <c r="I133" t="n">
+        <v>67.04590667242732</v>
+      </c>
+      <c r="J133" t="n">
+        <v>39.99946584676781</v>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T133" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U133" t="inlineStr"/>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>VIS-20261001105630-CDEFC7</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>3968</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Wazir Muhammad</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>115610</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ALI F/S</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:30</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>31.844438</v>
+      </c>
+      <c r="I134" t="n">
+        <v>70.91088430000001</v>
+      </c>
+      <c r="J134" t="n">
+        <v>20.38599967956543</v>
+      </c>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T134" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="U134" t="inlineStr"/>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>VIS-20261001105630-C9FA87</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>4955</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Muhammad Umair Shaikh</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>101734</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>PSO S/S 23 (DEFENCE)</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:30</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>24.8417596</v>
+      </c>
+      <c r="I135" t="n">
+        <v>67.05916499999999</v>
+      </c>
+      <c r="J135" t="n">
+        <v>20</v>
+      </c>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T135" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U135" t="inlineStr"/>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>VIS-20261001105639-EE915E</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>3244</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Shahid Nawaz</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>102604</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>MOONRAYS MODERN</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:39</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>30.1852636</v>
+      </c>
+      <c r="I136" t="n">
+        <v>71.44496839999999</v>
+      </c>
+      <c r="J136" t="n">
+        <v>29.12199974060059</v>
+      </c>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T136" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="U136" t="inlineStr"/>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>VIS-20261001105645-18635A</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>4371</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Qaiser nawab</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>115998</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>GALAXY SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:45</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>24.8406892</v>
+      </c>
+      <c r="I137" t="n">
+        <v>67.1335411</v>
+      </c>
+      <c r="J137" t="n">
+        <v>20</v>
+      </c>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T137" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="U137" t="inlineStr"/>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>VIS-20261001105646-8C228A</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Muhammad Ahmed</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>119124</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>QURBAN SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:46</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>24.8286255</v>
+      </c>
+      <c r="I138" t="n">
+        <v>67.0427437</v>
+      </c>
+      <c r="J138" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T138" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="U138" t="inlineStr"/>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>VIS-20261001105649-F94749</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Waqar Ali</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>112305</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>MOTOCARE F/S</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:56:49</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>33.7042514</v>
+      </c>
+      <c r="I139" t="n">
+        <v>73.0719127</v>
+      </c>
+      <c r="J139" t="n">
+        <v>13.73299980163574</v>
+      </c>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T139" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="U139" t="inlineStr"/>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>VIS-20261001105706-8F377E</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>4858</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Sania javed</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>119124</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>QURBAN SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:57:06</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>24.8285316</v>
+      </c>
+      <c r="I140" t="n">
+        <v>67.0426619</v>
+      </c>
+      <c r="J140" t="n">
+        <v>64.61799621582031</v>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T140" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="U140" t="inlineStr"/>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>VIS-20261001105726-DE3871</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2133</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>ADNAN AZMATULLAH KHAN</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>115998</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>GALAXY SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:57:26</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>24.8406936</v>
+      </c>
+      <c r="I141" t="n">
+        <v>67.1335413</v>
+      </c>
+      <c r="J141" t="n">
+        <v>13.24300003051758</v>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="U141" t="inlineStr"/>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>VIS-20261001105732-1E98D7</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>3489</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Zaheer Ahmed</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>119394</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>MIDTOWN SERVICES</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:57:32</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>30.2059372</v>
+      </c>
+      <c r="I142" t="n">
+        <v>71.50274330000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>6.749000072479248</v>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T142" t="n">
+        <v>223.3</v>
+      </c>
+      <c r="U142" t="inlineStr"/>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>VIS-20261001105741-30AFEB</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2768</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>M FAISAL CHISHTI</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>119124</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>QURBAN SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:57:41</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>24.8287713</v>
+      </c>
+      <c r="I143" t="n">
+        <v>67.0424833</v>
+      </c>
+      <c r="J143" t="n">
+        <v>3.789999961853027</v>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T143" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="U143" t="inlineStr"/>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>VIS-20261001105746-B93FA5</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>3032</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Nazia Qadeem</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>113349</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>AQEEL SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:57:46</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>24.8623834</v>
+      </c>
+      <c r="I144" t="n">
+        <v>67.0699853</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.57199859619141</v>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T144" t="n">
+        <v>12691.8</v>
+      </c>
+      <c r="U144" t="inlineStr"/>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>VIS-20261001105816-592B2E</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Mohammad Lal Khan</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>116118</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>MEHR BROTHERS</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:16</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>33.66724533507718</v>
+      </c>
+      <c r="I145" t="n">
+        <v>72.9954476124025</v>
+      </c>
+      <c r="J145" t="n">
+        <v>32.64382039651886</v>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T145" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="U145" t="inlineStr"/>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>VIS-20261001105827-2EE72B</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>720015</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Fatima Bibi</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>102404</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>GN P/S</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:27</t>
+        </is>
+      </c>
+      <c r="H146" t="n">
+        <v>24.8611944</v>
+      </c>
+      <c r="I146" t="n">
+        <v>67.0432599</v>
+      </c>
+      <c r="J146" t="n">
+        <v>14.33600044250488</v>
+      </c>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T146" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U146" t="inlineStr"/>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>VIS-20261001105828-30E57B</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>3565</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Muhammad Jawad</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>120542</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Al-Asad III</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:28</t>
+        </is>
+      </c>
+      <c r="H147" t="n">
+        <v>24.8480556</v>
+      </c>
+      <c r="I147" t="n">
+        <v>67.0466342</v>
+      </c>
+      <c r="J147" t="n">
+        <v>21.39999961853027</v>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T147" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="U147" t="inlineStr"/>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>VIS-20261001105830-B301D5</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>720018</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Haleema jamal</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>102404</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>GN P/S</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:30</t>
+        </is>
+      </c>
+      <c r="H148" t="n">
+        <v>24.86114197149691</v>
+      </c>
+      <c r="I148" t="n">
+        <v>67.04317511137465</v>
+      </c>
+      <c r="J148" t="n">
+        <v>27.98754535605991</v>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T148" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="U148" t="inlineStr"/>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>VIS-20261001105834-E6ED40</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>5008</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Faiqa Khawar</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>117116</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>HAMSAFAR GASOLINE</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:34</t>
+        </is>
+      </c>
+      <c r="H149" t="n">
+        <v>24.8691845</v>
+      </c>
+      <c r="I149" t="n">
+        <v>67.02300049999999</v>
+      </c>
+      <c r="J149" t="n">
+        <v>12.67300033569336</v>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T149" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="U149" t="inlineStr"/>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>VIS-20261001105834-871DE9</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>4465</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Noshaba sheikh</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>120542</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Al-Asad III</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:34</t>
+        </is>
+      </c>
+      <c r="H150" t="n">
+        <v>24.8480512</v>
+      </c>
+      <c r="I150" t="n">
+        <v>67.04663770000001</v>
+      </c>
+      <c r="J150" t="n">
+        <v>20</v>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T150" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="U150" t="inlineStr"/>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>VIS-20261001105836-C76BD7</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>5252</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>col Junaid Salahuddin Swati</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>102404</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>GN P/S</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:36</t>
+        </is>
+      </c>
+      <c r="H151" t="n">
+        <v>24.855112</v>
+      </c>
+      <c r="I151" t="n">
+        <v>67.0079286</v>
+      </c>
+      <c r="J151" t="n">
+        <v>13207.75677138323</v>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T151" t="n">
+        <v>3637.1</v>
+      </c>
+      <c r="U151" t="inlineStr"/>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>VIS-20261001105843-45D317</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2559</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>REHAN SAJID</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>118519</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>SALEEMI FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:43</t>
+        </is>
+      </c>
+      <c r="H152" t="n">
+        <v>30.1721818</v>
+      </c>
+      <c r="I152" t="n">
+        <v>71.5078407</v>
+      </c>
+      <c r="J152" t="n">
+        <v>20</v>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T152" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U152" t="inlineStr"/>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>VIS-20261001105845-593A29</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Sarah Akber</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>117116</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>HAMSAFAR GASOLINE</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:45</t>
+        </is>
+      </c>
+      <c r="H153" t="n">
+        <v>24.8691737</v>
+      </c>
+      <c r="I153" t="n">
+        <v>67.02300320000001</v>
+      </c>
+      <c r="J153" t="n">
+        <v>20</v>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T153" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U153" t="inlineStr"/>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>VIS-20261001105846-2CA70E</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>4246</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Yasir Mehmood</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>118042</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2F PETROLEUM  SERVICE</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:46</t>
+        </is>
+      </c>
+      <c r="H154" t="n">
+        <v>24.8841264</v>
+      </c>
+      <c r="I154" t="n">
+        <v>67.04038079999999</v>
+      </c>
+      <c r="J154" t="n">
+        <v>13.22700023651123</v>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T154" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="U154" t="inlineStr"/>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>VIS-20261001105848-C7A5C4</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Waqas Siddiqui</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>120239</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>PSO S/S 93 (WALL STREET)</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:48</t>
+        </is>
+      </c>
+      <c r="H155" t="n">
+        <v>24.8497517</v>
+      </c>
+      <c r="I155" t="n">
+        <v>67.0070458</v>
+      </c>
+      <c r="J155" t="n">
+        <v>19.72599983215332</v>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T155" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="U155" t="inlineStr"/>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>VIS-20261001105849-030266</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>3603</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Ali Gohar</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>117713</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>DUA PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:58:49</t>
+        </is>
+      </c>
+      <c r="H156" t="n">
+        <v>27.6772301</v>
+      </c>
+      <c r="I156" t="n">
+        <v>68.85894260000001</v>
+      </c>
+      <c r="J156" t="n">
+        <v>15.74600028991699</v>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T156" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U156" t="inlineStr"/>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>VIS-20261001105901-731485</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>ABDUL REHMAN</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>119124</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>QURBAN SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:59:01</t>
+        </is>
+      </c>
+      <c r="H157" t="n">
+        <v>24.8287682</v>
+      </c>
+      <c r="I157" t="n">
+        <v>67.0427454</v>
+      </c>
+      <c r="J157" t="n">
+        <v>23.55900001525879</v>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T157" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U157" t="inlineStr"/>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>VIS-20261001105917-40866A</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>3912</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Malik Mubin Ahmed</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>117439</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>GARDEN PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:59:17</t>
+        </is>
+      </c>
+      <c r="H158" t="n">
+        <v>24.8745729</v>
+      </c>
+      <c r="I158" t="n">
+        <v>67.0195512</v>
+      </c>
+      <c r="J158" t="n">
+        <v>39.65399932861328</v>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T158" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="U158" t="inlineStr"/>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>VIS-20261001105926-CA17E9</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Shakeel Ahmed</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>117342</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>JAUHAR AUTOS</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:59:26</t>
+        </is>
+      </c>
+      <c r="H159" t="n">
+        <v>24.8768565</v>
+      </c>
+      <c r="I159" t="n">
+        <v>67.0843702</v>
+      </c>
+      <c r="J159" t="n">
+        <v>43.95299911499023</v>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T159" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U159" t="inlineStr"/>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>VIS-20261001105927-7B47AA</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>710003</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Hafiz Abdur Rafay Khan</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>120542</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Al-Asad III</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:59:27</t>
+        </is>
+      </c>
+      <c r="H160" t="n">
+        <v>24.8480461</v>
+      </c>
+      <c r="I160" t="n">
+        <v>67.0466316</v>
+      </c>
+      <c r="J160" t="n">
+        <v>20</v>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T160" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="U160" t="inlineStr"/>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>VIS-20261001105937-DDE096</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>5109</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Muhammad Hamad Asghar</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>104286</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>PEARL FILL STATION</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:59:37</t>
+        </is>
+      </c>
+      <c r="H161" t="n">
+        <v>33.66048659606437</v>
+      </c>
+      <c r="I161" t="n">
+        <v>73.06319448450017</v>
+      </c>
+      <c r="J161" t="n">
+        <v>27.095014</v>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T161" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U161" t="inlineStr"/>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>VIS-20261001105939-E59462</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Muhammad Atif Latif</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>118042</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2F PETROLEUM  SERVICE</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:59:39</t>
+        </is>
+      </c>
+      <c r="H162" t="n">
+        <v>24.8841007722626</v>
+      </c>
+      <c r="I162" t="n">
+        <v>67.04048875538794</v>
+      </c>
+      <c r="J162" t="n">
+        <v>40</v>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T162" t="n">
+        <v>18</v>
+      </c>
+      <c r="U162" t="inlineStr"/>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>VIS-20261001105945-1C50DB</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>720023</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Saif Ali Toor</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>110575</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>NAJMUL GASOLINE</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-10-01 10:59:45</t>
+        </is>
+      </c>
+      <c r="H163" t="n">
+        <v>24.8865446</v>
+      </c>
+      <c r="I163" t="n">
+        <v>67.0314235</v>
+      </c>
+      <c r="J163" t="n">
+        <v>18.98299980163574</v>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T163" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="U163" t="inlineStr"/>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>VIS-20261001110009-5D28D2</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>4254</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Hasan Abbas Jaffery</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>110575</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>NAJMUL GASOLINE</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:09</t>
+        </is>
+      </c>
+      <c r="H164" t="n">
+        <v>24.8866128</v>
+      </c>
+      <c r="I164" t="n">
+        <v>67.031409</v>
+      </c>
+      <c r="J164" t="n">
+        <v>14.28499984741211</v>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T164" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="U164" t="inlineStr"/>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>VIS-20261001110009-D1D434</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>2433</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Dharmoo Vishan Das</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>117439</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>GARDEN PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:09</t>
+        </is>
+      </c>
+      <c r="H165" t="n">
+        <v>24.8743626</v>
+      </c>
+      <c r="I165" t="n">
+        <v>67.0201385</v>
+      </c>
+      <c r="J165" t="n">
+        <v>29.31900024414062</v>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T165" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="U165" t="inlineStr"/>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>VIS-20261001110010-272FE9</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Muhammad Faisal</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>110575</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>NAJMUL GASOLINE</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:10</t>
+        </is>
+      </c>
+      <c r="H166" t="n">
+        <v>24.8866032</v>
+      </c>
+      <c r="I166" t="n">
+        <v>67.0313938</v>
+      </c>
+      <c r="J166" t="n">
+        <v>21.95299911499023</v>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T166" t="n">
+        <v>21</v>
+      </c>
+      <c r="U166" t="inlineStr"/>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V121"/>
+  <autoFilter ref="A1:V166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V166"/>
+  <dimension ref="A1:V202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -10107,23 +10107,47 @@
       <c r="J136" t="n">
         <v>29.12199974060059</v>
       </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:04:37</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>30.1855988</v>
+      </c>
+      <c r="M136" t="n">
+        <v>71.4449122</v>
+      </c>
+      <c r="N136" t="n">
+        <v>19.2189998626709</v>
+      </c>
+      <c r="O136" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>00:07:58</t>
+        </is>
+      </c>
+      <c r="R136" t="n">
+        <v>0.1328</v>
+      </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T136" t="n">
         <v>55.5</v>
       </c>
-      <c r="U136" t="inlineStr"/>
+      <c r="U136" t="n">
+        <v>20.3</v>
+      </c>
       <c r="V136" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -12170,8 +12194,2480 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>VIS-20261001110021-1AAFD3</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>4828</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Muhammad Jibran Alam</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>110575</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>NAJMUL GASOLINE</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:21</t>
+        </is>
+      </c>
+      <c r="H167" t="n">
+        <v>24.8865944</v>
+      </c>
+      <c r="I167" t="n">
+        <v>67.03141720000001</v>
+      </c>
+      <c r="J167" t="n">
+        <v>23.7180004119873</v>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T167" t="n">
+        <v>19</v>
+      </c>
+      <c r="U167" t="inlineStr"/>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>VIS-20261001110030-5DC0D8</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>2123</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Zafur Akhlaque</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>117342</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>JAUHAR AUTOS</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:30</t>
+        </is>
+      </c>
+      <c r="H168" t="n">
+        <v>24.8766373</v>
+      </c>
+      <c r="I168" t="n">
+        <v>67.0845525</v>
+      </c>
+      <c r="J168" t="n">
+        <v>45.08100128173828</v>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T168" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="U168" t="inlineStr"/>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>VIS-20261001110037-F51EA1</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>720007</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Faisal Hussain</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>117116</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>HAMSAFAR GASOLINE</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:37</t>
+        </is>
+      </c>
+      <c r="H169" t="n">
+        <v>24.86926790329317</v>
+      </c>
+      <c r="I169" t="n">
+        <v>67.0230777057663</v>
+      </c>
+      <c r="J169" t="n">
+        <v>2.832659751176949</v>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T169" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="U169" t="inlineStr"/>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>VIS-20261001110041-222F6E</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>1192</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Wasin Baig</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>117753</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>GOLDEN</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:41</t>
+        </is>
+      </c>
+      <c r="H170" t="n">
+        <v>25.3766892</v>
+      </c>
+      <c r="I170" t="n">
+        <v>68.3742608</v>
+      </c>
+      <c r="J170" t="n">
+        <v>18.63599967956543</v>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T170" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="U170" t="inlineStr"/>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>VIS-20261001110057-5590AA</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>5009</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Hira Anees</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>116674</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>PSO S/S -03 (CLIFF PETROLEUM SERVIC</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:57</t>
+        </is>
+      </c>
+      <c r="H171" t="n">
+        <v>24.83560314662919</v>
+      </c>
+      <c r="I171" t="n">
+        <v>67.03364999928117</v>
+      </c>
+      <c r="J171" t="n">
+        <v>25.1447767135784</v>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T171" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="U171" t="inlineStr"/>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>VIS-20261001110059-6D4153</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Sidra Nawab</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>101608</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>BROTHERS SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:59</t>
+        </is>
+      </c>
+      <c r="H172" t="n">
+        <v>24.8670526</v>
+      </c>
+      <c r="I172" t="n">
+        <v>67.0837849</v>
+      </c>
+      <c r="J172" t="n">
+        <v>42.89699935913086</v>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T172" t="n">
+        <v>178.8</v>
+      </c>
+      <c r="U172" t="inlineStr"/>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>VIS-20261001110059-7C4B7B</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Imran Ahmed</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>101728</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>NASEER GASOLINE</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:00:59</t>
+        </is>
+      </c>
+      <c r="H173" t="n">
+        <v>24.8611997</v>
+      </c>
+      <c r="I173" t="n">
+        <v>67.00147010000001</v>
+      </c>
+      <c r="J173" t="n">
+        <v>18.29800033569336</v>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T173" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="U173" t="inlineStr"/>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>VIS-20261001110111-6FDBD2</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>2296</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Irshad Qureshi</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>110575</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>NAJMUL GASOLINE</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:01:11</t>
+        </is>
+      </c>
+      <c r="H174" t="n">
+        <v>24.8865948</v>
+      </c>
+      <c r="I174" t="n">
+        <v>67.0314036</v>
+      </c>
+      <c r="J174" t="n">
+        <v>13.07299995422363</v>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T174" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="U174" t="inlineStr"/>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>VIS-20261001110116-00444C</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>2563</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Ahmer Faraz</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>117439</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>GARDEN PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:01:16</t>
+        </is>
+      </c>
+      <c r="H175" t="n">
+        <v>24.87435255879454</v>
+      </c>
+      <c r="I175" t="n">
+        <v>67.0201348975551</v>
+      </c>
+      <c r="J175" t="n">
+        <v>13.99999999827343</v>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T175" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U175" t="inlineStr"/>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>VIS-20261001110120-FBB455</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>4761</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Abdullah</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>110299</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>HOOR PETROLEUM SERVICES</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:01:20</t>
+        </is>
+      </c>
+      <c r="H176" t="n">
+        <v>24.8837608</v>
+      </c>
+      <c r="I176" t="n">
+        <v>67.0469052</v>
+      </c>
+      <c r="J176" t="n">
+        <v>21.95400047302246</v>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T176" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="U176" t="inlineStr"/>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>VIS-20261001110123-6C5C86</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Aadil Mukhtiar</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>119145</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>KA ENERGY</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:01:23</t>
+        </is>
+      </c>
+      <c r="H177" t="n">
+        <v>30.2106117</v>
+      </c>
+      <c r="I177" t="n">
+        <v>71.4856635</v>
+      </c>
+      <c r="J177" t="n">
+        <v>20.14399909973145</v>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T177" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="U177" t="inlineStr"/>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>VIS-20261001110132-7C42C3</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>2473</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Muhammad Abdullah</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>117963</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>DHA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:01:32</t>
+        </is>
+      </c>
+      <c r="H178" t="n">
+        <v>33.5516682</v>
+      </c>
+      <c r="I178" t="n">
+        <v>73.0922973</v>
+      </c>
+      <c r="J178" t="n">
+        <v>18.69099998474121</v>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T178" t="n">
+        <v>18</v>
+      </c>
+      <c r="U178" t="inlineStr"/>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>VIS-20261001110140-CDDE57</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>5127</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Anoshia</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>101608</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>BROTHERS SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:01:40</t>
+        </is>
+      </c>
+      <c r="H179" t="n">
+        <v>24.86706</v>
+      </c>
+      <c r="I179" t="n">
+        <v>67.0838193</v>
+      </c>
+      <c r="J179" t="n">
+        <v>20</v>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T179" t="n">
+        <v>175.3</v>
+      </c>
+      <c r="U179" t="inlineStr"/>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>VIS-20261001110147-B19DEC</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>4712</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Sameea Jamal</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>119508</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>PSO S/S 87(SINDH)</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:01:47</t>
+        </is>
+      </c>
+      <c r="H180" t="n">
+        <v>24.8559852</v>
+      </c>
+      <c r="I180" t="n">
+        <v>67.0197229</v>
+      </c>
+      <c r="J180" t="n">
+        <v>6</v>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T180" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="U180" t="inlineStr"/>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>VIS-20261001110153-6D7000</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>3955</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Shumaila waseem</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>119508</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>PSO S/S 87(SINDH)</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:01:53</t>
+        </is>
+      </c>
+      <c r="H181" t="n">
+        <v>24.85597197221806</v>
+      </c>
+      <c r="I181" t="n">
+        <v>67.01974422551488</v>
+      </c>
+      <c r="J181" t="n">
+        <v>4.360185004425122</v>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T181" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="U181" t="inlineStr"/>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>VIS-20261001110206-EDEF25</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Iftikhar Amanat</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>101728</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>NASEER GASOLINE</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:02:06</t>
+        </is>
+      </c>
+      <c r="H182" t="n">
+        <v>24.861163</v>
+      </c>
+      <c r="I182" t="n">
+        <v>67.0015239</v>
+      </c>
+      <c r="J182" t="n">
+        <v>20.36700057983398</v>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T182" t="n">
+        <v>6</v>
+      </c>
+      <c r="U182" t="inlineStr"/>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>VIS-20261001110209-3075B8</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>3617</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Khalil Ur Rehman</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>101608</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>BROTHERS SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:02:09</t>
+        </is>
+      </c>
+      <c r="H183" t="n">
+        <v>24.8671362</v>
+      </c>
+      <c r="I183" t="n">
+        <v>67.0837803</v>
+      </c>
+      <c r="J183" t="n">
+        <v>10.42599964141846</v>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T183" t="n">
+        <v>179.4</v>
+      </c>
+      <c r="U183" t="inlineStr"/>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>VIS-20261001110217-960D87</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>2303</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Rana Muhammad Idrees</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>101580</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>MANSOOR SER STATION</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:02:17</t>
+        </is>
+      </c>
+      <c r="H184" t="n">
+        <v>24.90282</v>
+      </c>
+      <c r="I184" t="n">
+        <v>67.02449249999999</v>
+      </c>
+      <c r="J184" t="n">
+        <v>11.47900009155273</v>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="U184" t="inlineStr"/>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>VIS-20261001110227-EADC99</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Muhammad Adeel Bakhtiar Siddiqui</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>117116</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>HAMSAFAR GASOLINE</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:02:27</t>
+        </is>
+      </c>
+      <c r="H185" t="n">
+        <v>24.8691798</v>
+      </c>
+      <c r="I185" t="n">
+        <v>67.02300820000001</v>
+      </c>
+      <c r="J185" t="n">
+        <v>20</v>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T185" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U185" t="inlineStr"/>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>VIS-20261001110232-36ACA7</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>2195</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Sajid Ali Channa</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>101580</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>MANSOOR SER STATION</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:02:32</t>
+        </is>
+      </c>
+      <c r="H186" t="n">
+        <v>24.9028984</v>
+      </c>
+      <c r="I186" t="n">
+        <v>67.0243729</v>
+      </c>
+      <c r="J186" t="n">
+        <v>14.23700046539307</v>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T186" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="U186" t="inlineStr"/>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>VIS-20261001110243-783DCB</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>3526</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Kamran</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>116250</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>BISMILLAH GASOLINE SERVICE</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:02:43</t>
+        </is>
+      </c>
+      <c r="H187" t="n">
+        <v>24.8256561</v>
+      </c>
+      <c r="I187" t="n">
+        <v>67.15291259999999</v>
+      </c>
+      <c r="J187" t="n">
+        <v>20</v>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T187" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="U187" t="inlineStr"/>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>VIS-20261001110245-569368</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>4987</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Muhammad Qasim Malik</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>119840</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>TAJ - 8 F/S</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:02:45</t>
+        </is>
+      </c>
+      <c r="H188" t="n">
+        <v>31.4378072</v>
+      </c>
+      <c r="I188" t="n">
+        <v>73.0914528</v>
+      </c>
+      <c r="J188" t="n">
+        <v>13.16199970245361</v>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T188" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="U188" t="inlineStr"/>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>VIS-20261001110307-ECEE52</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>4665</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Naeema</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>114723</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>STADIUM SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:03:07</t>
+        </is>
+      </c>
+      <c r="H189" t="n">
+        <v>24.8909872</v>
+      </c>
+      <c r="I189" t="n">
+        <v>67.0768018</v>
+      </c>
+      <c r="J189" t="n">
+        <v>7.652999877929688</v>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T189" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="U189" t="inlineStr"/>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>VIS-20261001110349-14DFB8</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>5062</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>MOHAMMAD ZOHAIB BHOMBAL</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>116219</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>M.S TARIQ PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:03:49</t>
+        </is>
+      </c>
+      <c r="H190" t="n">
+        <v>24.8907136</v>
+      </c>
+      <c r="I190" t="n">
+        <v>67.038422</v>
+      </c>
+      <c r="J190" t="n">
+        <v>28.90900039672852</v>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T190" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="U190" t="inlineStr"/>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>VIS-20261001110350-AF8F9C</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>3956</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Rehan zaidi</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>101728</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>NASEER GASOLINE</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:03:50</t>
+        </is>
+      </c>
+      <c r="H191" t="n">
+        <v>24.8611091</v>
+      </c>
+      <c r="I191" t="n">
+        <v>67.0016445</v>
+      </c>
+      <c r="J191" t="n">
+        <v>23.70199966430664</v>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T191" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="U191" t="inlineStr"/>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>VIS-20261001110351-942BAF</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>2625</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>REHAN MASUD</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>119840</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>TAJ - 8 F/S</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:03:51</t>
+        </is>
+      </c>
+      <c r="H192" t="n">
+        <v>31.4378109</v>
+      </c>
+      <c r="I192" t="n">
+        <v>73.09144430000001</v>
+      </c>
+      <c r="J192" t="n">
+        <v>9.314000129699707</v>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T192" t="n">
+        <v>27</v>
+      </c>
+      <c r="U192" t="inlineStr"/>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>VIS-20261001110352-3F9917</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>4873</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Muhammad Usman</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>117793</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Q.STAR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:03:52</t>
+        </is>
+      </c>
+      <c r="H193" t="n">
+        <v>24.8531632</v>
+      </c>
+      <c r="I193" t="n">
+        <v>67.05293829999999</v>
+      </c>
+      <c r="J193" t="n">
+        <v>4</v>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T193" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="U193" t="inlineStr"/>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>VIS-20261001110403-B4A9D7</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Mehmood Ali</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>118042</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2F PETROLEUM  SERVICE</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:04:03</t>
+        </is>
+      </c>
+      <c r="H194" t="n">
+        <v>24.884125</v>
+      </c>
+      <c r="I194" t="n">
+        <v>67.04037870000001</v>
+      </c>
+      <c r="J194" t="n">
+        <v>20</v>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T194" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="U194" t="inlineStr"/>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>VIS-20261001110419-0DB77F</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2608</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Muhammad Siddique Rind</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>102404</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>GN P/S</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:04:19</t>
+        </is>
+      </c>
+      <c r="H195" t="n">
+        <v>24.8612049</v>
+      </c>
+      <c r="I195" t="n">
+        <v>67.04324630000001</v>
+      </c>
+      <c r="J195" t="n">
+        <v>12.72999954223633</v>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T195" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="U195" t="inlineStr"/>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>VIS-20261001110427-CBF3A6</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>4830</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Muhammad Ibrahim</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>116219</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>M.S TARIQ PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:04:27</t>
+        </is>
+      </c>
+      <c r="H196" t="n">
+        <v>24.8899233</v>
+      </c>
+      <c r="I196" t="n">
+        <v>67.0387417</v>
+      </c>
+      <c r="J196" t="n">
+        <v>11</v>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T196" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="U196" t="inlineStr"/>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>VIS-20261001110428-80E903</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>4290</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Shahzadi Mehboob</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>101734</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>PSO S/S 23 (DEFENCE)</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:04:28</t>
+        </is>
+      </c>
+      <c r="H197" t="n">
+        <v>24.8417615</v>
+      </c>
+      <c r="I197" t="n">
+        <v>67.0591428</v>
+      </c>
+      <c r="J197" t="n">
+        <v>28.10000038146973</v>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T197" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U197" t="inlineStr"/>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>VIS-20261001110437-5D52B5</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>3989</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Syed kamal Shah</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>115816</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>A-ONE PETROLEUM</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:04:37</t>
+        </is>
+      </c>
+      <c r="H198" t="n">
+        <v>33.6812001</v>
+      </c>
+      <c r="I198" t="n">
+        <v>73.0383714</v>
+      </c>
+      <c r="J198" t="n">
+        <v>11.30599975585938</v>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:04:51</t>
+        </is>
+      </c>
+      <c r="L198" t="n">
+        <v>33.6812099</v>
+      </c>
+      <c r="M198" t="n">
+        <v>73.0383674</v>
+      </c>
+      <c r="N198" t="n">
+        <v>11.43200016021729</v>
+      </c>
+      <c r="O198" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>00:00:14</t>
+        </is>
+      </c>
+      <c r="R198" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T198" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="U198" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>VIS-20261001110523-96D63F</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2349</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Attiqullah Khan</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>117315</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>NOOR PS</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:05:23</t>
+        </is>
+      </c>
+      <c r="H199" t="n">
+        <v>24.8602303</v>
+      </c>
+      <c r="I199" t="n">
+        <v>67.0569249</v>
+      </c>
+      <c r="J199" t="n">
+        <v>15.74600028991699</v>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T199" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U199" t="inlineStr"/>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>VIS-20261001110533-094406</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>4986</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Zain Imdad</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>101744</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>RASHIDI P/SER</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:05:33</t>
+        </is>
+      </c>
+      <c r="H200" t="n">
+        <v>27.53631507216626</v>
+      </c>
+      <c r="I200" t="n">
+        <v>68.7146342259073</v>
+      </c>
+      <c r="J200" t="n">
+        <v>48.53384830226442</v>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T200" t="n">
+        <v>44</v>
+      </c>
+      <c r="U200" t="inlineStr"/>
+      <c r="V200" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>VIS-20261001110538-E0AE02</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>500933</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Muhammad Junaid Pervaiz</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>110696</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>VENUS SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:05:38</t>
+        </is>
+      </c>
+      <c r="H201" t="n">
+        <v>24.84418</v>
+      </c>
+      <c r="I201" t="n">
+        <v>67.16146500000001</v>
+      </c>
+      <c r="J201" t="n">
+        <v>47.31700134277344</v>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T201" t="n">
+        <v>274.2</v>
+      </c>
+      <c r="U201" t="inlineStr"/>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>VIS-20261001110539-9F0525</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>4001</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Saba Shoaib</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>117315</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>NOOR PS</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:05:39</t>
+        </is>
+      </c>
+      <c r="H202" t="n">
+        <v>24.860279</v>
+      </c>
+      <c r="I202" t="n">
+        <v>67.0569174</v>
+      </c>
+      <c r="J202" t="n">
+        <v>14.64500045776367</v>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T202" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="U202" t="inlineStr"/>
+      <c r="V202" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V166"/>
+  <autoFilter ref="A1:V202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V202"/>
+  <dimension ref="A1:V203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -14666,8 +14666,76 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>VIS-20261001110542-EE237A</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Obaid Ahmed Siddiqui</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>117973</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>PSO S/S 76 (SHEERIN)</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:05:42</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>24.81924091985388</v>
+      </c>
+      <c r="I203" t="n">
+        <v>66.99427701776526</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3.529129908927168</v>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T203" t="n">
+        <v>17</v>
+      </c>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V202"/>
+  <autoFilter ref="A1:V203"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$203</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$202</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V203"/>
+  <dimension ref="A1:V202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -14666,76 +14666,8 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>VIS-20261001110542-EE237A</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>4503</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>Obaid Ahmed Siddiqui</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>117973</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>PSO S/S 76 (SHEERIN)</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>2026-10-01 11:05:42</t>
-        </is>
-      </c>
-      <c r="H203" t="n">
-        <v>24.81924091985388</v>
-      </c>
-      <c r="I203" t="n">
-        <v>66.99427701776526</v>
-      </c>
-      <c r="J203" t="n">
-        <v>3.529129908927168</v>
-      </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="inlineStr"/>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="T203" t="n">
-        <v>17</v>
-      </c>
-      <c r="U203" t="inlineStr"/>
-      <c r="V203" t="inlineStr">
-        <is>
-          <t>Within 1.5 km</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V203"/>
+  <autoFilter ref="A1:V202"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$226</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V202"/>
+  <dimension ref="A1:V226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -438,12 +438,12 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -2451,7 +2451,7 @@
         <v>73.06313830000001</v>
       </c>
       <c r="N28" t="n">
-        <v>39.95800018310547</v>
+        <v>39.95800018</v>
       </c>
       <c r="O28" t="n">
         <v>15.7</v>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>00:09:37</t>
+          <t>0:09:37</t>
         </is>
       </c>
       <c r="R28" t="n">
@@ -3913,20 +3913,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>4533</t>
-        </is>
+      <c r="C50" t="n">
+        <v>4533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>Abdul Majid Shaikh</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>120248</t>
-        </is>
+      <c r="E50" t="n">
+        <v>120248</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3945,7 +3941,7 @@
         <v>68.84141459999999</v>
       </c>
       <c r="J50" t="n">
-        <v>10.48999977111816</v>
+        <v>10.48999977</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3959,7 +3955,7 @@
         <v>68.8413657</v>
       </c>
       <c r="N50" t="n">
-        <v>10.37100028991699</v>
+        <v>10.37100029</v>
       </c>
       <c r="O50" t="n">
         <v>5.9</v>
@@ -3971,7 +3967,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>00:00:39</t>
+          <t>0:00:39</t>
         </is>
       </c>
       <c r="R50" t="n">
@@ -4005,20 +4001,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1647</t>
-        </is>
+      <c r="C51" t="n">
+        <v>1647</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>Habib Rehman</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>101719</t>
-        </is>
+      <c r="E51" t="n">
+        <v>101719</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4073,20 +4065,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2348</t>
-        </is>
+      <c r="C52" t="n">
+        <v>2348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>Shahjahan</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>120248</t>
-        </is>
+      <c r="E52" t="n">
+        <v>120248</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4105,7 +4093,7 @@
         <v>68.8413881</v>
       </c>
       <c r="J52" t="n">
-        <v>28.10000038146973</v>
+        <v>28.10000038</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4119,7 +4107,7 @@
         <v>68.8413869</v>
       </c>
       <c r="N52" t="n">
-        <v>45.6879997253418</v>
+        <v>45.68799973</v>
       </c>
       <c r="O52" t="n">
         <v>0.9</v>
@@ -4131,7 +4119,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>00:00:10</t>
+          <t>0:00:10</t>
         </is>
       </c>
       <c r="R52" t="n">
@@ -4165,20 +4153,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2703</t>
-        </is>
+      <c r="C53" t="n">
+        <v>2703</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>Abdul Khalique Khan</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>101864</t>
-        </is>
+      <c r="E53" t="n">
+        <v>101864</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4197,7 +4181,7 @@
         <v>68.3629579</v>
       </c>
       <c r="J53" t="n">
-        <v>21.85300064086914</v>
+        <v>21.85300064</v>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
@@ -4233,20 +4217,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>3269</t>
-        </is>
+      <c r="C54" t="n">
+        <v>3269</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
           <t>Raham Ali</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>115853</t>
-        </is>
+      <c r="E54" t="n">
+        <v>115853</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4265,7 +4245,7 @@
         <v>73.07825149999999</v>
       </c>
       <c r="J54" t="n">
-        <v>7.206999778747559</v>
+        <v>7.206999779</v>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
@@ -4301,20 +4281,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>4594</t>
-        </is>
+      <c r="C55" t="n">
+        <v>4594</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
           <t>Waqas Mustafa Ghouri</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>102505</t>
-        </is>
+      <c r="E55" t="n">
+        <v>102505</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4333,7 +4309,7 @@
         <v>68.8466837</v>
       </c>
       <c r="J55" t="n">
-        <v>24.63699913024902</v>
+        <v>24.63699913</v>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
@@ -4369,20 +4345,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>3628</t>
-        </is>
+      <c r="C56" t="n">
+        <v>3628</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>Zain Ahmad</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>120054</t>
-        </is>
+      <c r="E56" t="n">
+        <v>120054</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4401,7 +4373,7 @@
         <v>68.8558573</v>
       </c>
       <c r="J56" t="n">
-        <v>22.51000022888184</v>
+        <v>22.51000023</v>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
@@ -4437,20 +4409,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
+      <c r="C57" t="n">
+        <v>3183</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>Muhammad Afzal Arain</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>101611</t>
-        </is>
+      <c r="E57" t="n">
+        <v>101611</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4495,7 +4463,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>00:00:16</t>
+          <t>0:00:16</t>
         </is>
       </c>
       <c r="R57" t="n">
@@ -4529,20 +4497,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>4909</t>
-        </is>
+      <c r="C58" t="n">
+        <v>4909</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>Victor Bashir</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>110951</t>
-        </is>
+      <c r="E58" t="n">
+        <v>110951</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4561,7 +4525,7 @@
         <v>68.3539834</v>
       </c>
       <c r="J58" t="n">
-        <v>38.22499847412109</v>
+        <v>38.22499847</v>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
@@ -4597,20 +4561,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>4925</t>
-        </is>
+      <c r="C59" t="n">
+        <v>4925</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>Usama Tasif</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>119468</t>
-        </is>
+      <c r="E59" t="n">
+        <v>119468</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -4629,7 +4589,7 @@
         <v>73.0772047</v>
       </c>
       <c r="J59" t="n">
-        <v>28.26199913024902</v>
+        <v>28.26199913</v>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
@@ -4665,20 +4625,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>4988</t>
-        </is>
+      <c r="C60" t="n">
+        <v>4988</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>SYEDA KHADIJA FATIMA</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>101664</t>
-        </is>
+      <c r="E60" t="n">
+        <v>101664</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -4691,13 +4647,13 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>24.8786544426191</v>
+        <v>24.87865444</v>
       </c>
       <c r="I60" t="n">
-        <v>67.0459278413461</v>
+        <v>67.04592784</v>
       </c>
       <c r="J60" t="n">
-        <v>30.92412171635922</v>
+        <v>30.92412172</v>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -4733,20 +4689,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>3433</t>
-        </is>
+      <c r="C61" t="n">
+        <v>3433</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>Mansoor ur Rehman</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>118519</t>
-        </is>
+      <c r="E61" t="n">
+        <v>118519</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -4801,20 +4753,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>3183</t>
-        </is>
+      <c r="C62" t="n">
+        <v>3183</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>Muhammad Afzal Arain</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>101611</t>
-        </is>
+      <c r="E62" t="n">
+        <v>101611</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -4833,7 +4781,7 @@
         <v>67.02208539999999</v>
       </c>
       <c r="J62" t="n">
-        <v>20.66799926757812</v>
+        <v>20.66799927</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4847,7 +4795,7 @@
         <v>67.0220905</v>
       </c>
       <c r="N62" t="n">
-        <v>16.63100051879883</v>
+        <v>16.63100052</v>
       </c>
       <c r="O62" t="n">
         <v>0.5</v>
@@ -4859,7 +4807,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>00:00:35</t>
+          <t>0:00:35</t>
         </is>
       </c>
       <c r="R62" t="n">
@@ -4893,20 +4841,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>4424</t>
-        </is>
+      <c r="C63" t="n">
+        <v>4424</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
           <t>Dhaniyal Petroleum</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>115228</t>
-        </is>
+      <c r="E63" t="n">
+        <v>115228</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -4925,7 +4869,7 @@
         <v>73.2178428</v>
       </c>
       <c r="J63" t="n">
-        <v>12.99199962615967</v>
+        <v>12.99199963</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4939,7 +4883,7 @@
         <v>73.21805000000001</v>
       </c>
       <c r="N63" t="n">
-        <v>5.599999904632568</v>
+        <v>5.599999905</v>
       </c>
       <c r="O63" t="n">
         <v>25.2</v>
@@ -4951,7 +4895,7 @@
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>00:00:31</t>
+          <t>0:00:31</t>
         </is>
       </c>
       <c r="R63" t="n">
@@ -4985,20 +4929,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
+      <c r="C64" t="n">
+        <v>2379</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>Mashkoor A Shamim</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>115228</t>
-        </is>
+      <c r="E64" t="n">
+        <v>115228</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -5017,7 +4957,7 @@
         <v>73.2178771</v>
       </c>
       <c r="J64" t="n">
-        <v>16.52899932861328</v>
+        <v>16.52899933</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5043,7 +4983,7 @@
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>00:00:50</t>
+          <t>0:00:50</t>
         </is>
       </c>
       <c r="R64" t="n">
@@ -5077,20 +5017,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>3726</t>
-        </is>
+      <c r="C65" t="n">
+        <v>3726</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>Saba irfan</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>101664</t>
-        </is>
+      <c r="E65" t="n">
+        <v>101664</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -5109,7 +5045,7 @@
         <v>67.0456707</v>
       </c>
       <c r="J65" t="n">
-        <v>20.92399978637695</v>
+        <v>20.92399979</v>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
@@ -5145,20 +5081,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>5212</t>
-        </is>
+      <c r="C66" t="n">
+        <v>5212</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>Syed Muhammad Umair</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>101664</t>
-        </is>
+      <c r="E66" t="n">
+        <v>101664</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -5177,7 +5109,7 @@
         <v>67.0456286</v>
       </c>
       <c r="J66" t="n">
-        <v>23.92900085449219</v>
+        <v>23.92900085</v>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
@@ -5213,20 +5145,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
+      <c r="C67" t="n">
+        <v>4906</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>Hira Fatima</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>115764</t>
-        </is>
+      <c r="E67" t="n">
+        <v>115764</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -5281,20 +5209,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>3118</t>
-        </is>
+      <c r="C68" t="n">
+        <v>3118</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>Mehar afroze</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>117793</t>
-        </is>
+      <c r="E68" t="n">
+        <v>117793</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -5307,13 +5231,13 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>24.85308776499481</v>
+        <v>24.85308776</v>
       </c>
       <c r="I68" t="n">
-        <v>67.0525579841546</v>
+        <v>67.05255798</v>
       </c>
       <c r="J68" t="n">
-        <v>27.75169213503676</v>
+        <v>27.75169214</v>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
@@ -5349,20 +5273,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>4627</t>
-        </is>
+      <c r="C69" t="n">
+        <v>4627</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>Atif Waqar Toor</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>119649</t>
-        </is>
+      <c r="E69" t="n">
+        <v>119649</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5407,7 +5327,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>00:00:17</t>
+          <t>0:00:17</t>
         </is>
       </c>
       <c r="R69" t="n">
@@ -5441,20 +5361,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
+      <c r="C70" t="n">
+        <v>4563</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>Waqas Ahmad Shah</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>115610</t>
-        </is>
+      <c r="E70" t="n">
+        <v>115610</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -5473,7 +5389,7 @@
         <v>70.9110376</v>
       </c>
       <c r="J70" t="n">
-        <v>13.9980001449585</v>
+        <v>13.99800014</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5499,7 +5415,7 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>00:00:14</t>
+          <t>0:00:14</t>
         </is>
       </c>
       <c r="R70" t="n">
@@ -5533,20 +5449,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>5115</t>
-        </is>
+      <c r="C71" t="n">
+        <v>5115</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>Hammad Tariq Mirza</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>104263</t>
-        </is>
+      <c r="E71" t="n">
+        <v>104263</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -5565,7 +5477,7 @@
         <v>72.85060420000001</v>
       </c>
       <c r="J71" t="n">
-        <v>33.70399856567383</v>
+        <v>33.70399857</v>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
@@ -5601,20 +5513,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="C72" t="n">
+        <v>3443</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
           <t>Muhammad shariq khan</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>115282</t>
-        </is>
+      <c r="E72" t="n">
+        <v>115282</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -5633,7 +5541,7 @@
         <v>67.0113163</v>
       </c>
       <c r="J72" t="n">
-        <v>13.15299987792969</v>
+        <v>13.15299988</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5647,7 +5555,7 @@
         <v>67.01133299999999</v>
       </c>
       <c r="N72" t="n">
-        <v>12.42599964141846</v>
+        <v>12.42599964</v>
       </c>
       <c r="O72" t="n">
         <v>2.5</v>
@@ -5659,7 +5567,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>00:04:03</t>
+          <t>0:04:03</t>
         </is>
       </c>
       <c r="R72" t="n">
@@ -5693,20 +5601,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>5110</t>
-        </is>
+      <c r="C73" t="n">
+        <v>5110</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>Syed Kamran Haider</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>102987</t>
-        </is>
+      <c r="E73" t="n">
+        <v>102987</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -5725,7 +5629,7 @@
         <v>71.4592933</v>
       </c>
       <c r="J73" t="n">
-        <v>7.300000190734863</v>
+        <v>7.300000191</v>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
@@ -5761,20 +5665,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>4664</t>
-        </is>
+      <c r="C74" t="n">
+        <v>4664</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>Ayesha Khan</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>115569</t>
-        </is>
+      <c r="E74" t="n">
+        <v>115569</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -5793,7 +5693,7 @@
         <v>72.7251741</v>
       </c>
       <c r="J74" t="n">
-        <v>14.38599967956543</v>
+        <v>14.38599968</v>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
@@ -5829,20 +5729,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>4627</t>
-        </is>
+      <c r="C75" t="n">
+        <v>4627</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>Atif Waqar Toor</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>119649</t>
-        </is>
+      <c r="E75" t="n">
+        <v>119649</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -5897,20 +5793,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2877</t>
-        </is>
+      <c r="C76" t="n">
+        <v>2877</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Aftab ur rehman</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>115569</t>
-        </is>
+      <c r="E76" t="n">
+        <v>115569</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -5929,7 +5821,7 @@
         <v>72.725165</v>
       </c>
       <c r="J76" t="n">
-        <v>14.03699970245361</v>
+        <v>14.0369997</v>
       </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
@@ -5965,20 +5857,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>3337</t>
-        </is>
+      <c r="C77" t="n">
+        <v>3337</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>Mudassir Altag</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>115764</t>
-        </is>
+      <c r="E77" t="n">
+        <v>115764</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -5997,7 +5885,7 @@
         <v>73.6908055</v>
       </c>
       <c r="J77" t="n">
-        <v>5.407000064849854</v>
+        <v>5.407000065</v>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
@@ -6033,20 +5921,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
+      <c r="C78" t="n">
+        <v>4563</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
           <t>Waqas Ahmad Shah</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>115610</t>
-        </is>
+      <c r="E78" t="n">
+        <v>115610</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -6101,20 +5985,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2803</t>
-        </is>
+      <c r="C79" t="n">
+        <v>2803</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>Saima aftab</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>115582</t>
-        </is>
+      <c r="E79" t="n">
+        <v>115582</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6133,7 +6013,7 @@
         <v>73.0307949</v>
       </c>
       <c r="J79" t="n">
-        <v>15.92199993133545</v>
+        <v>15.92199993</v>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
@@ -6169,20 +6049,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
+      <c r="C80" t="n">
+        <v>2441</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>Muhammad Faisal Shahzad</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>119649</t>
-        </is>
+      <c r="E80" t="n">
+        <v>119649</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -6237,20 +6113,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>4726</t>
-        </is>
+      <c r="C81" t="n">
+        <v>4726</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>Rubbia Moten</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>115569</t>
-        </is>
+      <c r="E81" t="n">
+        <v>115569</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -6263,13 +6135,13 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>33.76396322193338</v>
+        <v>33.76396322</v>
       </c>
       <c r="I81" t="n">
-        <v>72.72512793827059</v>
+        <v>72.72512793999999</v>
       </c>
       <c r="J81" t="n">
-        <v>20.65444269134041</v>
+        <v>20.65444269</v>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
@@ -6305,20 +6177,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>4023</t>
-        </is>
+      <c r="C82" t="n">
+        <v>4023</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>Waqas</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>101781</t>
-        </is>
+      <c r="E82" t="n">
+        <v>101781</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -6337,7 +6205,7 @@
         <v>68.35887150000001</v>
       </c>
       <c r="J82" t="n">
-        <v>43.55599975585938</v>
+        <v>43.55599976</v>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
@@ -6373,20 +6241,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>5236</t>
-        </is>
+      <c r="C83" t="n">
+        <v>5236</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>Ilsa Nidal</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>119440</t>
-        </is>
+      <c r="E83" t="n">
+        <v>119440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -6399,13 +6263,13 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>24.86738921146792</v>
+        <v>24.86738921</v>
       </c>
       <c r="I83" t="n">
-        <v>67.02498770978858</v>
+        <v>67.02498771</v>
       </c>
       <c r="J83" t="n">
-        <v>39.99802691234568</v>
+        <v>39.99802691</v>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
@@ -6441,20 +6305,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2840</t>
-        </is>
+      <c r="C84" t="n">
+        <v>2840</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
           <t>Saba Ahmed</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>120542</t>
-        </is>
+      <c r="E84" t="n">
+        <v>120542</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -6467,13 +6327,13 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>24.84804295872743</v>
+        <v>24.84804296</v>
       </c>
       <c r="I84" t="n">
-        <v>67.04645151997653</v>
+        <v>67.04645152000001</v>
       </c>
       <c r="J84" t="n">
-        <v>7.874778465949883</v>
+        <v>7.874778466</v>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr"/>
@@ -6509,20 +6369,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2602</t>
-        </is>
+      <c r="C85" t="n">
+        <v>2602</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
           <t>Fahad murtaza</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>117078</t>
-        </is>
+      <c r="E85" t="n">
+        <v>117078</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -6541,7 +6397,7 @@
         <v>67.0294251</v>
       </c>
       <c r="J85" t="n">
-        <v>23.11199951171875</v>
+        <v>23.11199951</v>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
@@ -6577,20 +6433,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2590</t>
-        </is>
+      <c r="C86" t="n">
+        <v>2590</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>Altaf Khattak</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>119649</t>
-        </is>
+      <c r="E86" t="n">
+        <v>119649</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -6645,20 +6497,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
+      <c r="C87" t="n">
+        <v>326</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
           <t>Shamim Abbas Tarar</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>119062</t>
-        </is>
+      <c r="E87" t="n">
+        <v>119062</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -6677,7 +6525,7 @@
         <v>73.72893209999999</v>
       </c>
       <c r="J87" t="n">
-        <v>27.61899948120117</v>
+        <v>27.61899948</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6703,7 +6551,7 @@
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>00:00:19</t>
+          <t>0:00:19</t>
         </is>
       </c>
       <c r="R87" t="n">
@@ -6737,20 +6585,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>1670</t>
-        </is>
+      <c r="C88" t="n">
+        <v>1670</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>Muhammad Shoaib</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>117078</t>
-        </is>
+      <c r="E88" t="n">
+        <v>117078</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -6769,7 +6613,7 @@
         <v>67.0294418</v>
       </c>
       <c r="J88" t="n">
-        <v>20.95000076293945</v>
+        <v>20.95000076</v>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
@@ -6805,20 +6649,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2179</t>
-        </is>
+      <c r="C89" t="n">
+        <v>2179</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>Saira shoaib</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>117793</t>
-        </is>
+      <c r="E89" t="n">
+        <v>117793</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -6831,13 +6671,13 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>24.85292598809838</v>
+        <v>24.85292599</v>
       </c>
       <c r="I89" t="n">
-        <v>67.05300793917331</v>
+        <v>67.05300794</v>
       </c>
       <c r="J89" t="n">
-        <v>39.5574247269759</v>
+        <v>39.55742473</v>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
@@ -6873,20 +6713,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>4031</t>
-        </is>
+      <c r="C90" t="n">
+        <v>4031</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>Muhammad Zulfiqar Ali</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>102987</t>
-        </is>
+      <c r="E90" t="n">
+        <v>102987</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -6905,7 +6741,7 @@
         <v>71.45936020000001</v>
       </c>
       <c r="J90" t="n">
-        <v>17.0939998626709</v>
+        <v>17.09399986</v>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
@@ -6941,20 +6777,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>720010</t>
-        </is>
+      <c r="C91" t="n">
+        <v>720010</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>Adeena Yawer</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>116674</t>
-        </is>
+      <c r="E91" t="n">
+        <v>116674</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -6973,7 +6805,7 @@
         <v>67.0339041</v>
       </c>
       <c r="J91" t="n">
-        <v>33.13600158691406</v>
+        <v>33.13600159</v>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
@@ -7009,20 +6841,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2185</t>
-        </is>
+      <c r="C92" t="n">
+        <v>2185</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
           <t>Allah Dino Mirani</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>101781</t>
-        </is>
+      <c r="E92" t="n">
+        <v>101781</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -7077,20 +6905,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2513</t>
-        </is>
+      <c r="C93" t="n">
+        <v>2513</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>Farooq Asghar</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>119290</t>
-        </is>
+      <c r="E93" t="n">
+        <v>119290</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -7145,20 +6969,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>3597</t>
-        </is>
+      <c r="C94" t="n">
+        <v>3597</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
           <t>Rimsha Iqbal</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>104279</t>
-        </is>
+      <c r="E94" t="n">
+        <v>104279</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -7171,13 +6991,13 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>33.64683497431298</v>
+        <v>33.64683497</v>
       </c>
       <c r="I94" t="n">
-        <v>72.91575492656544</v>
+        <v>72.91575493000001</v>
       </c>
       <c r="J94" t="n">
-        <v>39.97399397343361</v>
+        <v>39.97399397</v>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
@@ -7213,20 +7033,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2769</t>
-        </is>
+      <c r="C95" t="n">
+        <v>2769</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
           <t>Rabia yasir Afridi</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>104279</t>
-        </is>
+      <c r="E95" t="n">
+        <v>104279</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -7245,7 +7061,7 @@
         <v>72.915862</v>
       </c>
       <c r="J95" t="n">
-        <v>14.9689998626709</v>
+        <v>14.96899986</v>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
@@ -7281,20 +7097,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>4288</t>
-        </is>
+      <c r="C96" t="n">
+        <v>4288</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
           <t>Sana Durrani</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>120542</t>
-        </is>
+      <c r="E96" t="n">
+        <v>120542</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -7313,7 +7125,7 @@
         <v>67.0460279</v>
       </c>
       <c r="J96" t="n">
-        <v>5.10200023651123</v>
+        <v>5.102000237</v>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
@@ -7349,20 +7161,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>4640</t>
-        </is>
+      <c r="C97" t="n">
+        <v>4640</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>Waqar Haider</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>120542</t>
-        </is>
+      <c r="E97" t="n">
+        <v>120542</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -7417,20 +7225,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>5078</t>
-        </is>
+      <c r="C98" t="n">
+        <v>5078</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
           <t>Aqsa Mumtaz</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>114529</t>
-        </is>
+      <c r="E98" t="n">
+        <v>114529</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -7443,13 +7247,13 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>24.84995280796351</v>
+        <v>24.84995281</v>
       </c>
       <c r="I98" t="n">
-        <v>67.020035421549</v>
+        <v>67.02003542</v>
       </c>
       <c r="J98" t="n">
-        <v>16.50806252351778</v>
+        <v>16.50806252</v>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
@@ -7485,20 +7289,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
+      <c r="C99" t="n">
+        <v>3443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>Muhammad shariq khan</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>115282</t>
-        </is>
+      <c r="E99" t="n">
+        <v>115282</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -7517,7 +7317,7 @@
         <v>67.0113329</v>
       </c>
       <c r="J99" t="n">
-        <v>13.37600040435791</v>
+        <v>13.3760004</v>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
@@ -7553,20 +7353,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>4598</t>
-        </is>
+      <c r="C100" t="n">
+        <v>4598</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
           <t>Zainab amir</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>104279</t>
-        </is>
+      <c r="E100" t="n">
+        <v>104279</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -7585,7 +7381,7 @@
         <v>72.9158621</v>
       </c>
       <c r="J100" t="n">
-        <v>15.24400043487549</v>
+        <v>15.24400043</v>
       </c>
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
@@ -7621,20 +7417,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
+      <c r="C101" t="n">
+        <v>4590</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
           <t>Muhammad Shahzad Ahmed</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>114529</t>
-        </is>
+      <c r="E101" t="n">
+        <v>114529</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -7653,7 +7445,7 @@
         <v>67.0200624</v>
       </c>
       <c r="J101" t="n">
-        <v>46.70800018310547</v>
+        <v>46.70800018</v>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
@@ -7689,20 +7481,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2979</t>
-        </is>
+      <c r="C102" t="n">
+        <v>2979</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
           <t>FAISAL MEHMOOD</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>114662</t>
-        </is>
+      <c r="E102" t="n">
+        <v>114662</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -7721,7 +7509,7 @@
         <v>67.03870499999999</v>
       </c>
       <c r="J102" t="n">
-        <v>12.83600044250488</v>
+        <v>12.83600044</v>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
@@ -7757,20 +7545,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>4969</t>
-        </is>
+      <c r="C103" t="n">
+        <v>4969</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
           <t>Waqar Ahmed</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>101760</t>
-        </is>
+      <c r="E103" t="n">
+        <v>101760</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -7825,20 +7609,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>4779</t>
-        </is>
+      <c r="C104" t="n">
+        <v>4779</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>Shaista Faisal</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>114529</t>
-        </is>
+      <c r="E104" t="n">
+        <v>114529</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -7857,7 +7637,7 @@
         <v>67.0200816</v>
       </c>
       <c r="J104" t="n">
-        <v>4.099999904632568</v>
+        <v>4.099999905</v>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
@@ -7893,20 +7673,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>5022</t>
-        </is>
+      <c r="C105" t="n">
+        <v>5022</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>Ahsan Anwar</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>119440</t>
-        </is>
+      <c r="E105" t="n">
+        <v>119440</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -7925,7 +7701,7 @@
         <v>67.02487530000001</v>
       </c>
       <c r="J105" t="n">
-        <v>11.61800003051758</v>
+        <v>11.61800003</v>
       </c>
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
@@ -7961,20 +7737,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>3290</t>
-        </is>
+      <c r="C106" t="n">
+        <v>3290</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
           <t>Nissa Yasir</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>114662</t>
-        </is>
+      <c r="E106" t="n">
+        <v>114662</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -7987,13 +7759,13 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>24.87753756126155</v>
+        <v>24.87753756</v>
       </c>
       <c r="I106" t="n">
-        <v>67.03874965404376</v>
+        <v>67.03874965</v>
       </c>
       <c r="J106" t="n">
-        <v>14.16613577768025</v>
+        <v>14.16613578</v>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
@@ -8029,20 +7801,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>5075</t>
-        </is>
+      <c r="C107" t="n">
+        <v>5075</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
           <t>Raj Kumar</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>101781</t>
-        </is>
+      <c r="E107" t="n">
+        <v>101781</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -8061,7 +7829,7 @@
         <v>68.35921380000001</v>
       </c>
       <c r="J107" t="n">
-        <v>4.598999977111816</v>
+        <v>4.598999977</v>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
@@ -8097,20 +7865,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>4930</t>
-        </is>
+      <c r="C108" t="n">
+        <v>4930</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
           <t>WALEED AHMED</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>116118</t>
-        </is>
+      <c r="E108" t="n">
+        <v>116118</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -8129,7 +7893,7 @@
         <v>72.9958242</v>
       </c>
       <c r="J108" t="n">
-        <v>12.02400016784668</v>
+        <v>12.02400017</v>
       </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
@@ -8165,20 +7929,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>5229</t>
-        </is>
+      <c r="C109" t="n">
+        <v>5229</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>Muhammad Zain</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>117078</t>
-        </is>
+      <c r="E109" t="n">
+        <v>117078</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -8197,7 +7957,7 @@
         <v>67.029387</v>
       </c>
       <c r="J109" t="n">
-        <v>24.38199996948242</v>
+        <v>24.38199997</v>
       </c>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
@@ -8233,20 +7993,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>5015</t>
-        </is>
+      <c r="C110" t="n">
+        <v>5015</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
           <t>Hassan Shahid</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>115029</t>
-        </is>
+      <c r="E110" t="n">
+        <v>115029</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -8259,13 +8015,13 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>30.24163731911212</v>
+        <v>30.24163732</v>
       </c>
       <c r="I110" t="n">
-        <v>71.5022891512978</v>
+        <v>71.50228915</v>
       </c>
       <c r="J110" t="n">
-        <v>39.99172002685452</v>
+        <v>39.99172003</v>
       </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
@@ -8301,20 +8057,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>4831</t>
-        </is>
+      <c r="C111" t="n">
+        <v>4831</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
           <t>Saad Aamer</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
+      <c r="E111" t="n">
+        <v>103261</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -8333,7 +8085,7 @@
         <v>74.230581</v>
       </c>
       <c r="J111" t="n">
-        <v>22.18099975585938</v>
+        <v>22.18099976</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8347,7 +8099,7 @@
         <v>74.2302263</v>
       </c>
       <c r="N111" t="n">
-        <v>22.9109992980957</v>
+        <v>22.9109993</v>
       </c>
       <c r="O111" t="n">
         <v>33.7</v>
@@ -8359,7 +8111,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>00:00:15</t>
+          <t>0:00:15</t>
         </is>
       </c>
       <c r="R111" t="n">
@@ -8393,20 +8145,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>3570</t>
-        </is>
+      <c r="C112" t="n">
+        <v>3570</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>Inam Ullah</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>117963</t>
-        </is>
+      <c r="E112" t="n">
+        <v>117963</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -8425,7 +8173,7 @@
         <v>73.0923124</v>
       </c>
       <c r="J112" t="n">
-        <v>9.975000381469727</v>
+        <v>9.975000380999999</v>
       </c>
       <c r="K112" t="inlineStr"/>
       <c r="L112" t="inlineStr"/>
@@ -8461,20 +8209,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>5173</t>
-        </is>
+      <c r="C113" t="n">
+        <v>5173</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>kazim jamil</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>116118</t>
-        </is>
+      <c r="E113" t="n">
+        <v>116118</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -8493,7 +8237,7 @@
         <v>72.9956275</v>
       </c>
       <c r="J113" t="n">
-        <v>15.58199977874756</v>
+        <v>15.58199978</v>
       </c>
       <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
@@ -8529,20 +8273,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>5123</t>
-        </is>
+      <c r="C114" t="n">
+        <v>5123</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
           <t>Affan Saleem</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>119547</t>
-        </is>
+      <c r="E114" t="n">
+        <v>119547</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -8561,7 +8301,7 @@
         <v>72.94676010000001</v>
       </c>
       <c r="J114" t="n">
-        <v>20.44300079345703</v>
+        <v>20.44300079</v>
       </c>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
@@ -8597,20 +8337,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>3410</t>
-        </is>
+      <c r="C115" t="n">
+        <v>3410</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
           <t>Kashif Alu</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>102604</t>
-        </is>
+      <c r="E115" t="n">
+        <v>102604</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -8629,7 +8365,7 @@
         <v>71.4450255</v>
       </c>
       <c r="J115" t="n">
-        <v>16.32699966430664</v>
+        <v>16.32699966</v>
       </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
@@ -8665,20 +8401,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
+      <c r="C116" t="n">
+        <v>2892</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>Muhammad Ilyas Soomro</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>102014</t>
-        </is>
+      <c r="E116" t="n">
+        <v>102014</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -8697,7 +8429,7 @@
         <v>68.3396561</v>
       </c>
       <c r="J116" t="n">
-        <v>14.64599990844727</v>
+        <v>14.64599991</v>
       </c>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
@@ -8733,20 +8465,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>3165</t>
-        </is>
+      <c r="C117" t="n">
+        <v>3165</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>Imran Siddique Minhas</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>104263</t>
-        </is>
+      <c r="E117" t="n">
+        <v>104263</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -8765,7 +8493,7 @@
         <v>72.8505183</v>
       </c>
       <c r="J117" t="n">
-        <v>5.199999809265137</v>
+        <v>5.199999809</v>
       </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
@@ -8801,20 +8529,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>4547</t>
-        </is>
+      <c r="C118" t="n">
+        <v>4547</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>Kamil Iqbal</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>118293</t>
-        </is>
+      <c r="E118" t="n">
+        <v>118293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -8833,7 +8557,7 @@
         <v>71.4306241</v>
       </c>
       <c r="J118" t="n">
-        <v>13.51099967956543</v>
+        <v>13.51099968</v>
       </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
@@ -8869,20 +8593,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>5004</t>
-        </is>
+      <c r="C119" t="n">
+        <v>5004</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>Mahesh kumar</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>115998</t>
-        </is>
+      <c r="E119" t="n">
+        <v>115998</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -8937,20 +8657,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>4922</t>
-        </is>
+      <c r="C120" t="n">
+        <v>4922</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>Kanwar Yousuf Ali Khan</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>114662</t>
-        </is>
+      <c r="E120" t="n">
+        <v>114662</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -8969,7 +8685,7 @@
         <v>67.0387083</v>
       </c>
       <c r="J120" t="n">
-        <v>11.61800003051758</v>
+        <v>11.61800003</v>
       </c>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
@@ -9005,20 +8721,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>4976</t>
-        </is>
+      <c r="C121" t="n">
+        <v>4976</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
           <t>Malik Zeshan Khalid</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>120209</t>
-        </is>
+      <c r="E121" t="n">
+        <v>120209</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -9073,20 +8785,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>4681</t>
-        </is>
+      <c r="C122" t="n">
+        <v>4681</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
           <t>Zainab Nawaz</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>120650</t>
-        </is>
+      <c r="E122" t="n">
+        <v>120650</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -9099,13 +8807,13 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>33.57376939470232</v>
+        <v>33.57376939</v>
       </c>
       <c r="I122" t="n">
-        <v>73.03956177176075</v>
+        <v>73.03956177000001</v>
       </c>
       <c r="J122" t="n">
-        <v>40.31179310774912</v>
+        <v>40.31179311</v>
       </c>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
@@ -9141,20 +8849,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>5019</t>
-        </is>
+      <c r="C123" t="n">
+        <v>5019</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
           <t>Ghazi Sanaullah</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>112305</t>
-        </is>
+      <c r="E123" t="n">
+        <v>112305</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -9209,20 +8913,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>4511</t>
-        </is>
+      <c r="C124" t="n">
+        <v>4511</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>Sania tabbasum</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>120650</t>
-        </is>
+      <c r="E124" t="n">
+        <v>120650</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -9241,7 +8941,7 @@
         <v>73.0394088</v>
       </c>
       <c r="J124" t="n">
-        <v>22.07500076293945</v>
+        <v>22.07500076</v>
       </c>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
@@ -9277,20 +8977,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>4793</t>
-        </is>
+      <c r="C125" t="n">
+        <v>4793</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>Abdul Bari</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>117753</t>
-        </is>
+      <c r="E125" t="n">
+        <v>117753</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -9309,7 +9005,7 @@
         <v>68.37423149999999</v>
       </c>
       <c r="J125" t="n">
-        <v>15.66800022125244</v>
+        <v>15.66800022</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9323,7 +9019,7 @@
         <v>68.3742182</v>
       </c>
       <c r="N125" t="n">
-        <v>4.25600004196167</v>
+        <v>4.256000042</v>
       </c>
       <c r="O125" t="n">
         <v>8</v>
@@ -9335,7 +9031,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>00:00:17</t>
+          <t>0:00:17</t>
         </is>
       </c>
       <c r="R125" t="n">
@@ -9369,20 +9065,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>2792</t>
-        </is>
+      <c r="C126" t="n">
+        <v>2792</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>Abdur Rehman</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>115029</t>
-        </is>
+      <c r="E126" t="n">
+        <v>115029</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -9401,7 +9093,7 @@
         <v>71.5023087</v>
       </c>
       <c r="J126" t="n">
-        <v>23.20599937438965</v>
+        <v>23.20599937</v>
       </c>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
@@ -9437,20 +9129,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>2853</t>
-        </is>
+      <c r="C127" t="n">
+        <v>2853</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>Hina Shakil</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>101703</t>
-        </is>
+      <c r="E127" t="n">
+        <v>101703</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -9505,20 +9193,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>5148</t>
-        </is>
+      <c r="C128" t="n">
+        <v>5148</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
           <t>Jamal Elahi</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>119290</t>
-        </is>
+      <c r="E128" t="n">
+        <v>119290</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -9537,7 +9221,7 @@
         <v>73.0629636</v>
       </c>
       <c r="J128" t="n">
-        <v>18.38699913024902</v>
+        <v>18.38699913</v>
       </c>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
@@ -9573,20 +9257,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>4793</t>
-        </is>
+      <c r="C129" t="n">
+        <v>4793</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
           <t>Abdul Bari</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>117753</t>
-        </is>
+      <c r="E129" t="n">
+        <v>117753</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -9605,7 +9285,7 @@
         <v>68.3742211</v>
       </c>
       <c r="J129" t="n">
-        <v>7.848999977111816</v>
+        <v>7.848999977</v>
       </c>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
@@ -9641,20 +9321,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>1708</t>
-        </is>
+      <c r="C130" t="n">
+        <v>1708</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>Zulfiqar Ali</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>114529</t>
-        </is>
+      <c r="E130" t="n">
+        <v>114529</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -9709,20 +9385,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>5041</t>
-        </is>
+      <c r="C131" t="n">
+        <v>5041</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>Bushra Taufique</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>101703</t>
-        </is>
+      <c r="E131" t="n">
+        <v>101703</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -9741,7 +9413,7 @@
         <v>67.0079286</v>
       </c>
       <c r="J131" t="n">
-        <v>13207.75677138323</v>
+        <v>13207.75677</v>
       </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
@@ -9777,20 +9449,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>4588</t>
-        </is>
+      <c r="C132" t="n">
+        <v>4588</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
           <t>Raheel Syed</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>117753</t>
-        </is>
+      <c r="E132" t="n">
+        <v>117753</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -9809,7 +9477,7 @@
         <v>68.3741114</v>
       </c>
       <c r="J132" t="n">
-        <v>9.133999824523926</v>
+        <v>9.133999825</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -9823,7 +9491,7 @@
         <v>68.3742604</v>
       </c>
       <c r="N132" t="n">
-        <v>17.09600067138672</v>
+        <v>17.09600067</v>
       </c>
       <c r="O132" t="n">
         <v>33.6</v>
@@ -9835,7 +9503,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>00:00:27</t>
+          <t>0:00:27</t>
         </is>
       </c>
       <c r="R132" t="n">
@@ -9869,20 +9537,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>2736</t>
-        </is>
+      <c r="C133" t="n">
+        <v>2736</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
           <t>Izhar Ahmed</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>101703</t>
-        </is>
+      <c r="E133" t="n">
+        <v>101703</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -9895,13 +9559,13 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>24.87503691539372</v>
+        <v>24.87503692</v>
       </c>
       <c r="I133" t="n">
-        <v>67.04590667242732</v>
+        <v>67.04590666999999</v>
       </c>
       <c r="J133" t="n">
-        <v>39.99946584676781</v>
+        <v>39.99946585</v>
       </c>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
@@ -9937,20 +9601,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>3968</t>
-        </is>
+      <c r="C134" t="n">
+        <v>3968</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>Wazir Muhammad</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>115610</t>
-        </is>
+      <c r="E134" t="n">
+        <v>115610</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -9969,7 +9629,7 @@
         <v>70.91088430000001</v>
       </c>
       <c r="J134" t="n">
-        <v>20.38599967956543</v>
+        <v>20.38599968</v>
       </c>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
@@ -10005,20 +9665,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>4955</t>
-        </is>
+      <c r="C135" t="n">
+        <v>4955</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>Muhammad Umair Shaikh</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>101734</t>
-        </is>
+      <c r="E135" t="n">
+        <v>101734</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -10073,20 +9729,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>3244</t>
-        </is>
+      <c r="C136" t="n">
+        <v>3244</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
           <t>Shahid Nawaz</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>102604</t>
-        </is>
+      <c r="E136" t="n">
+        <v>102604</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -10105,7 +9757,7 @@
         <v>71.44496839999999</v>
       </c>
       <c r="J136" t="n">
-        <v>29.12199974060059</v>
+        <v>29.12199974</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
@@ -10119,7 +9771,7 @@
         <v>71.4449122</v>
       </c>
       <c r="N136" t="n">
-        <v>19.2189998626709</v>
+        <v>19.21899986</v>
       </c>
       <c r="O136" t="n">
         <v>37.7</v>
@@ -10131,7 +9783,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>00:07:58</t>
+          <t>0:07:58</t>
         </is>
       </c>
       <c r="R136" t="n">
@@ -10165,20 +9817,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>4371</t>
-        </is>
+      <c r="C137" t="n">
+        <v>4371</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>Qaiser nawab</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>115998</t>
-        </is>
+      <c r="E137" t="n">
+        <v>115998</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -10233,20 +9881,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>5211</t>
-        </is>
+      <c r="C138" t="n">
+        <v>5211</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
           <t>Muhammad Ahmed</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>119124</t>
-        </is>
+      <c r="E138" t="n">
+        <v>119124</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -10301,20 +9945,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
+      <c r="C139" t="n">
+        <v>3400</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>Waqar Ali</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>112305</t>
-        </is>
+      <c r="E139" t="n">
+        <v>112305</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -10333,7 +9973,7 @@
         <v>73.0719127</v>
       </c>
       <c r="J139" t="n">
-        <v>13.73299980163574</v>
+        <v>13.7329998</v>
       </c>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
@@ -10369,20 +10009,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>4858</t>
-        </is>
+      <c r="C140" t="n">
+        <v>4858</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
           <t>Sania javed</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>119124</t>
-        </is>
+      <c r="E140" t="n">
+        <v>119124</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -10401,7 +10037,7 @@
         <v>67.0426619</v>
       </c>
       <c r="J140" t="n">
-        <v>64.61799621582031</v>
+        <v>64.61799621999999</v>
       </c>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
@@ -10437,20 +10073,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
+      <c r="C141" t="n">
+        <v>2133</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
           <t>ADNAN AZMATULLAH KHAN</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>115998</t>
-        </is>
+      <c r="E141" t="n">
+        <v>115998</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -10469,7 +10101,7 @@
         <v>67.1335413</v>
       </c>
       <c r="J141" t="n">
-        <v>13.24300003051758</v>
+        <v>13.24300003</v>
       </c>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
@@ -10505,20 +10137,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>3489</t>
-        </is>
+      <c r="C142" t="n">
+        <v>3489</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>Zaheer Ahmed</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>119394</t>
-        </is>
+      <c r="E142" t="n">
+        <v>119394</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -10537,7 +10165,7 @@
         <v>71.50274330000001</v>
       </c>
       <c r="J142" t="n">
-        <v>6.749000072479248</v>
+        <v>6.749000072</v>
       </c>
       <c r="K142" t="inlineStr"/>
       <c r="L142" t="inlineStr"/>
@@ -10573,20 +10201,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2768</t>
-        </is>
+      <c r="C143" t="n">
+        <v>2768</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
           <t>M FAISAL CHISHTI</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>119124</t>
-        </is>
+      <c r="E143" t="n">
+        <v>119124</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -10605,7 +10229,7 @@
         <v>67.0424833</v>
       </c>
       <c r="J143" t="n">
-        <v>3.789999961853027</v>
+        <v>3.789999962</v>
       </c>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
@@ -10641,20 +10265,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>3032</t>
-        </is>
+      <c r="C144" t="n">
+        <v>3032</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>Nazia Qadeem</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>113349</t>
-        </is>
+      <c r="E144" t="n">
+        <v>113349</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -10673,7 +10293,7 @@
         <v>67.0699853</v>
       </c>
       <c r="J144" t="n">
-        <v>34.57199859619141</v>
+        <v>34.5719986</v>
       </c>
       <c r="K144" t="inlineStr"/>
       <c r="L144" t="inlineStr"/>
@@ -10709,20 +10329,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="C145" t="n">
+        <v>2834</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
           <t>Mohammad Lal Khan</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>116118</t>
-        </is>
+      <c r="E145" t="n">
+        <v>116118</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -10735,13 +10351,13 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>33.66724533507718</v>
+        <v>33.66724534</v>
       </c>
       <c r="I145" t="n">
-        <v>72.9954476124025</v>
+        <v>72.99544761</v>
       </c>
       <c r="J145" t="n">
-        <v>32.64382039651886</v>
+        <v>32.6438204</v>
       </c>
       <c r="K145" t="inlineStr"/>
       <c r="L145" t="inlineStr"/>
@@ -10777,20 +10393,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>720015</t>
-        </is>
+      <c r="C146" t="n">
+        <v>720015</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>Fatima Bibi</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>102404</t>
-        </is>
+      <c r="E146" t="n">
+        <v>102404</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -10809,7 +10421,7 @@
         <v>67.0432599</v>
       </c>
       <c r="J146" t="n">
-        <v>14.33600044250488</v>
+        <v>14.33600044</v>
       </c>
       <c r="K146" t="inlineStr"/>
       <c r="L146" t="inlineStr"/>
@@ -10845,20 +10457,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>3565</t>
-        </is>
+      <c r="C147" t="n">
+        <v>3565</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
           <t>Muhammad Jawad</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>120542</t>
-        </is>
+      <c r="E147" t="n">
+        <v>120542</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -10877,7 +10485,7 @@
         <v>67.0466342</v>
       </c>
       <c r="J147" t="n">
-        <v>21.39999961853027</v>
+        <v>21.39999962</v>
       </c>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
@@ -10913,20 +10521,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>720018</t>
-        </is>
+      <c r="C148" t="n">
+        <v>720018</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
           <t>Haleema jamal</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>102404</t>
-        </is>
+      <c r="E148" t="n">
+        <v>102404</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -10939,13 +10543,13 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>24.86114197149691</v>
+        <v>24.86114197</v>
       </c>
       <c r="I148" t="n">
-        <v>67.04317511137465</v>
+        <v>67.04317511000001</v>
       </c>
       <c r="J148" t="n">
-        <v>27.98754535605991</v>
+        <v>27.98754536</v>
       </c>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
@@ -10981,20 +10585,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>5008</t>
-        </is>
+      <c r="C149" t="n">
+        <v>5008</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
           <t>Faiqa Khawar</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>117116</t>
-        </is>
+      <c r="E149" t="n">
+        <v>117116</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -11013,7 +10613,7 @@
         <v>67.02300049999999</v>
       </c>
       <c r="J149" t="n">
-        <v>12.67300033569336</v>
+        <v>12.67300034</v>
       </c>
       <c r="K149" t="inlineStr"/>
       <c r="L149" t="inlineStr"/>
@@ -11049,20 +10649,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>4465</t>
-        </is>
+      <c r="C150" t="n">
+        <v>4465</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
           <t>Noshaba sheikh</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>120542</t>
-        </is>
+      <c r="E150" t="n">
+        <v>120542</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -11117,20 +10713,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>5252</t>
-        </is>
+      <c r="C151" t="n">
+        <v>5252</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
           <t>col Junaid Salahuddin Swati</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>102404</t>
-        </is>
+      <c r="E151" t="n">
+        <v>102404</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -11149,7 +10741,7 @@
         <v>67.0079286</v>
       </c>
       <c r="J151" t="n">
-        <v>13207.75677138323</v>
+        <v>13207.75677</v>
       </c>
       <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
@@ -11185,20 +10777,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2559</t>
-        </is>
+      <c r="C152" t="n">
+        <v>2559</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
           <t>REHAN SAJID</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>118519</t>
-        </is>
+      <c r="E152" t="n">
+        <v>118519</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -11253,20 +10841,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>3368</t>
-        </is>
+      <c r="C153" t="n">
+        <v>3368</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>Sarah Akber</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>117116</t>
-        </is>
+      <c r="E153" t="n">
+        <v>117116</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -11321,20 +10905,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>4246</t>
-        </is>
+      <c r="C154" t="n">
+        <v>4246</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>Yasir Mehmood</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>118042</t>
-        </is>
+      <c r="E154" t="n">
+        <v>118042</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -11353,7 +10933,7 @@
         <v>67.04038079999999</v>
       </c>
       <c r="J154" t="n">
-        <v>13.22700023651123</v>
+        <v>13.22700024</v>
       </c>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
@@ -11389,20 +10969,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>5201</t>
-        </is>
+      <c r="C155" t="n">
+        <v>5201</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
           <t>Waqas Siddiqui</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>120239</t>
-        </is>
+      <c r="E155" t="n">
+        <v>120239</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -11421,7 +10997,7 @@
         <v>67.0070458</v>
       </c>
       <c r="J155" t="n">
-        <v>19.72599983215332</v>
+        <v>19.72599983</v>
       </c>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
@@ -11457,20 +11033,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>3603</t>
-        </is>
+      <c r="C156" t="n">
+        <v>3603</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
           <t>Ali Gohar</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>117713</t>
-        </is>
+      <c r="E156" t="n">
+        <v>117713</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -11489,7 +11061,7 @@
         <v>68.85894260000001</v>
       </c>
       <c r="J156" t="n">
-        <v>15.74600028991699</v>
+        <v>15.74600029</v>
       </c>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
@@ -11525,20 +11097,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
+      <c r="C157" t="n">
+        <v>4979</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
           <t>ABDUL REHMAN</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>119124</t>
-        </is>
+      <c r="E157" t="n">
+        <v>119124</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -11557,7 +11125,7 @@
         <v>67.0427454</v>
       </c>
       <c r="J157" t="n">
-        <v>23.55900001525879</v>
+        <v>23.55900002</v>
       </c>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
@@ -11593,20 +11161,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>3912</t>
-        </is>
+      <c r="C158" t="n">
+        <v>3912</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
           <t>Malik Mubin Ahmed</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>117439</t>
-        </is>
+      <c r="E158" t="n">
+        <v>117439</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -11625,7 +11189,7 @@
         <v>67.0195512</v>
       </c>
       <c r="J158" t="n">
-        <v>39.65399932861328</v>
+        <v>39.65399933</v>
       </c>
       <c r="K158" t="inlineStr"/>
       <c r="L158" t="inlineStr"/>
@@ -11661,20 +11225,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
+      <c r="C159" t="n">
+        <v>3399</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
           <t>Shakeel Ahmed</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>117342</t>
-        </is>
+      <c r="E159" t="n">
+        <v>117342</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -11693,7 +11253,7 @@
         <v>67.0843702</v>
       </c>
       <c r="J159" t="n">
-        <v>43.95299911499023</v>
+        <v>43.95299911</v>
       </c>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
@@ -11729,20 +11289,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>710003</t>
-        </is>
+      <c r="C160" t="n">
+        <v>710003</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>Hafiz Abdur Rafay Khan</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>120542</t>
-        </is>
+      <c r="E160" t="n">
+        <v>120542</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -11797,20 +11353,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>5109</t>
-        </is>
+      <c r="C161" t="n">
+        <v>5109</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>Muhammad Hamad Asghar</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>104286</t>
-        </is>
+      <c r="E161" t="n">
+        <v>104286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -11823,10 +11375,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>33.66048659606437</v>
+        <v>33.6604866</v>
       </c>
       <c r="I161" t="n">
-        <v>73.06319448450017</v>
+        <v>73.06319448000001</v>
       </c>
       <c r="J161" t="n">
         <v>27.095014</v>
@@ -11865,20 +11417,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
+      <c r="C162" t="n">
+        <v>2383</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
           <t>Muhammad Atif Latif</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>118042</t>
-        </is>
+      <c r="E162" t="n">
+        <v>118042</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -11891,10 +11439,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>24.8841007722626</v>
+        <v>24.88410077</v>
       </c>
       <c r="I162" t="n">
-        <v>67.04048875538794</v>
+        <v>67.04048876</v>
       </c>
       <c r="J162" t="n">
         <v>40</v>
@@ -11933,20 +11481,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>720023</t>
-        </is>
+      <c r="C163" t="n">
+        <v>720023</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
           <t>Saif Ali Toor</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>110575</t>
-        </is>
+      <c r="E163" t="n">
+        <v>110575</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -11965,7 +11509,7 @@
         <v>67.0314235</v>
       </c>
       <c r="J163" t="n">
-        <v>18.98299980163574</v>
+        <v>18.9829998</v>
       </c>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
@@ -12001,20 +11545,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>4254</t>
-        </is>
+      <c r="C164" t="n">
+        <v>4254</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
           <t>Hasan Abbas Jaffery</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>110575</t>
-        </is>
+      <c r="E164" t="n">
+        <v>110575</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -12033,7 +11573,7 @@
         <v>67.031409</v>
       </c>
       <c r="J164" t="n">
-        <v>14.28499984741211</v>
+        <v>14.28499985</v>
       </c>
       <c r="K164" t="inlineStr"/>
       <c r="L164" t="inlineStr"/>
@@ -12069,20 +11609,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>2433</t>
-        </is>
+      <c r="C165" t="n">
+        <v>2433</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>Dharmoo Vishan Das</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>117439</t>
-        </is>
+      <c r="E165" t="n">
+        <v>117439</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -12101,7 +11637,7 @@
         <v>67.0201385</v>
       </c>
       <c r="J165" t="n">
-        <v>29.31900024414062</v>
+        <v>29.31900024</v>
       </c>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
@@ -12137,20 +11673,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>2737</t>
-        </is>
+      <c r="C166" t="n">
+        <v>2737</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
           <t>Muhammad Faisal</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>110575</t>
-        </is>
+      <c r="E166" t="n">
+        <v>110575</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -12169,7 +11701,7 @@
         <v>67.0313938</v>
       </c>
       <c r="J166" t="n">
-        <v>21.95299911499023</v>
+        <v>21.95299911</v>
       </c>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
@@ -12205,20 +11737,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>4828</t>
-        </is>
+      <c r="C167" t="n">
+        <v>4828</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
           <t>Muhammad Jibran Alam</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>110575</t>
-        </is>
+      <c r="E167" t="n">
+        <v>110575</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -12237,7 +11765,7 @@
         <v>67.03141720000001</v>
       </c>
       <c r="J167" t="n">
-        <v>23.7180004119873</v>
+        <v>23.71800041</v>
       </c>
       <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr"/>
@@ -12273,20 +11801,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>2123</t>
-        </is>
+      <c r="C168" t="n">
+        <v>2123</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
           <t>Zafur Akhlaque</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>117342</t>
-        </is>
+      <c r="E168" t="n">
+        <v>117342</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -12305,7 +11829,7 @@
         <v>67.0845525</v>
       </c>
       <c r="J168" t="n">
-        <v>45.08100128173828</v>
+        <v>45.08100128</v>
       </c>
       <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
@@ -12341,20 +11865,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>720007</t>
-        </is>
+      <c r="C169" t="n">
+        <v>720007</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
           <t>Faisal Hussain</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>117116</t>
-        </is>
+      <c r="E169" t="n">
+        <v>117116</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -12367,13 +11887,13 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>24.86926790329317</v>
+        <v>24.8692679</v>
       </c>
       <c r="I169" t="n">
-        <v>67.0230777057663</v>
+        <v>67.02307771</v>
       </c>
       <c r="J169" t="n">
-        <v>2.832659751176949</v>
+        <v>2.832659751</v>
       </c>
       <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr"/>
@@ -12409,20 +11929,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
+      <c r="C170" t="n">
+        <v>1192</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>Wasin Baig</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>117753</t>
-        </is>
+      <c r="E170" t="n">
+        <v>117753</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -12441,7 +11957,7 @@
         <v>68.3742608</v>
       </c>
       <c r="J170" t="n">
-        <v>18.63599967956543</v>
+        <v>18.63599968</v>
       </c>
       <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
@@ -12477,20 +11993,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>5009</t>
-        </is>
+      <c r="C171" t="n">
+        <v>5009</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>Hira Anees</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>116674</t>
-        </is>
+      <c r="E171" t="n">
+        <v>116674</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -12503,13 +12015,13 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>24.83560314662919</v>
+        <v>24.83560315</v>
       </c>
       <c r="I171" t="n">
-        <v>67.03364999928117</v>
+        <v>67.03364999999999</v>
       </c>
       <c r="J171" t="n">
-        <v>25.1447767135784</v>
+        <v>25.14477671</v>
       </c>
       <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr"/>
@@ -12545,20 +12057,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
+      <c r="C172" t="n">
+        <v>5259</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
           <t>Sidra Nawab</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>101608</t>
-        </is>
+      <c r="E172" t="n">
+        <v>101608</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -12577,7 +12085,7 @@
         <v>67.0837849</v>
       </c>
       <c r="J172" t="n">
-        <v>42.89699935913086</v>
+        <v>42.89699936</v>
       </c>
       <c r="K172" t="inlineStr"/>
       <c r="L172" t="inlineStr"/>
@@ -12613,20 +12121,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>3415</t>
-        </is>
+      <c r="C173" t="n">
+        <v>3415</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
           <t>Imran Ahmed</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>101728</t>
-        </is>
+      <c r="E173" t="n">
+        <v>101728</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -12645,7 +12149,7 @@
         <v>67.00147010000001</v>
       </c>
       <c r="J173" t="n">
-        <v>18.29800033569336</v>
+        <v>18.29800034</v>
       </c>
       <c r="K173" t="inlineStr"/>
       <c r="L173" t="inlineStr"/>
@@ -12681,20 +12185,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
+      <c r="C174" t="n">
+        <v>2296</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
           <t>Irshad Qureshi</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>110575</t>
-        </is>
+      <c r="E174" t="n">
+        <v>110575</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -12713,7 +12213,7 @@
         <v>67.0314036</v>
       </c>
       <c r="J174" t="n">
-        <v>13.07299995422363</v>
+        <v>13.07299995</v>
       </c>
       <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
@@ -12749,20 +12249,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>2563</t>
-        </is>
+      <c r="C175" t="n">
+        <v>2563</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
           <t>Ahmer Faraz</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>117439</t>
-        </is>
+      <c r="E175" t="n">
+        <v>117439</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -12775,13 +12271,13 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>24.87435255879454</v>
+        <v>24.87435256</v>
       </c>
       <c r="I175" t="n">
-        <v>67.0201348975551</v>
+        <v>67.0201349</v>
       </c>
       <c r="J175" t="n">
-        <v>13.99999999827343</v>
+        <v>14</v>
       </c>
       <c r="K175" t="inlineStr"/>
       <c r="L175" t="inlineStr"/>
@@ -12817,20 +12313,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>4761</t>
-        </is>
+      <c r="C176" t="n">
+        <v>4761</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
           <t>Abdullah</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>110299</t>
-        </is>
+      <c r="E176" t="n">
+        <v>110299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -12849,7 +12341,7 @@
         <v>67.0469052</v>
       </c>
       <c r="J176" t="n">
-        <v>21.95400047302246</v>
+        <v>21.95400047</v>
       </c>
       <c r="K176" t="inlineStr"/>
       <c r="L176" t="inlineStr"/>
@@ -12885,20 +12377,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>4635</t>
-        </is>
+      <c r="C177" t="n">
+        <v>4635</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
           <t>Aadil Mukhtiar</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>119145</t>
-        </is>
+      <c r="E177" t="n">
+        <v>119145</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -12917,7 +12405,7 @@
         <v>71.4856635</v>
       </c>
       <c r="J177" t="n">
-        <v>20.14399909973145</v>
+        <v>20.1439991</v>
       </c>
       <c r="K177" t="inlineStr"/>
       <c r="L177" t="inlineStr"/>
@@ -12953,20 +12441,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>2473</t>
-        </is>
+      <c r="C178" t="n">
+        <v>2473</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
           <t>Muhammad Abdullah</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>117963</t>
-        </is>
+      <c r="E178" t="n">
+        <v>117963</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -12985,7 +12469,7 @@
         <v>73.0922973</v>
       </c>
       <c r="J178" t="n">
-        <v>18.69099998474121</v>
+        <v>18.69099998</v>
       </c>
       <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr"/>
@@ -13021,20 +12505,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>5127</t>
-        </is>
+      <c r="C179" t="n">
+        <v>5127</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
           <t>Anoshia</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>101608</t>
-        </is>
+      <c r="E179" t="n">
+        <v>101608</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -13089,20 +12569,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>4712</t>
-        </is>
+      <c r="C180" t="n">
+        <v>4712</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
           <t>Sameea Jamal</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>119508</t>
-        </is>
+      <c r="E180" t="n">
+        <v>119508</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -13157,20 +12633,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>3955</t>
-        </is>
+      <c r="C181" t="n">
+        <v>3955</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
           <t>Shumaila waseem</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>119508</t>
-        </is>
+      <c r="E181" t="n">
+        <v>119508</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -13183,13 +12655,13 @@
         </is>
       </c>
       <c r="H181" t="n">
-        <v>24.85597197221806</v>
+        <v>24.85597197</v>
       </c>
       <c r="I181" t="n">
-        <v>67.01974422551488</v>
+        <v>67.01974423</v>
       </c>
       <c r="J181" t="n">
-        <v>4.360185004425122</v>
+        <v>4.360185004</v>
       </c>
       <c r="K181" t="inlineStr"/>
       <c r="L181" t="inlineStr"/>
@@ -13225,20 +12697,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
+      <c r="C182" t="n">
+        <v>2382</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
           <t>Iftikhar Amanat</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>101728</t>
-        </is>
+      <c r="E182" t="n">
+        <v>101728</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -13257,7 +12725,7 @@
         <v>67.0015239</v>
       </c>
       <c r="J182" t="n">
-        <v>20.36700057983398</v>
+        <v>20.36700058</v>
       </c>
       <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
@@ -13293,20 +12761,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>3617</t>
-        </is>
+      <c r="C183" t="n">
+        <v>3617</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
           <t>Khalil Ur Rehman</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>101608</t>
-        </is>
+      <c r="E183" t="n">
+        <v>101608</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -13325,7 +12789,7 @@
         <v>67.0837803</v>
       </c>
       <c r="J183" t="n">
-        <v>10.42599964141846</v>
+        <v>10.42599964</v>
       </c>
       <c r="K183" t="inlineStr"/>
       <c r="L183" t="inlineStr"/>
@@ -13361,20 +12825,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>2303</t>
-        </is>
+      <c r="C184" t="n">
+        <v>2303</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
           <t>Rana Muhammad Idrees</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>101580</t>
-        </is>
+      <c r="E184" t="n">
+        <v>101580</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -13393,7 +12853,7 @@
         <v>67.02449249999999</v>
       </c>
       <c r="J184" t="n">
-        <v>11.47900009155273</v>
+        <v>11.47900009</v>
       </c>
       <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
@@ -13429,20 +12889,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>3181</t>
-        </is>
+      <c r="C185" t="n">
+        <v>3181</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
           <t>Muhammad Adeel Bakhtiar Siddiqui</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>117116</t>
-        </is>
+      <c r="E185" t="n">
+        <v>117116</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -13497,20 +12953,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>2195</t>
-        </is>
+      <c r="C186" t="n">
+        <v>2195</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
           <t>Sajid Ali Channa</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>101580</t>
-        </is>
+      <c r="E186" t="n">
+        <v>101580</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -13529,7 +12981,7 @@
         <v>67.0243729</v>
       </c>
       <c r="J186" t="n">
-        <v>14.23700046539307</v>
+        <v>14.23700047</v>
       </c>
       <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
@@ -13565,20 +13017,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>3526</t>
-        </is>
+      <c r="C187" t="n">
+        <v>3526</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
           <t>Kamran</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>116250</t>
-        </is>
+      <c r="E187" t="n">
+        <v>116250</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -13633,20 +13081,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>4987</t>
-        </is>
+      <c r="C188" t="n">
+        <v>4987</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>Muhammad Qasim Malik</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>119840</t>
-        </is>
+      <c r="E188" t="n">
+        <v>119840</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -13665,7 +13109,7 @@
         <v>73.0914528</v>
       </c>
       <c r="J188" t="n">
-        <v>13.16199970245361</v>
+        <v>13.1619997</v>
       </c>
       <c r="K188" t="inlineStr"/>
       <c r="L188" t="inlineStr"/>
@@ -13701,20 +13145,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>4665</t>
-        </is>
+      <c r="C189" t="n">
+        <v>4665</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
           <t>Naeema</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>114723</t>
-        </is>
+      <c r="E189" t="n">
+        <v>114723</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -13733,7 +13173,7 @@
         <v>67.0768018</v>
       </c>
       <c r="J189" t="n">
-        <v>7.652999877929688</v>
+        <v>7.652999878</v>
       </c>
       <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
@@ -13769,20 +13209,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>5062</t>
-        </is>
+      <c r="C190" t="n">
+        <v>5062</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
           <t>MOHAMMAD ZOHAIB BHOMBAL</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>116219</t>
-        </is>
+      <c r="E190" t="n">
+        <v>116219</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -13801,7 +13237,7 @@
         <v>67.038422</v>
       </c>
       <c r="J190" t="n">
-        <v>28.90900039672852</v>
+        <v>28.9090004</v>
       </c>
       <c r="K190" t="inlineStr"/>
       <c r="L190" t="inlineStr"/>
@@ -13837,20 +13273,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>3956</t>
-        </is>
+      <c r="C191" t="n">
+        <v>3956</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
           <t>Rehan zaidi</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>101728</t>
-        </is>
+      <c r="E191" t="n">
+        <v>101728</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -13869,7 +13301,7 @@
         <v>67.0016445</v>
       </c>
       <c r="J191" t="n">
-        <v>23.70199966430664</v>
+        <v>23.70199966</v>
       </c>
       <c r="K191" t="inlineStr"/>
       <c r="L191" t="inlineStr"/>
@@ -13905,20 +13337,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>2625</t>
-        </is>
+      <c r="C192" t="n">
+        <v>2625</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
           <t>REHAN MASUD</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>119840</t>
-        </is>
+      <c r="E192" t="n">
+        <v>119840</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -13937,7 +13365,7 @@
         <v>73.09144430000001</v>
       </c>
       <c r="J192" t="n">
-        <v>9.314000129699707</v>
+        <v>9.31400013</v>
       </c>
       <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
@@ -13973,20 +13401,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>4873</t>
-        </is>
+      <c r="C193" t="n">
+        <v>4873</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
           <t>Muhammad Usman</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>117793</t>
-        </is>
+      <c r="E193" t="n">
+        <v>117793</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -14041,20 +13465,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>1540</t>
-        </is>
+      <c r="C194" t="n">
+        <v>1540</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
           <t>Mehmood Ali</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>118042</t>
-        </is>
+      <c r="E194" t="n">
+        <v>118042</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -14109,20 +13529,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>2608</t>
-        </is>
+      <c r="C195" t="n">
+        <v>2608</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
           <t>Muhammad Siddique Rind</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>102404</t>
-        </is>
+      <c r="E195" t="n">
+        <v>102404</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -14141,7 +13557,7 @@
         <v>67.04324630000001</v>
       </c>
       <c r="J195" t="n">
-        <v>12.72999954223633</v>
+        <v>12.72999954</v>
       </c>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
@@ -14177,20 +13593,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>4830</t>
-        </is>
+      <c r="C196" t="n">
+        <v>4830</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
           <t>Muhammad Ibrahim</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>116219</t>
-        </is>
+      <c r="E196" t="n">
+        <v>116219</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -14245,20 +13657,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>4290</t>
-        </is>
+      <c r="C197" t="n">
+        <v>4290</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
           <t>Shahzadi Mehboob</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>101734</t>
-        </is>
+      <c r="E197" t="n">
+        <v>101734</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -14277,7 +13685,7 @@
         <v>67.0591428</v>
       </c>
       <c r="J197" t="n">
-        <v>28.10000038146973</v>
+        <v>28.10000038</v>
       </c>
       <c r="K197" t="inlineStr"/>
       <c r="L197" t="inlineStr"/>
@@ -14313,20 +13721,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>3989</t>
-        </is>
+      <c r="C198" t="n">
+        <v>3989</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
           <t>Syed kamal Shah</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>115816</t>
-        </is>
+      <c r="E198" t="n">
+        <v>115816</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -14345,7 +13749,7 @@
         <v>73.0383714</v>
       </c>
       <c r="J198" t="n">
-        <v>11.30599975585938</v>
+        <v>11.30599976</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -14359,7 +13763,7 @@
         <v>73.0383674</v>
       </c>
       <c r="N198" t="n">
-        <v>11.43200016021729</v>
+        <v>11.43200016</v>
       </c>
       <c r="O198" t="n">
         <v>1.2</v>
@@ -14371,7 +13775,7 @@
       </c>
       <c r="Q198" t="inlineStr">
         <is>
-          <t>00:00:14</t>
+          <t>0:00:14</t>
         </is>
       </c>
       <c r="R198" t="n">
@@ -14405,20 +13809,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
+      <c r="C199" t="n">
+        <v>2349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
           <t>Attiqullah Khan</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>117315</t>
-        </is>
+      <c r="E199" t="n">
+        <v>117315</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -14437,7 +13837,7 @@
         <v>67.0569249</v>
       </c>
       <c r="J199" t="n">
-        <v>15.74600028991699</v>
+        <v>15.74600029</v>
       </c>
       <c r="K199" t="inlineStr"/>
       <c r="L199" t="inlineStr"/>
@@ -14473,20 +13873,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>4986</t>
-        </is>
+      <c r="C200" t="n">
+        <v>4986</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
           <t>Zain Imdad</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>101744</t>
-        </is>
+      <c r="E200" t="n">
+        <v>101744</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -14499,13 +13895,13 @@
         </is>
       </c>
       <c r="H200" t="n">
-        <v>27.53631507216626</v>
+        <v>27.53631507</v>
       </c>
       <c r="I200" t="n">
-        <v>68.7146342259073</v>
+        <v>68.71463423</v>
       </c>
       <c r="J200" t="n">
-        <v>48.53384830226442</v>
+        <v>48.5338483</v>
       </c>
       <c r="K200" t="inlineStr"/>
       <c r="L200" t="inlineStr"/>
@@ -14541,20 +13937,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>500933</t>
-        </is>
+      <c r="C201" t="n">
+        <v>500933</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
           <t>Muhammad Junaid Pervaiz</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>110696</t>
-        </is>
+      <c r="E201" t="n">
+        <v>110696</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -14573,7 +13965,7 @@
         <v>67.16146500000001</v>
       </c>
       <c r="J201" t="n">
-        <v>47.31700134277344</v>
+        <v>47.31700134</v>
       </c>
       <c r="K201" t="inlineStr"/>
       <c r="L201" t="inlineStr"/>
@@ -14609,20 +14001,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>4001</t>
-        </is>
+      <c r="C202" t="n">
+        <v>4001</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
           <t>Saba Shoaib</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>117315</t>
-        </is>
+      <c r="E202" t="n">
+        <v>117315</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -14641,7 +14029,7 @@
         <v>67.0569174</v>
       </c>
       <c r="J202" t="n">
-        <v>14.64500045776367</v>
+        <v>14.64500046</v>
       </c>
       <c r="K202" t="inlineStr"/>
       <c r="L202" t="inlineStr"/>
@@ -14666,8 +14054,1584 @@
         </is>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>VIS-20261001110542-EE237A</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>4503</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Obaid Ahmed Siddiqui</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>117973</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>PSO S/S 76 (SHEERIN)</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:05:42</t>
+        </is>
+      </c>
+      <c r="H203" t="n">
+        <v>24.81924092</v>
+      </c>
+      <c r="I203" t="n">
+        <v>66.99427702</v>
+      </c>
+      <c r="J203" t="n">
+        <v>3.529129909</v>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T203" t="n">
+        <v>17</v>
+      </c>
+      <c r="U203" t="inlineStr"/>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>VIS-20261001110620-9625FE</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2975</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Faiza Ambreen</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>117315</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>NOOR PS</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:06:20</t>
+        </is>
+      </c>
+      <c r="H204" t="n">
+        <v>24.860244</v>
+      </c>
+      <c r="I204" t="n">
+        <v>67.0569168</v>
+      </c>
+      <c r="J204" t="n">
+        <v>20.30800056</v>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T204" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="U204" t="inlineStr"/>
+      <c r="V204" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>VIS-20261001110633-6B47FB</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>3411</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Amjad</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>117973</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>PSO S/S 76 (SHEERIN)</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:06:33</t>
+        </is>
+      </c>
+      <c r="H205" t="n">
+        <v>24.819133</v>
+      </c>
+      <c r="I205" t="n">
+        <v>66.9942296</v>
+      </c>
+      <c r="J205" t="n">
+        <v>20.10000038</v>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T205" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="U205" t="inlineStr"/>
+      <c r="V205" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>VIS-20261001110649-BD44F3</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>4805</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Arjan Dass</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>110859</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>CRYSTAL F/S</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:06:49</t>
+        </is>
+      </c>
+      <c r="H206" t="n">
+        <v>24.9281485</v>
+      </c>
+      <c r="I206" t="n">
+        <v>67.08890220000001</v>
+      </c>
+      <c r="J206" t="n">
+        <v>14.56499958</v>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T206" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="U206" t="inlineStr"/>
+      <c r="V206" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>VIS-20261001110649-2A2F64</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>4978</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Hiramushtaq</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>116355</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>UNIQUE SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:06:49</t>
+        </is>
+      </c>
+      <c r="H207" t="n">
+        <v>24.86564309</v>
+      </c>
+      <c r="I207" t="n">
+        <v>67.08038003</v>
+      </c>
+      <c r="J207" t="n">
+        <v>14</v>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T207" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="U207" t="inlineStr"/>
+      <c r="V207" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>VIS-20261001110654-CCDD13</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>4131</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Muhammad Shahid</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>110523</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>SAFA ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:06:54</t>
+        </is>
+      </c>
+      <c r="H208" t="n">
+        <v>24.8406393</v>
+      </c>
+      <c r="I208" t="n">
+        <v>67.09842</v>
+      </c>
+      <c r="J208" t="n">
+        <v>22.41300011</v>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T208" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="U208" t="inlineStr"/>
+      <c r="V208" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>VIS-20261001110656-B791C2</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Irfan Baig</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>110696</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>VENUS SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:06:56</t>
+        </is>
+      </c>
+      <c r="H209" t="n">
+        <v>24.84633707</v>
+      </c>
+      <c r="I209" t="n">
+        <v>67.15969198000001</v>
+      </c>
+      <c r="J209" t="n">
+        <v>47.47635907</v>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T209" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="U209" t="inlineStr"/>
+      <c r="V209" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>VIS-20261001110656-9D3E54</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1765</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Iqbal Ahmed</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>110696</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>VENUS SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:06:56</t>
+        </is>
+      </c>
+      <c r="H210" t="n">
+        <v>24.845886</v>
+      </c>
+      <c r="I210" t="n">
+        <v>67.1595963</v>
+      </c>
+      <c r="J210" t="n">
+        <v>16.38299942</v>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T210" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="U210" t="inlineStr"/>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>VIS-20261001110700-3B68FC</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>4260</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Faiza Jamil</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>116355</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>UNIQUE SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:00</t>
+        </is>
+      </c>
+      <c r="H211" t="n">
+        <v>24.865721</v>
+      </c>
+      <c r="I211" t="n">
+        <v>67.08018319999999</v>
+      </c>
+      <c r="J211" t="n">
+        <v>40.33599854</v>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T211" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="U211" t="inlineStr"/>
+      <c r="V211" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>VIS-20261001110700-36E727</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>2498</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Kamran Waseeq</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>116219</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>M.S TARIQ PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:00</t>
+        </is>
+      </c>
+      <c r="H212" t="n">
+        <v>24.8906212</v>
+      </c>
+      <c r="I212" t="n">
+        <v>67.03846900000001</v>
+      </c>
+      <c r="J212" t="n">
+        <v>24.68300056</v>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T212" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U212" t="inlineStr"/>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>VIS-20261001110702-E4E9BC</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1610</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>ABDUL WAHID</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>110696</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>VENUS SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:02</t>
+        </is>
+      </c>
+      <c r="H213" t="n">
+        <v>24.8457602</v>
+      </c>
+      <c r="I213" t="n">
+        <v>67.1596366</v>
+      </c>
+      <c r="J213" t="n">
+        <v>6.900000095</v>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T213" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="U213" t="inlineStr"/>
+      <c r="V213" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>VIS-20261001110703-48097B</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>1468</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>anwar shah</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>101722</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>PSO S/S 7 (A.B GHAZI)</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:03</t>
+        </is>
+      </c>
+      <c r="H214" t="n">
+        <v>24.8079735</v>
+      </c>
+      <c r="I214" t="n">
+        <v>67.0368831</v>
+      </c>
+      <c r="J214" t="n">
+        <v>12.51900005</v>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T214" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="U214" t="inlineStr"/>
+      <c r="V214" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>VIS-20261001110704-B21028</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>3244</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Shahid Nawaz</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>102604</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>MOONRAYS MODERN</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:04</t>
+        </is>
+      </c>
+      <c r="H215" t="n">
+        <v>30.185645</v>
+      </c>
+      <c r="I215" t="n">
+        <v>71.444935</v>
+      </c>
+      <c r="J215" t="n">
+        <v>23.29999924</v>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:10:36</t>
+        </is>
+      </c>
+      <c r="L215" t="n">
+        <v>30.1856133</v>
+      </c>
+      <c r="M215" t="n">
+        <v>71.4449633</v>
+      </c>
+      <c r="N215" t="n">
+        <v>40.45000076293945</v>
+      </c>
+      <c r="O215" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>00:03:32</t>
+        </is>
+      </c>
+      <c r="R215" t="n">
+        <v>0.0589</v>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T215" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="U215" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>VIS-20261001110705-AADBE0</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>4376</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Adil Hussain</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>118512</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>A&amp;Y SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:05</t>
+        </is>
+      </c>
+      <c r="H216" t="n">
+        <v>24.8727813</v>
+      </c>
+      <c r="I216" t="n">
+        <v>66.973046</v>
+      </c>
+      <c r="J216" t="n">
+        <v>28.10000038</v>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T216" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U216" t="inlineStr"/>
+      <c r="V216" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>VIS-20261001110708-A04EB7</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>4324</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Usman Shah</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>110523</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>SAFA ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:08</t>
+        </is>
+      </c>
+      <c r="H217" t="n">
+        <v>24.8406356</v>
+      </c>
+      <c r="I217" t="n">
+        <v>67.0983865</v>
+      </c>
+      <c r="J217" t="n">
+        <v>13.45199966</v>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T217" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="U217" t="inlineStr"/>
+      <c r="V217" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>VIS-20261001110709-6D1860</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>720013</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Abdul Mateen Baloch</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>118512</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>A&amp;Y SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:09</t>
+        </is>
+      </c>
+      <c r="H218" t="n">
+        <v>24.8728163</v>
+      </c>
+      <c r="I218" t="n">
+        <v>66.97282959</v>
+      </c>
+      <c r="J218" t="n">
+        <v>10.8578609</v>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T218" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="U218" t="inlineStr"/>
+      <c r="V218" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>VIS-20261001110710-B12007</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>4741</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Urooj Arif</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>101734</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>PSO S/S 23 (DEFENCE)</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:10</t>
+        </is>
+      </c>
+      <c r="H219" t="n">
+        <v>24.8417592</v>
+      </c>
+      <c r="I219" t="n">
+        <v>67.0591648</v>
+      </c>
+      <c r="J219" t="n">
+        <v>20</v>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T219" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U219" t="inlineStr"/>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>VIS-20261001110711-FCE662</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>4464</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Kamlesh Kumar</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>118391</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>KOHINOOR P/S</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:11</t>
+        </is>
+      </c>
+      <c r="H220" t="n">
+        <v>25.3745905</v>
+      </c>
+      <c r="I220" t="n">
+        <v>68.3548255</v>
+      </c>
+      <c r="J220" t="n">
+        <v>14.66499996</v>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T220" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="U220" t="inlineStr"/>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>VIS-20261001110712-E57311</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>4861</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Anzar Memon</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>116219</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>M.S TARIQ PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:12</t>
+        </is>
+      </c>
+      <c r="H221" t="n">
+        <v>24.89088541</v>
+      </c>
+      <c r="I221" t="n">
+        <v>67.03838843</v>
+      </c>
+      <c r="J221" t="n">
+        <v>24.99998782</v>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T221" t="n">
+        <v>33</v>
+      </c>
+      <c r="U221" t="inlineStr"/>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>VIS-20261001110722-1A3B01</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>4790</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Fatima Areeba Asad</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>101591</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>MASJID E KHIZRA</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:07:22</t>
+        </is>
+      </c>
+      <c r="H222" t="n">
+        <v>24.8588724</v>
+      </c>
+      <c r="I222" t="n">
+        <v>67.0221985</v>
+      </c>
+      <c r="J222" t="n">
+        <v>17.92099953</v>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T222" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="U222" t="inlineStr"/>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>VIS-20261001110941-0B2A98</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>2740</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Imran Haider</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>101585</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>MALKA SONS PET PUMP</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:09:41</t>
+        </is>
+      </c>
+      <c r="H223" t="n">
+        <v>24.84684684684685</v>
+      </c>
+      <c r="I223" t="n">
+        <v>66.99415957623781</v>
+      </c>
+      <c r="J223" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T223" t="n">
+        <v>1120.6</v>
+      </c>
+      <c r="U223" t="inlineStr"/>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>VIS-20261001111002-5A8C61</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>4145</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Khalid  Mehmood</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>117315</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>NOOR PS</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:10:02</t>
+        </is>
+      </c>
+      <c r="H224" t="n">
+        <v>24.8602146</v>
+      </c>
+      <c r="I224" t="n">
+        <v>67.0569098</v>
+      </c>
+      <c r="J224" t="n">
+        <v>17.51899909973145</v>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T224" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="U224" t="inlineStr"/>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>VIS-20261001111037-46609C</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Muhammad Shoaib Baran</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>118512</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>A&amp;Y SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:10:37</t>
+        </is>
+      </c>
+      <c r="H225" t="n">
+        <v>24.87276</v>
+      </c>
+      <c r="I225" t="n">
+        <v>66.972815</v>
+      </c>
+      <c r="J225" t="n">
+        <v>31.85000038146973</v>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T225" t="n">
+        <v>26</v>
+      </c>
+      <c r="U225" t="inlineStr"/>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>VIS-20261001111101-BEF36F</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>2283</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Kamal Mustafa</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>117315</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>NOOR PS</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:11:01</t>
+        </is>
+      </c>
+      <c r="H226" t="n">
+        <v>24.860314</v>
+      </c>
+      <c r="I226" t="n">
+        <v>67.0569064</v>
+      </c>
+      <c r="J226" t="n">
+        <v>12.08500003814697</v>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T226" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U226" t="inlineStr"/>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V202"/>
+  <autoFilter ref="A1:V226"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$226</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V226"/>
+  <dimension ref="A1:V241"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,13 +437,13 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -14875,7 +14875,7 @@
         <v>71.4449633</v>
       </c>
       <c r="N215" t="n">
-        <v>40.45000076293945</v>
+        <v>40.45000076</v>
       </c>
       <c r="O215" t="n">
         <v>4.5</v>
@@ -14887,7 +14887,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>00:03:32</t>
+          <t>0:03:32</t>
         </is>
       </c>
       <c r="R215" t="n">
@@ -15369,20 +15369,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
+      <c r="C223" t="n">
+        <v>2740</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
           <t>Imran Haider</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>101585</t>
-        </is>
+      <c r="E223" t="n">
+        <v>101585</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -15395,10 +15391,10 @@
         </is>
       </c>
       <c r="H223" t="n">
-        <v>24.84684684684685</v>
+        <v>24.84684685</v>
       </c>
       <c r="I223" t="n">
-        <v>66.99415957623781</v>
+        <v>66.99415958</v>
       </c>
       <c r="J223" t="n">
         <v>2000</v>
@@ -15437,20 +15433,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>4145</t>
-        </is>
+      <c r="C224" t="n">
+        <v>4145</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
           <t>Khalid  Mehmood</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>117315</t>
-        </is>
+      <c r="E224" t="n">
+        <v>117315</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -15469,7 +15461,7 @@
         <v>67.0569098</v>
       </c>
       <c r="J224" t="n">
-        <v>17.51899909973145</v>
+        <v>17.5189991</v>
       </c>
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
@@ -15505,20 +15497,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>5057</t>
-        </is>
+      <c r="C225" t="n">
+        <v>5057</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
           <t>Muhammad Shoaib Baran</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>118512</t>
-        </is>
+      <c r="E225" t="n">
+        <v>118512</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -15537,7 +15525,7 @@
         <v>66.972815</v>
       </c>
       <c r="J225" t="n">
-        <v>31.85000038146973</v>
+        <v>31.85000038</v>
       </c>
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
@@ -15573,20 +15561,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
+      <c r="C226" t="n">
+        <v>2283</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
           <t>Kamal Mustafa</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>117315</t>
-        </is>
+      <c r="E226" t="n">
+        <v>117315</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -15605,7 +15589,7 @@
         <v>67.0569064</v>
       </c>
       <c r="J226" t="n">
-        <v>12.08500003814697</v>
+        <v>12.08500004</v>
       </c>
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
@@ -15630,8 +15614,996 @@
         </is>
       </c>
     </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>VIS-20261001111132-C103D4</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>2991</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Imtiaz Ali Abro</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>110523</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>SAFA ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:11:32</t>
+        </is>
+      </c>
+      <c r="H227" t="n">
+        <v>24.8407356</v>
+      </c>
+      <c r="I227" t="n">
+        <v>67.098473</v>
+      </c>
+      <c r="J227" t="n">
+        <v>21.32500076</v>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T227" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="U227" t="inlineStr"/>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>VIS-20261001111203-565303</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>3250</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Irfan Baig</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>110696</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>VENUS SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:12:03</t>
+        </is>
+      </c>
+      <c r="H228" t="n">
+        <v>24.84640039</v>
+      </c>
+      <c r="I228" t="n">
+        <v>67.1597304</v>
+      </c>
+      <c r="J228" t="n">
+        <v>33.9790866</v>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T228" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="U228" t="inlineStr"/>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>VIS-20261001111208-486FD1</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>510371</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Muhammad Haris</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>116355</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>UNIQUE SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:12:08</t>
+        </is>
+      </c>
+      <c r="H229" t="n">
+        <v>24.8657106</v>
+      </c>
+      <c r="I229" t="n">
+        <v>67.0802503</v>
+      </c>
+      <c r="J229" t="n">
+        <v>22.41900063</v>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T229" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U229" t="inlineStr"/>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>VIS-20261001111210-8C84FA</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>501450</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Muhammad Moaz</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>119508</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>PSO S/S 87(SINDH)</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:12:10</t>
+        </is>
+      </c>
+      <c r="H230" t="n">
+        <v>24.8559716</v>
+      </c>
+      <c r="I230" t="n">
+        <v>67.01998242000001</v>
+      </c>
+      <c r="J230" t="n">
+        <v>39.99999978</v>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T230" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="U230" t="inlineStr"/>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>VIS-20261001111222-1CAC3D</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>720006</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Jamal mustafa khan</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>101591</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>MASJID E KHIZRA</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:12:22</t>
+        </is>
+      </c>
+      <c r="H231" t="n">
+        <v>24.8589458</v>
+      </c>
+      <c r="I231" t="n">
+        <v>67.02221539999999</v>
+      </c>
+      <c r="J231" t="n">
+        <v>9.083000182999999</v>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T231" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="U231" t="inlineStr"/>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>VIS-20261001111228-748372</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>3958</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Ejaz Ahmed</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>112839</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SHAHEEN SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:12:28</t>
+        </is>
+      </c>
+      <c r="H232" t="n">
+        <v>24.8871116</v>
+      </c>
+      <c r="I232" t="n">
+        <v>67.1457219</v>
+      </c>
+      <c r="J232" t="n">
+        <v>30.94099998</v>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T232" t="n">
+        <v>19</v>
+      </c>
+      <c r="U232" t="inlineStr"/>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>VIS-20261001111233-5B3518</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>5084</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Talha Rashid</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>118391</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>KOHINOOR P/S</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:12:33</t>
+        </is>
+      </c>
+      <c r="H233" t="n">
+        <v>25.3745317</v>
+      </c>
+      <c r="I233" t="n">
+        <v>68.3548761</v>
+      </c>
+      <c r="J233" t="n">
+        <v>18.18199921</v>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T233" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="U233" t="inlineStr"/>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>VIS-20261001111304-FB3CF0</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>720021</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Syeda Fatima Khalid</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>120605</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>A &amp; S P/S</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:13:04</t>
+        </is>
+      </c>
+      <c r="H234" t="n">
+        <v>24.8852492</v>
+      </c>
+      <c r="I234" t="n">
+        <v>67.17355535</v>
+      </c>
+      <c r="J234" t="n">
+        <v>26.05825654</v>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T234" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="U234" t="inlineStr"/>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>VIS-20261001111413-31B5A0</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3608</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Muhammad Yousaf Suri</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>120406</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>ENCLAVE FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:14:13</t>
+        </is>
+      </c>
+      <c r="H235" t="n">
+        <v>33.6864475</v>
+      </c>
+      <c r="I235" t="n">
+        <v>73.2486976</v>
+      </c>
+      <c r="J235" t="n">
+        <v>9.935000419616699</v>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T235" t="n">
+        <v>32073.9</v>
+      </c>
+      <c r="U235" t="inlineStr"/>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>VIS-20261001111413-4F6862</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>5175</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Arslan Amjad Bohio</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>118367</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>AHMAD BROTHERS</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:14:13</t>
+        </is>
+      </c>
+      <c r="H236" t="n">
+        <v>24.8734645</v>
+      </c>
+      <c r="I236" t="n">
+        <v>67.0487454</v>
+      </c>
+      <c r="J236" t="n">
+        <v>20.6879997253418</v>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T236" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U236" t="inlineStr"/>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>VIS-20261001111415-BE2D64</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>4951</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Syed Muhammad Imad Hasani</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>119508</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>PSO S/S 87(SINDH)</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:14:15</t>
+        </is>
+      </c>
+      <c r="H237" t="n">
+        <v>24.8560443</v>
+      </c>
+      <c r="I237" t="n">
+        <v>67.0198315</v>
+      </c>
+      <c r="J237" t="n">
+        <v>16.54000091552734</v>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T237" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="U237" t="inlineStr"/>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>VIS-20261001111417-2A957D</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>3185</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Saba amjad</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>101722</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>PSO S/S 7 (A.B GHAZI)</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:14:17</t>
+        </is>
+      </c>
+      <c r="H238" t="n">
+        <v>24.8080452</v>
+      </c>
+      <c r="I238" t="n">
+        <v>67.0369524</v>
+      </c>
+      <c r="J238" t="n">
+        <v>25.46699905395508</v>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T238" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="U238" t="inlineStr"/>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>VIS-20261001111432-23E589</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Simrah Nadir</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>112839</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>SHAHEEN SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:14:32</t>
+        </is>
+      </c>
+      <c r="H239" t="n">
+        <v>24.88693100407102</v>
+      </c>
+      <c r="I239" t="n">
+        <v>67.14561240391174</v>
+      </c>
+      <c r="J239" t="n">
+        <v>12.79189101450818</v>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T239" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="U239" t="inlineStr"/>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>VIS-20261001111517-CDC805</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Sheikh Yawar Mumtaz</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>112839</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>SHAHEEN SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:15:17</t>
+        </is>
+      </c>
+      <c r="H240" t="n">
+        <v>24.8871813</v>
+      </c>
+      <c r="I240" t="n">
+        <v>67.14571599999999</v>
+      </c>
+      <c r="J240" t="n">
+        <v>32.65900039672852</v>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr"/>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T240" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="U240" t="inlineStr"/>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>VIS-20261001111611-999447</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>5250</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Syeda ibtasama khatoon</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>117973</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>PSO S/S 76 (SHEERIN)</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:16:11</t>
+        </is>
+      </c>
+      <c r="H241" t="n">
+        <v>24.81901635397644</v>
+      </c>
+      <c r="I241" t="n">
+        <v>66.99438144975981</v>
+      </c>
+      <c r="J241" t="n">
+        <v>12.68416606484229</v>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T241" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="U241" t="inlineStr"/>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V226"/>
+  <autoFilter ref="A1:V241"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$245</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V241"/>
+  <dimension ref="A1:V245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,9 +437,9 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -16137,20 +16137,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>3608</t>
-        </is>
+      <c r="C235" t="n">
+        <v>3608</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
           <t>Muhammad Yousaf Suri</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>120406</t>
-        </is>
+      <c r="E235" t="n">
+        <v>120406</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -16169,7 +16165,7 @@
         <v>73.2486976</v>
       </c>
       <c r="J235" t="n">
-        <v>9.935000419616699</v>
+        <v>9.93500042</v>
       </c>
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
@@ -16205,20 +16201,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr">
-        <is>
-          <t>5175</t>
-        </is>
+      <c r="C236" t="n">
+        <v>5175</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
           <t>Arslan Amjad Bohio</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
-        <is>
-          <t>118367</t>
-        </is>
+      <c r="E236" t="n">
+        <v>118367</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -16237,7 +16229,7 @@
         <v>67.0487454</v>
       </c>
       <c r="J236" t="n">
-        <v>20.6879997253418</v>
+        <v>20.68799973</v>
       </c>
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr"/>
@@ -16273,20 +16265,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>4951</t>
-        </is>
+      <c r="C237" t="n">
+        <v>4951</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
           <t>Syed Muhammad Imad Hasani</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
-        <is>
-          <t>119508</t>
-        </is>
+      <c r="E237" t="n">
+        <v>119508</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -16305,7 +16293,7 @@
         <v>67.0198315</v>
       </c>
       <c r="J237" t="n">
-        <v>16.54000091552734</v>
+        <v>16.54000092</v>
       </c>
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
@@ -16341,20 +16329,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>3185</t>
-        </is>
+      <c r="C238" t="n">
+        <v>3185</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
           <t>Saba amjad</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
-        <is>
-          <t>101722</t>
-        </is>
+      <c r="E238" t="n">
+        <v>101722</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -16373,7 +16357,7 @@
         <v>67.0369524</v>
       </c>
       <c r="J238" t="n">
-        <v>25.46699905395508</v>
+        <v>25.46699905</v>
       </c>
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr"/>
@@ -16409,20 +16393,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>4719</t>
-        </is>
+      <c r="C239" t="n">
+        <v>4719</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
           <t>Simrah Nadir</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>112839</t>
-        </is>
+      <c r="E239" t="n">
+        <v>112839</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -16435,13 +16415,13 @@
         </is>
       </c>
       <c r="H239" t="n">
-        <v>24.88693100407102</v>
+        <v>24.886931</v>
       </c>
       <c r="I239" t="n">
-        <v>67.14561240391174</v>
+        <v>67.1456124</v>
       </c>
       <c r="J239" t="n">
-        <v>12.79189101450818</v>
+        <v>12.79189101</v>
       </c>
       <c r="K239" t="inlineStr"/>
       <c r="L239" t="inlineStr"/>
@@ -16477,20 +16457,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>3174</t>
-        </is>
+      <c r="C240" t="n">
+        <v>3174</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
           <t>Sheikh Yawar Mumtaz</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
-        <is>
-          <t>112839</t>
-        </is>
+      <c r="E240" t="n">
+        <v>112839</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -16509,7 +16485,7 @@
         <v>67.14571599999999</v>
       </c>
       <c r="J240" t="n">
-        <v>32.65900039672852</v>
+        <v>32.6590004</v>
       </c>
       <c r="K240" t="inlineStr"/>
       <c r="L240" t="inlineStr"/>
@@ -16545,20 +16521,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>5250</t>
-        </is>
+      <c r="C241" t="n">
+        <v>5250</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
           <t>Syeda ibtasama khatoon</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>117973</t>
-        </is>
+      <c r="E241" t="n">
+        <v>117973</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -16571,13 +16543,13 @@
         </is>
       </c>
       <c r="H241" t="n">
-        <v>24.81901635397644</v>
+        <v>24.81901635</v>
       </c>
       <c r="I241" t="n">
-        <v>66.99438144975981</v>
+        <v>66.99438145000001</v>
       </c>
       <c r="J241" t="n">
-        <v>12.68416606484229</v>
+        <v>12.68416606</v>
       </c>
       <c r="K241" t="inlineStr"/>
       <c r="L241" t="inlineStr"/>
@@ -16602,8 +16574,268 @@
         </is>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>VIS-20261001111832-502C73</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>3590</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Awais Saleem</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>120209</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>PSO S/S 91 (GULBERG)</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:18:32</t>
+        </is>
+      </c>
+      <c r="H242" t="n">
+        <v>24.9378373</v>
+      </c>
+      <c r="I242" t="n">
+        <v>67.0762642</v>
+      </c>
+      <c r="J242" t="n">
+        <v>20.65699959</v>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr"/>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T242" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U242" t="inlineStr"/>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>VIS-20261001111858-B9B614</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>501430</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Aila Siddiqui</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>112839</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>SHAHEEN SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:18:58</t>
+        </is>
+      </c>
+      <c r="H243" t="n">
+        <v>24.887146</v>
+      </c>
+      <c r="I243" t="n">
+        <v>67.1456956</v>
+      </c>
+      <c r="J243" t="n">
+        <v>34.70999908</v>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T243" t="n">
+        <v>22</v>
+      </c>
+      <c r="U243" t="inlineStr"/>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>VIS-20261001111935-AA06AC</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>720020</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Muhammad Usman</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>120605</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>A &amp; S P/S</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:19:35</t>
+        </is>
+      </c>
+      <c r="H244" t="n">
+        <v>24.8852178</v>
+      </c>
+      <c r="I244" t="n">
+        <v>67.173661</v>
+      </c>
+      <c r="J244" t="n">
+        <v>20</v>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T244" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="U244" t="inlineStr"/>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>VIS-20261001112155-371AFB</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Waqas Nazim Siddiqui</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>113237</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>PSO S/S-70 (Globe)</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:21:55</t>
+        </is>
+      </c>
+      <c r="H245" t="n">
+        <v>24.9271979</v>
+      </c>
+      <c r="I245" t="n">
+        <v>67.0328748</v>
+      </c>
+      <c r="J245" t="n">
+        <v>18.2189998626709</v>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T245" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="U245" t="inlineStr"/>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V241"/>
+  <autoFilter ref="A1:V245"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$249</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V245"/>
+  <dimension ref="A1:V249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,7 +439,7 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
@@ -16777,20 +16777,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>2905</t>
-        </is>
+      <c r="C245" t="n">
+        <v>2905</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
           <t>Waqas Nazim Siddiqui</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>113237</t>
-        </is>
+      <c r="E245" t="n">
+        <v>113237</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -16809,7 +16805,7 @@
         <v>67.0328748</v>
       </c>
       <c r="J245" t="n">
-        <v>18.2189998626709</v>
+        <v>18.21899986</v>
       </c>
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr"/>
@@ -16834,8 +16830,268 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>VIS-20261001112308-1F38A7</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>4796</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Taha Hussain</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>101722</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>PSO S/S 7 (A.B GHAZI)</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:23:08</t>
+        </is>
+      </c>
+      <c r="H246" t="n">
+        <v>24.80798196</v>
+      </c>
+      <c r="I246" t="n">
+        <v>67.03676564</v>
+      </c>
+      <c r="J246" t="n">
+        <v>12.93703884</v>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T246" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="U246" t="inlineStr"/>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>VIS-20261001112308-90DA34</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>720003</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>M Waqas Ansari</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>120605</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>A &amp; S P/S</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:23:08</t>
+        </is>
+      </c>
+      <c r="H247" t="n">
+        <v>24.8852177</v>
+      </c>
+      <c r="I247" t="n">
+        <v>67.1736612</v>
+      </c>
+      <c r="J247" t="n">
+        <v>20</v>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T247" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="U247" t="inlineStr"/>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>VIS-20261001112415-58C91A</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>4927</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Ayesha Siddiqi</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>120209</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>PSO S/S 91 (GULBERG)</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:24:15</t>
+        </is>
+      </c>
+      <c r="H248" t="n">
+        <v>24.9378173</v>
+      </c>
+      <c r="I248" t="n">
+        <v>67.0764499</v>
+      </c>
+      <c r="J248" t="n">
+        <v>11.96500015</v>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T248" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U248" t="inlineStr"/>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>VIS-20261001112816-F3D6B1</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>3716</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Usman Ghani Malik</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>101663</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>NEW AERO SER STATION</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:28:16</t>
+        </is>
+      </c>
+      <c r="H249" t="n">
+        <v>24.8928655</v>
+      </c>
+      <c r="I249" t="n">
+        <v>67.1587699</v>
+      </c>
+      <c r="J249" t="n">
+        <v>23.61000061035156</v>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T249" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="U249" t="inlineStr"/>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V245"/>
+  <autoFilter ref="A1:V249"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$258</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V249"/>
+  <dimension ref="A1:V258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -17033,20 +17033,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>3716</t>
-        </is>
+      <c r="C249" t="n">
+        <v>3716</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
           <t>Usman Ghani Malik</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>101663</t>
-        </is>
+      <c r="E249" t="n">
+        <v>101663</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -17065,7 +17061,7 @@
         <v>67.1587699</v>
       </c>
       <c r="J249" t="n">
-        <v>23.61000061035156</v>
+        <v>23.61000061</v>
       </c>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
@@ -17090,8 +17086,592 @@
         </is>
       </c>
     </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>VIS-20261001112931-D6ACF4</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>3189</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Rashid Mukhtar</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>115282</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>RAHEEL SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:29:31</t>
+        </is>
+      </c>
+      <c r="H250" t="n">
+        <v>24.8683175</v>
+      </c>
+      <c r="I250" t="n">
+        <v>67.0113355</v>
+      </c>
+      <c r="J250" t="n">
+        <v>15.18900013</v>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T250" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="U250" t="inlineStr"/>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>VIS-20261001112949-086AFF</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>1511</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NASEEM Ahmed</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>101722</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>PSO S/S 7 (A.B GHAZI)</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:29:49</t>
+        </is>
+      </c>
+      <c r="H251" t="n">
+        <v>24.80800676</v>
+      </c>
+      <c r="I251" t="n">
+        <v>67.03682752</v>
+      </c>
+      <c r="J251" t="n">
+        <v>14.5819751</v>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T251" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="U251" t="inlineStr"/>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>VIS-20261001113001-61EA13</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>3977</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Syed Zeeshan Akhtar</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>110785</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>PETARIAN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:30:01</t>
+        </is>
+      </c>
+      <c r="H252" t="n">
+        <v>24.9005982</v>
+      </c>
+      <c r="I252" t="n">
+        <v>67.0187365</v>
+      </c>
+      <c r="J252" t="n">
+        <v>26.7159996</v>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T252" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="U252" t="inlineStr"/>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>VIS-20261001113030-0E5577</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2333</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Aamir Muhammad Yousuf Brohi</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>120290</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>SKY BLUE SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:30:30</t>
+        </is>
+      </c>
+      <c r="H253" t="n">
+        <v>24.9182716</v>
+      </c>
+      <c r="I253" t="n">
+        <v>67.0528441</v>
+      </c>
+      <c r="J253" t="n">
+        <v>44.40800095</v>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T253" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="U253" t="inlineStr"/>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>VIS-20261001113219-80E64A</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2706</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Waleed Ahsan</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>101594</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>NAWAZ SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:32:19</t>
+        </is>
+      </c>
+      <c r="H254" t="n">
+        <v>24.85311622</v>
+      </c>
+      <c r="I254" t="n">
+        <v>66.99438178</v>
+      </c>
+      <c r="J254" t="n">
+        <v>15.594516</v>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T254" t="n">
+        <v>26</v>
+      </c>
+      <c r="U254" t="inlineStr"/>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>VIS-20261001113252-5A3E66</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2192</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Syed Tariq Shehzad</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>113237</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>PSO S/S-70 (Globe)</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:32:52</t>
+        </is>
+      </c>
+      <c r="H255" t="n">
+        <v>24.9271977</v>
+      </c>
+      <c r="I255" t="n">
+        <v>67.0329983</v>
+      </c>
+      <c r="J255" t="n">
+        <v>16.1760006</v>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T255" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U255" t="inlineStr"/>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>VIS-20261001113257-B38C08</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>5124</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>JATIN KUMAR</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>115469</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>LANDHI GASOLINE SERVICE</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:32:57</t>
+        </is>
+      </c>
+      <c r="H256" t="n">
+        <v>24.8458927</v>
+      </c>
+      <c r="I256" t="n">
+        <v>67.2046533</v>
+      </c>
+      <c r="J256" t="n">
+        <v>20</v>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T256" t="n">
+        <v>9</v>
+      </c>
+      <c r="U256" t="inlineStr"/>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>VIS-20261001114002-355B0B</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>3944</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Asif</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>116207</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>AL BADAR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:40:02</t>
+        </is>
+      </c>
+      <c r="H257" t="n">
+        <v>24.8840719</v>
+      </c>
+      <c r="I257" t="n">
+        <v>66.97703869999999</v>
+      </c>
+      <c r="J257" t="n">
+        <v>11.73499965667725</v>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T257" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="U257" t="inlineStr"/>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>VIS-20261001114008-30B53C</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>4450</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Azam Nafees</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>101545</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>RAZA PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:40:08</t>
+        </is>
+      </c>
+      <c r="H258" t="n">
+        <v>24.8844844</v>
+      </c>
+      <c r="I258" t="n">
+        <v>67.0291096</v>
+      </c>
+      <c r="J258" t="n">
+        <v>33.85100173950195</v>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T258" t="n">
+        <v>18</v>
+      </c>
+      <c r="U258" t="inlineStr"/>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V249"/>
+  <autoFilter ref="A1:V258"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$258</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$265</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V258"/>
+  <dimension ref="A1:V265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -17545,20 +17545,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>3944</t>
-        </is>
+      <c r="C257" t="n">
+        <v>3944</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
           <t>Asif</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>116207</t>
-        </is>
+      <c r="E257" t="n">
+        <v>116207</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -17577,7 +17573,7 @@
         <v>66.97703869999999</v>
       </c>
       <c r="J257" t="n">
-        <v>11.73499965667725</v>
+        <v>11.73499966</v>
       </c>
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr"/>
@@ -17613,20 +17609,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>4450</t>
-        </is>
+      <c r="C258" t="n">
+        <v>4450</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
           <t>Azam Nafees</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>101545</t>
-        </is>
+      <c r="E258" t="n">
+        <v>101545</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -17645,7 +17637,7 @@
         <v>67.0291096</v>
       </c>
       <c r="J258" t="n">
-        <v>33.85100173950195</v>
+        <v>33.85100174</v>
       </c>
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
@@ -17670,8 +17662,468 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>VIS-20261001114136-E3D7D9</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>4405</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Faisal Ahmed Khan</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>117965</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>SAM PETROLEUM 2</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41:36</t>
+        </is>
+      </c>
+      <c r="H259" t="n">
+        <v>24.8387612</v>
+      </c>
+      <c r="I259" t="n">
+        <v>67.2590556</v>
+      </c>
+      <c r="J259" t="n">
+        <v>17.42399979</v>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T259" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="U259" t="inlineStr"/>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>VIS-20261001114142-4DC905</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>wasim mohiuddin</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>101722</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>PSO S/S 7 (A.B GHAZI)</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41:42</t>
+        </is>
+      </c>
+      <c r="H260" t="n">
+        <v>24.8081827</v>
+      </c>
+      <c r="I260" t="n">
+        <v>67.03688889999999</v>
+      </c>
+      <c r="J260" t="n">
+        <v>17.03300095</v>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T260" t="n">
+        <v>100</v>
+      </c>
+      <c r="U260" t="inlineStr"/>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>VIS-20261001114148-B17AA5</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>1491</v>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>farhan hussain farshori</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>101722</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>PSO S/S 7 (A.B GHAZI)</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:41:48</t>
+        </is>
+      </c>
+      <c r="H261" t="n">
+        <v>24.8080756</v>
+      </c>
+      <c r="I261" t="n">
+        <v>67.036979</v>
+      </c>
+      <c r="J261" t="n">
+        <v>29.45000076</v>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T261" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="U261" t="inlineStr"/>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>VIS-20261001114229-A625E0</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>5074</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Syed Fahiluddin Faraz</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>119420</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>HAFIZ PS</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:42:29</t>
+        </is>
+      </c>
+      <c r="H262" t="n">
+        <v>24.9454141</v>
+      </c>
+      <c r="I262" t="n">
+        <v>67.1090159</v>
+      </c>
+      <c r="J262" t="n">
+        <v>20</v>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T262" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="U262" t="inlineStr"/>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>VIS-20261001114418-585017</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>2622</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Aamir Habib</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>112541</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>FARZAM &amp; CO.</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:44:18</t>
+        </is>
+      </c>
+      <c r="H263" t="n">
+        <v>24.9211664</v>
+      </c>
+      <c r="I263" t="n">
+        <v>67.14572699999999</v>
+      </c>
+      <c r="J263" t="n">
+        <v>20</v>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T263" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="U263" t="inlineStr"/>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>VIS-20261001114444-9AEA26</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>5128</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Saad Ahmed Ansari</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>116170</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>MALIR F/S</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:44:44</t>
+        </is>
+      </c>
+      <c r="H264" t="n">
+        <v>24.8700436</v>
+      </c>
+      <c r="I264" t="n">
+        <v>67.2004407</v>
+      </c>
+      <c r="J264" t="n">
+        <v>1.047000050544739</v>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T264" t="n">
+        <v>242.1</v>
+      </c>
+      <c r="U264" t="inlineStr"/>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>VIS-20261001114523-011FA5</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>2963</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Wakeel Ahmed</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>101598</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>TRICO SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:45:23</t>
+        </is>
+      </c>
+      <c r="H265" t="n">
+        <v>24.8912183</v>
+      </c>
+      <c r="I265" t="n">
+        <v>67.0807868</v>
+      </c>
+      <c r="J265" t="n">
+        <v>13.59000015258789</v>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T265" t="n">
+        <v>6</v>
+      </c>
+      <c r="U265" t="inlineStr"/>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V258"/>
+  <autoFilter ref="A1:V265"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$265</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$273</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V265"/>
+  <dimension ref="A1:V273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -17929,20 +17929,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>2622</t>
-        </is>
+      <c r="C263" t="n">
+        <v>2622</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
           <t>Aamir Habib</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
-        <is>
-          <t>112541</t>
-        </is>
+      <c r="E263" t="n">
+        <v>112541</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -17997,20 +17993,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>5128</t>
-        </is>
+      <c r="C264" t="n">
+        <v>5128</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
           <t>Saad Ahmed Ansari</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
-        <is>
-          <t>116170</t>
-        </is>
+      <c r="E264" t="n">
+        <v>116170</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -18029,7 +18021,7 @@
         <v>67.2004407</v>
       </c>
       <c r="J264" t="n">
-        <v>1.047000050544739</v>
+        <v>1.047000051</v>
       </c>
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
@@ -18065,20 +18057,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>2963</t>
-        </is>
+      <c r="C265" t="n">
+        <v>2963</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
           <t>Wakeel Ahmed</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>101598</t>
-        </is>
+      <c r="E265" t="n">
+        <v>101598</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -18097,7 +18085,7 @@
         <v>67.0807868</v>
       </c>
       <c r="J265" t="n">
-        <v>13.59000015258789</v>
+        <v>13.59000015</v>
       </c>
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
@@ -18122,8 +18110,528 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>VIS-20261001114644-5C09DE</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>4006</v>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Shahid Musani</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>120605</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>A &amp; S P/S</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:46:44</t>
+        </is>
+      </c>
+      <c r="H266" t="n">
+        <v>24.8852178</v>
+      </c>
+      <c r="I266" t="n">
+        <v>67.173661</v>
+      </c>
+      <c r="J266" t="n">
+        <v>20</v>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T266" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="U266" t="inlineStr"/>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>VIS-20261001114757-9DD0A3</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>4289</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Danish Iqbal</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>120290</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>SKY BLUE SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:47:57</t>
+        </is>
+      </c>
+      <c r="H267" t="n">
+        <v>24.9182465</v>
+      </c>
+      <c r="I267" t="n">
+        <v>67.05285600000001</v>
+      </c>
+      <c r="J267" t="n">
+        <v>43.03900146</v>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T267" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="U267" t="inlineStr"/>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>VIS-20261001114834-5ECED5</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>1387</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Junaid Ali Khan</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>101545</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>RAZA PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:48:34</t>
+        </is>
+      </c>
+      <c r="H268" t="n">
+        <v>24.8846774</v>
+      </c>
+      <c r="I268" t="n">
+        <v>67.0291514</v>
+      </c>
+      <c r="J268" t="n">
+        <v>14.63700008</v>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T268" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="U268" t="inlineStr"/>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>VIS-20261001114906-F0EBB0</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>3262</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Muhammad Arshid</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>120287</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>ARABIAN GASOLINE</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:49:06</t>
+        </is>
+      </c>
+      <c r="H269" t="n">
+        <v>24.8392959</v>
+      </c>
+      <c r="I269" t="n">
+        <v>67.11966270000001</v>
+      </c>
+      <c r="J269" t="n">
+        <v>20</v>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T269" t="n">
+        <v>40</v>
+      </c>
+      <c r="U269" t="inlineStr"/>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>VIS-20261001114913-8467D1</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>3975</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Javed Ahmed</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>120287</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>ARABIAN GASOLINE</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:49:13</t>
+        </is>
+      </c>
+      <c r="H270" t="n">
+        <v>24.8393148</v>
+      </c>
+      <c r="I270" t="n">
+        <v>67.1196626</v>
+      </c>
+      <c r="J270" t="n">
+        <v>7.731999874</v>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T270" t="n">
+        <v>42</v>
+      </c>
+      <c r="U270" t="inlineStr"/>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>VIS-20261001114918-3F3C9D</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>4050</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>MUHAMMAD SHAMSHAIR ALI KHAN</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>116170</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>MALIR F/S</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:49:18</t>
+        </is>
+      </c>
+      <c r="H271" t="n">
+        <v>24.8700613</v>
+      </c>
+      <c r="I271" t="n">
+        <v>67.20021130000001</v>
+      </c>
+      <c r="J271" t="n">
+        <v>20</v>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T271" t="n">
+        <v>219.4</v>
+      </c>
+      <c r="U271" t="inlineStr"/>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>VIS-20261001115032-C03A5A</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>4844</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Muhammad Yasir Khan</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>120287</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>ARABIAN GASOLINE</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:50:32</t>
+        </is>
+      </c>
+      <c r="H272" t="n">
+        <v>24.8393062</v>
+      </c>
+      <c r="I272" t="n">
+        <v>67.1196626</v>
+      </c>
+      <c r="J272" t="n">
+        <v>15.46399974822998</v>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T272" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="U272" t="inlineStr"/>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>VIS-20261001115037-545118</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>3714</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Muhammad Saeed</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>113862</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>KHYBER SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:50:37</t>
+        </is>
+      </c>
+      <c r="H273" t="n">
+        <v>24.8551748</v>
+      </c>
+      <c r="I273" t="n">
+        <v>67.22880240000001</v>
+      </c>
+      <c r="J273" t="n">
+        <v>26.89100074768066</v>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr"/>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T273" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="U273" t="inlineStr"/>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V265"/>
+  <autoFilter ref="A1:V273"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$273</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$285</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V273"/>
+  <dimension ref="A1:V285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,8 +437,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -18505,20 +18505,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr">
-        <is>
-          <t>4844</t>
-        </is>
+      <c r="C272" t="n">
+        <v>4844</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
           <t>Muhammad Yasir Khan</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr">
-        <is>
-          <t>120287</t>
-        </is>
+      <c r="E272" t="n">
+        <v>120287</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -18537,7 +18533,7 @@
         <v>67.1196626</v>
       </c>
       <c r="J272" t="n">
-        <v>15.46399974822998</v>
+        <v>15.46399975</v>
       </c>
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
@@ -18573,20 +18569,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>3714</t>
-        </is>
+      <c r="C273" t="n">
+        <v>3714</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
           <t>Muhammad Saeed</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr">
-        <is>
-          <t>113862</t>
-        </is>
+      <c r="E273" t="n">
+        <v>113862</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -18605,7 +18597,7 @@
         <v>67.22880240000001</v>
       </c>
       <c r="J273" t="n">
-        <v>26.89100074768066</v>
+        <v>26.89100075</v>
       </c>
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
@@ -18630,8 +18622,796 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>VIS-20261001115046-DACCD0</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>1762</v>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Muhammad Junaid</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>113354</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>DALMIA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:50:46</t>
+        </is>
+      </c>
+      <c r="H274" t="n">
+        <v>24.8996958</v>
+      </c>
+      <c r="I274" t="n">
+        <v>67.1077662</v>
+      </c>
+      <c r="J274" t="n">
+        <v>44.13000107</v>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr"/>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T274" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U274" t="inlineStr"/>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>VIS-20261001115051-75BFC8</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>3591</v>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Muhammad Irfan khan</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>119590</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>MOHSIN F/S</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:50:51</t>
+        </is>
+      </c>
+      <c r="H275" t="n">
+        <v>31.7631003</v>
+      </c>
+      <c r="I275" t="n">
+        <v>70.9236264</v>
+      </c>
+      <c r="J275" t="n">
+        <v>18.34900093</v>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr"/>
+      <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
+      <c r="R275" t="inlineStr"/>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T275" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="U275" t="inlineStr"/>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>VIS-20261001115206-C6E51A</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>5042</v>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Shiraz Ahmed</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>118850</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>MEHDI PETROLEUM SER</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:52:06</t>
+        </is>
+      </c>
+      <c r="H276" t="n">
+        <v>24.901995</v>
+      </c>
+      <c r="I276" t="n">
+        <v>67.2028672</v>
+      </c>
+      <c r="J276" t="n">
+        <v>24.89999962</v>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
+      <c r="R276" t="inlineStr"/>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T276" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="U276" t="inlineStr"/>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>VIS-20261001115242-57EDBD</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>4872</v>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Shifa Iqbal</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>118367</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>AHMAD BROTHERS</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:52:42</t>
+        </is>
+      </c>
+      <c r="H277" t="n">
+        <v>24.8734429</v>
+      </c>
+      <c r="I277" t="n">
+        <v>67.04875699999999</v>
+      </c>
+      <c r="J277" t="n">
+        <v>17.23200035</v>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr"/>
+      <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
+      <c r="R277" t="inlineStr"/>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T277" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U277" t="inlineStr"/>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>VIS-20261001115244-97491D</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>3197</v>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Tanveer Ahmed</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>117438</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>CHOWRANGI SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:52:44</t>
+        </is>
+      </c>
+      <c r="H278" t="n">
+        <v>24.9009009</v>
+      </c>
+      <c r="I278" t="n">
+        <v>67.04333384</v>
+      </c>
+      <c r="J278" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="inlineStr"/>
+      <c r="R278" t="inlineStr"/>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T278" t="n">
+        <v>1271.5</v>
+      </c>
+      <c r="U278" t="inlineStr"/>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>VIS-20261001115306-8CCC7F</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>3297</v>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Muhammad Arif</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>120287</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>ARABIAN GASOLINE</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:53:06</t>
+        </is>
+      </c>
+      <c r="H279" t="n">
+        <v>24.84684685</v>
+      </c>
+      <c r="I279" t="n">
+        <v>67.10866453</v>
+      </c>
+      <c r="J279" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T279" t="n">
+        <v>1423.7</v>
+      </c>
+      <c r="U279" t="inlineStr"/>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>VIS-20261001115310-3B4F9F</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>4022</v>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Shakeel Ahmed Khan</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>114912</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>WESTERN TRUCKING STATION</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:53:10</t>
+        </is>
+      </c>
+      <c r="H280" t="n">
+        <v>24.8604925</v>
+      </c>
+      <c r="I280" t="n">
+        <v>67.3500624</v>
+      </c>
+      <c r="J280" t="n">
+        <v>16.28199959</v>
+      </c>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T280" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="U280" t="inlineStr"/>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>VIS-20261001115508-BBB404</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>3070</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Syed zulfiqar ali shah</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>117842</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>ASKARI FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:55:08</t>
+        </is>
+      </c>
+      <c r="H281" t="n">
+        <v>27.699055</v>
+      </c>
+      <c r="I281" t="n">
+        <v>68.8654272</v>
+      </c>
+      <c r="J281" t="n">
+        <v>17.55299949645996</v>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T281" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="U281" t="inlineStr"/>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>VIS-20261001115512-D26363</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>3287</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Asif ahmed</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>114944</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>NAFEY FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:55:12</t>
+        </is>
+      </c>
+      <c r="H282" t="n">
+        <v>24.98601897048085</v>
+      </c>
+      <c r="I282" t="n">
+        <v>67.08589140510246</v>
+      </c>
+      <c r="J282" t="n">
+        <v>45.75079422370207</v>
+      </c>
+      <c r="K282" t="inlineStr"/>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr"/>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T282" t="n">
+        <v>42.3</v>
+      </c>
+      <c r="U282" t="inlineStr"/>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>VIS-20261001115524-BA1D17</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>3970</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Zahid Hussain</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>119590</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>MOHSIN F/S</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:55:24</t>
+        </is>
+      </c>
+      <c r="H283" t="n">
+        <v>31.7630548</v>
+      </c>
+      <c r="I283" t="n">
+        <v>70.9235875</v>
+      </c>
+      <c r="J283" t="n">
+        <v>6.122000217437744</v>
+      </c>
+      <c r="K283" t="inlineStr"/>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr"/>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
+      <c r="R283" t="inlineStr"/>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T283" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="U283" t="inlineStr"/>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>VIS-20261001115552-FC7DFE</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>5048</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Abu Ali Nasr</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>101728</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>NASEER GASOLINE</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:55:52</t>
+        </is>
+      </c>
+      <c r="H284" t="n">
+        <v>24.8611731</v>
+      </c>
+      <c r="I284" t="n">
+        <v>67.0013945</v>
+      </c>
+      <c r="J284" t="n">
+        <v>26.85199928283691</v>
+      </c>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr"/>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
+      <c r="R284" t="inlineStr"/>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T284" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="U284" t="inlineStr"/>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>VIS-20261001115552-E2637E</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>2951</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>YASIR ABBAS CHUGHTAI</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>115187</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>IBRAHIM P/S</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:55:52</t>
+        </is>
+      </c>
+      <c r="H285" t="n">
+        <v>30.2205458</v>
+      </c>
+      <c r="I285" t="n">
+        <v>71.5156855</v>
+      </c>
+      <c r="J285" t="n">
+        <v>11.9060001373291</v>
+      </c>
+      <c r="K285" t="inlineStr"/>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr"/>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
+      <c r="R285" t="inlineStr"/>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T285" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="U285" t="inlineStr"/>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V273"/>
+  <autoFilter ref="A1:V285"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$285</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$291</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V285"/>
+  <dimension ref="A1:V291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,8 +437,8 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -18087,23 +18087,47 @@
       <c r="J265" t="n">
         <v>13.59000015</v>
       </c>
-      <c r="K265" t="inlineStr"/>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr"/>
-      <c r="N265" t="inlineStr"/>
-      <c r="O265" t="inlineStr"/>
-      <c r="P265" t="inlineStr"/>
-      <c r="Q265" t="inlineStr"/>
-      <c r="R265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:56:04</t>
+        </is>
+      </c>
+      <c r="L265" t="n">
+        <v>24.89132498</v>
+      </c>
+      <c r="M265" t="n">
+        <v>67.08059889</v>
+      </c>
+      <c r="N265" t="n">
+        <v>46.81295776</v>
+      </c>
+      <c r="O265" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>0:10:41</t>
+        </is>
+      </c>
+      <c r="R265" t="n">
+        <v>0.1781</v>
+      </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T265" t="n">
         <v>6</v>
       </c>
-      <c r="U265" t="inlineStr"/>
+      <c r="U265" t="n">
+        <v>18.3</v>
+      </c>
       <c r="V265" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -19081,20 +19105,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C281" t="inlineStr">
-        <is>
-          <t>3070</t>
-        </is>
+      <c r="C281" t="n">
+        <v>3070</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
           <t>Syed zulfiqar ali shah</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr">
-        <is>
-          <t>117842</t>
-        </is>
+      <c r="E281" t="n">
+        <v>117842</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -19113,7 +19133,7 @@
         <v>68.8654272</v>
       </c>
       <c r="J281" t="n">
-        <v>17.55299949645996</v>
+        <v>17.5529995</v>
       </c>
       <c r="K281" t="inlineStr"/>
       <c r="L281" t="inlineStr"/>
@@ -19149,20 +19169,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr">
-        <is>
-          <t>3287</t>
-        </is>
+      <c r="C282" t="n">
+        <v>3287</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
           <t>Asif ahmed</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr">
-        <is>
-          <t>114944</t>
-        </is>
+      <c r="E282" t="n">
+        <v>114944</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -19175,13 +19191,13 @@
         </is>
       </c>
       <c r="H282" t="n">
-        <v>24.98601897048085</v>
+        <v>24.98601897</v>
       </c>
       <c r="I282" t="n">
-        <v>67.08589140510246</v>
+        <v>67.08589141</v>
       </c>
       <c r="J282" t="n">
-        <v>45.75079422370207</v>
+        <v>45.75079422</v>
       </c>
       <c r="K282" t="inlineStr"/>
       <c r="L282" t="inlineStr"/>
@@ -19217,20 +19233,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
-        <is>
-          <t>3970</t>
-        </is>
+      <c r="C283" t="n">
+        <v>3970</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
           <t>Zahid Hussain</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>119590</t>
-        </is>
+      <c r="E283" t="n">
+        <v>119590</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -19249,7 +19261,7 @@
         <v>70.9235875</v>
       </c>
       <c r="J283" t="n">
-        <v>6.122000217437744</v>
+        <v>6.122000217</v>
       </c>
       <c r="K283" t="inlineStr"/>
       <c r="L283" t="inlineStr"/>
@@ -19285,20 +19297,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C284" t="inlineStr">
-        <is>
-          <t>5048</t>
-        </is>
+      <c r="C284" t="n">
+        <v>5048</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
           <t>Abu Ali Nasr</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr">
-        <is>
-          <t>101728</t>
-        </is>
+      <c r="E284" t="n">
+        <v>101728</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -19317,7 +19325,7 @@
         <v>67.0013945</v>
       </c>
       <c r="J284" t="n">
-        <v>26.85199928283691</v>
+        <v>26.85199928</v>
       </c>
       <c r="K284" t="inlineStr"/>
       <c r="L284" t="inlineStr"/>
@@ -19353,20 +19361,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C285" t="inlineStr">
-        <is>
-          <t>2951</t>
-        </is>
+      <c r="C285" t="n">
+        <v>2951</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
           <t>YASIR ABBAS CHUGHTAI</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr">
-        <is>
-          <t>115187</t>
-        </is>
+      <c r="E285" t="n">
+        <v>115187</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -19385,7 +19389,7 @@
         <v>71.5156855</v>
       </c>
       <c r="J285" t="n">
-        <v>11.9060001373291</v>
+        <v>11.90600014</v>
       </c>
       <c r="K285" t="inlineStr"/>
       <c r="L285" t="inlineStr"/>
@@ -19410,8 +19414,400 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>VIS-20261001115557-6E8C5C</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>4237</v>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Syed Shariq Zahoor</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>118707</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>PSO S/S 28 BHITTAI</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:55:57</t>
+        </is>
+      </c>
+      <c r="H286" t="n">
+        <v>24.8318049</v>
+      </c>
+      <c r="I286" t="n">
+        <v>67.07860290000001</v>
+      </c>
+      <c r="J286" t="n">
+        <v>23.87100029</v>
+      </c>
+      <c r="K286" t="inlineStr"/>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr"/>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
+      <c r="R286" t="inlineStr"/>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T286" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="U286" t="inlineStr"/>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>VIS-20261001115600-79DBD6</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>3713</v>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Kousar Ahsan</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>101598</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>TRICO SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:56:00</t>
+        </is>
+      </c>
+      <c r="H287" t="n">
+        <v>24.8912207</v>
+      </c>
+      <c r="I287" t="n">
+        <v>67.0807732</v>
+      </c>
+      <c r="J287" t="n">
+        <v>20.10000038</v>
+      </c>
+      <c r="K287" t="inlineStr"/>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr"/>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
+      <c r="R287" t="inlineStr"/>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T287" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U287" t="inlineStr"/>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>VIS-20261001115600-554BB4</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>4395</v>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Imran Ali</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>101683</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>JAMSHED S/S</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:56:00</t>
+        </is>
+      </c>
+      <c r="H288" t="n">
+        <v>24.9486042</v>
+      </c>
+      <c r="I288" t="n">
+        <v>67.02352329999999</v>
+      </c>
+      <c r="J288" t="n">
+        <v>32.70100021</v>
+      </c>
+      <c r="K288" t="inlineStr"/>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr"/>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
+      <c r="R288" t="inlineStr"/>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T288" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="U288" t="inlineStr"/>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>VIS-20261001115618-AD7394</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>2966</v>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Shahzaman Ali Jan Larik</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>101744</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>RASHIDI P/SER</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2026-10-01 11:56:18</t>
+        </is>
+      </c>
+      <c r="H289" t="n">
+        <v>27.5365872</v>
+      </c>
+      <c r="I289" t="n">
+        <v>68.7145527</v>
+      </c>
+      <c r="J289" t="n">
+        <v>28.10000038</v>
+      </c>
+      <c r="K289" t="inlineStr"/>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr"/>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
+      <c r="R289" t="inlineStr"/>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T289" t="n">
+        <v>18</v>
+      </c>
+      <c r="U289" t="inlineStr"/>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>VIS-20261001120209-EB8230</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>2401</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Samreen Jamali</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>101598</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>TRICO SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:02:09</t>
+        </is>
+      </c>
+      <c r="H290" t="n">
+        <v>24.8912158</v>
+      </c>
+      <c r="I290" t="n">
+        <v>67.0807776</v>
+      </c>
+      <c r="J290" t="n">
+        <v>14.44799995422363</v>
+      </c>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr"/>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
+      <c r="R290" t="inlineStr"/>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T290" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="U290" t="inlineStr"/>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>VIS-20261001120214-601A3C</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>2963</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Wakeel Ahmed</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>101598</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>TRICO SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:02:14</t>
+        </is>
+      </c>
+      <c r="H291" t="n">
+        <v>24.89131601</v>
+      </c>
+      <c r="I291" t="n">
+        <v>67.08107443999999</v>
+      </c>
+      <c r="J291" t="n">
+        <v>38.78829193115234</v>
+      </c>
+      <c r="K291" t="inlineStr"/>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr"/>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
+      <c r="R291" t="inlineStr"/>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T291" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="U291" t="inlineStr"/>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V285"/>
+  <autoFilter ref="A1:V291"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$291</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$301</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V291"/>
+  <dimension ref="A1:V301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,13 +437,13 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -671,23 +671,47 @@
       <c r="J3" t="n">
         <v>12.3039999</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:03:25</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>24.933211</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67.1551109</v>
+      </c>
+      <c r="N3" t="n">
+        <v>12.46800041</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16249.6</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Big Difference</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2:59:08</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>2.9856</v>
+      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T3" t="n">
         <v>16247</v>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>15.6</v>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>Mismatch &gt; 1.5 km</t>
@@ -16807,23 +16831,47 @@
       <c r="J245" t="n">
         <v>18.21899986</v>
       </c>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:08</t>
+        </is>
+      </c>
+      <c r="L245" t="n">
+        <v>24.9271913</v>
+      </c>
+      <c r="M245" t="n">
+        <v>67.0329515</v>
+      </c>
+      <c r="N245" t="n">
+        <v>16.41600036621094</v>
+      </c>
+      <c r="O245" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>00:46:13</t>
+        </is>
+      </c>
+      <c r="R245" t="n">
+        <v>0.7703</v>
+      </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T245" t="n">
         <v>11.4</v>
       </c>
-      <c r="U245" t="inlineStr"/>
+      <c r="U245" t="n">
+        <v>4.5</v>
+      </c>
       <c r="V245" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -17447,23 +17495,47 @@
       <c r="J255" t="n">
         <v>16.1760006</v>
       </c>
-      <c r="K255" t="inlineStr"/>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
-      <c r="N255" t="inlineStr"/>
-      <c r="O255" t="inlineStr"/>
-      <c r="P255" t="inlineStr"/>
-      <c r="Q255" t="inlineStr"/>
-      <c r="R255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:10</t>
+        </is>
+      </c>
+      <c r="L255" t="n">
+        <v>24.9272089</v>
+      </c>
+      <c r="M255" t="n">
+        <v>67.032931</v>
+      </c>
+      <c r="N255" t="n">
+        <v>17.29500007629395</v>
+      </c>
+      <c r="O255" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>00:35:18</t>
+        </is>
+      </c>
+      <c r="R255" t="n">
+        <v>0.5883</v>
+      </c>
       <c r="S255" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T255" t="n">
         <v>4.6</v>
       </c>
-      <c r="U255" t="inlineStr"/>
+      <c r="U255" t="n">
+        <v>7.3</v>
+      </c>
       <c r="V255" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -17639,23 +17711,47 @@
       <c r="J258" t="n">
         <v>33.85100174</v>
       </c>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
-      <c r="N258" t="inlineStr"/>
-      <c r="O258" t="inlineStr"/>
-      <c r="P258" t="inlineStr"/>
-      <c r="Q258" t="inlineStr"/>
-      <c r="R258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:03:12</t>
+        </is>
+      </c>
+      <c r="L258" t="n">
+        <v>24.8846779</v>
+      </c>
+      <c r="M258" t="n">
+        <v>67.0291393</v>
+      </c>
+      <c r="N258" t="n">
+        <v>20</v>
+      </c>
+      <c r="O258" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>0:23:04</t>
+        </is>
+      </c>
+      <c r="R258" t="n">
+        <v>0.3844</v>
+      </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T258" t="n">
         <v>18</v>
       </c>
-      <c r="U258" t="inlineStr"/>
+      <c r="U258" t="n">
+        <v>17.5</v>
+      </c>
       <c r="V258" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -19681,20 +19777,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr">
-        <is>
-          <t>2401</t>
-        </is>
+      <c r="C290" t="n">
+        <v>2401</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
           <t>Samreen Jamali</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>101598</t>
-        </is>
+      <c r="E290" t="n">
+        <v>101598</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -19713,7 +19805,7 @@
         <v>67.0807776</v>
       </c>
       <c r="J290" t="n">
-        <v>14.44799995422363</v>
+        <v>14.44799995</v>
       </c>
       <c r="K290" t="inlineStr"/>
       <c r="L290" t="inlineStr"/>
@@ -19749,20 +19841,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>2963</t>
-        </is>
+      <c r="C291" t="n">
+        <v>2963</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
           <t>Wakeel Ahmed</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>101598</t>
-        </is>
+      <c r="E291" t="n">
+        <v>101598</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -19781,7 +19869,7 @@
         <v>67.08107443999999</v>
       </c>
       <c r="J291" t="n">
-        <v>38.78829193115234</v>
+        <v>38.78829193</v>
       </c>
       <c r="K291" t="inlineStr"/>
       <c r="L291" t="inlineStr"/>
@@ -19806,8 +19894,660 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>VIS-20261001120231-3B3EC8</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>5253</v>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Shoaib Raza</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>119420</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>HAFIZ PS</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:02:31</t>
+        </is>
+      </c>
+      <c r="H292" t="n">
+        <v>24.9454005</v>
+      </c>
+      <c r="I292" t="n">
+        <v>67.1090129</v>
+      </c>
+      <c r="J292" t="n">
+        <v>18.12199974</v>
+      </c>
+      <c r="K292" t="inlineStr"/>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr"/>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
+      <c r="R292" t="inlineStr"/>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T292" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="U292" t="inlineStr"/>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>VIS-20261001120243-062E99</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>4898</v>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Talha Junejo</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>118850</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>MEHDI PETROLEUM SER</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:02:43</t>
+        </is>
+      </c>
+      <c r="H293" t="n">
+        <v>24.901995</v>
+      </c>
+      <c r="I293" t="n">
+        <v>67.2028672</v>
+      </c>
+      <c r="J293" t="n">
+        <v>24.89999962</v>
+      </c>
+      <c r="K293" t="inlineStr"/>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr"/>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
+      <c r="R293" t="inlineStr"/>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T293" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="U293" t="inlineStr"/>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>VIS-20261001120247-BBA5CA</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>4883</v>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Jawad Ur Rehman</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>101577</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>METRO SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:02:47</t>
+        </is>
+      </c>
+      <c r="H294" t="n">
+        <v>24.9249804</v>
+      </c>
+      <c r="I294" t="n">
+        <v>67.0309225</v>
+      </c>
+      <c r="J294" t="n">
+        <v>19.97999954</v>
+      </c>
+      <c r="K294" t="inlineStr"/>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr"/>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
+      <c r="R294" t="inlineStr"/>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T294" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="U294" t="inlineStr"/>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>VIS-20261001120259-D5B292</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>501380</v>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Muhammad Taha khan</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>101577</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>METRO SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:02:59</t>
+        </is>
+      </c>
+      <c r="H295" t="n">
+        <v>24.9250045</v>
+      </c>
+      <c r="I295" t="n">
+        <v>67.0309432</v>
+      </c>
+      <c r="J295" t="n">
+        <v>17.37999916</v>
+      </c>
+      <c r="K295" t="inlineStr"/>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr"/>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
+      <c r="R295" t="inlineStr"/>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T295" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="U295" t="inlineStr"/>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>VIS-20261001120304-F097E4</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>4200</v>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Tanveer sultana</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>101598</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>TRICO SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:03:04</t>
+        </is>
+      </c>
+      <c r="H296" t="n">
+        <v>24.8912276</v>
+      </c>
+      <c r="I296" t="n">
+        <v>67.0807782</v>
+      </c>
+      <c r="J296" t="n">
+        <v>13.81900024</v>
+      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
+      <c r="R296" t="inlineStr"/>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T296" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U296" t="inlineStr"/>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>VIS-20261001120306-6E4907</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>5088</v>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Muhammad Luqman Khalid</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>101704</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>MOON STAR SER.STATIONS</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:03:06</t>
+        </is>
+      </c>
+      <c r="H297" t="n">
+        <v>24.8515934</v>
+      </c>
+      <c r="I297" t="n">
+        <v>67.1826332</v>
+      </c>
+      <c r="J297" t="n">
+        <v>20</v>
+      </c>
+      <c r="K297" t="inlineStr"/>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr"/>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
+      <c r="R297" t="inlineStr"/>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T297" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U297" t="inlineStr"/>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>VIS-20261001120318-E8E658</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>1536</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Irfan Ali</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>116628</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>METRO SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:03:18</t>
+        </is>
+      </c>
+      <c r="H298" t="n">
+        <v>25.3758648</v>
+      </c>
+      <c r="I298" t="n">
+        <v>68.3574442</v>
+      </c>
+      <c r="J298" t="n">
+        <v>10.58199978</v>
+      </c>
+      <c r="K298" t="inlineStr"/>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr"/>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
+      <c r="R298" t="inlineStr"/>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T298" t="n">
+        <v>1406.2</v>
+      </c>
+      <c r="U298" t="inlineStr"/>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>VIS-20261001120800-C8D886</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>4897</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Amjad Ashraf</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>114944</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>NAFEY FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:00</t>
+        </is>
+      </c>
+      <c r="H299" t="n">
+        <v>24.9860725</v>
+      </c>
+      <c r="I299" t="n">
+        <v>67.0863461</v>
+      </c>
+      <c r="J299" t="n">
+        <v>7.926000118255615</v>
+      </c>
+      <c r="K299" t="inlineStr"/>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr"/>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr"/>
+      <c r="R299" t="inlineStr"/>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T299" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="U299" t="inlineStr"/>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>VIS-20261001120808-518A6D</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>4287</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>sajid ahmed</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>101545</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>RAZA PETROL SERVICE</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:08</t>
+        </is>
+      </c>
+      <c r="H300" t="n">
+        <v>24.8844781</v>
+      </c>
+      <c r="I300" t="n">
+        <v>67.0291797</v>
+      </c>
+      <c r="J300" t="n">
+        <v>26.7180004119873</v>
+      </c>
+      <c r="K300" t="inlineStr"/>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr"/>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
+      <c r="R300" t="inlineStr"/>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T300" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="U300" t="inlineStr"/>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>VIS-20261001120810-5A5878</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>1810</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>M khalid Khan lodhi</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>114944</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>NAFEY FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:10</t>
+        </is>
+      </c>
+      <c r="H301" t="n">
+        <v>24.99099099099099</v>
+      </c>
+      <c r="I301" t="n">
+        <v>67.0916901822235</v>
+      </c>
+      <c r="J301" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K301" t="inlineStr"/>
+      <c r="L301" t="inlineStr"/>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr"/>
+      <c r="O301" t="inlineStr"/>
+      <c r="P301" t="inlineStr"/>
+      <c r="Q301" t="inlineStr"/>
+      <c r="R301" t="inlineStr"/>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T301" t="n">
+        <v>775.1</v>
+      </c>
+      <c r="U301" t="inlineStr"/>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V291"/>
+  <autoFilter ref="A1:V301"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$302</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V301"/>
+  <dimension ref="A1:V302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2026-10-01 12:08:10</t>
+          <t>2026-10-01 12:08:17</t>
         </is>
       </c>
       <c r="L255" t="n">
@@ -17519,11 +17519,11 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>00:35:18</t>
+          <t>00:35:25</t>
         </is>
       </c>
       <c r="R255" t="n">
-        <v>0.5883</v>
+        <v>0.5903</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -20191,23 +20191,47 @@
       <c r="J296" t="n">
         <v>13.81900024</v>
       </c>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
-      <c r="O296" t="inlineStr"/>
-      <c r="P296" t="inlineStr"/>
-      <c r="Q296" t="inlineStr"/>
-      <c r="R296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:21</t>
+        </is>
+      </c>
+      <c r="L296" t="n">
+        <v>24.8912197</v>
+      </c>
+      <c r="M296" t="n">
+        <v>67.0807547</v>
+      </c>
+      <c r="N296" t="n">
+        <v>27.69599914550781</v>
+      </c>
+      <c r="O296" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>00:05:17</t>
+        </is>
+      </c>
+      <c r="R296" t="n">
+        <v>0.0881</v>
+      </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T296" t="n">
         <v>4.8</v>
       </c>
-      <c r="U296" t="inlineStr"/>
+      <c r="U296" t="n">
+        <v>5.8</v>
+      </c>
       <c r="V296" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -20546,8 +20570,76 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>VIS-20261001120822-9463F3</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>5071</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Muhammad Shahzaib</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>101704</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>MOON STAR SER.STATIONS</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:22</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>24.8515921</v>
+      </c>
+      <c r="I302" t="n">
+        <v>67.18264189999999</v>
+      </c>
+      <c r="J302" t="n">
+        <v>20</v>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="inlineStr"/>
+      <c r="R302" t="inlineStr"/>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T302" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="U302" t="inlineStr"/>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V301"/>
+  <autoFilter ref="A1:V302"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$302</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$301</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V302"/>
+  <dimension ref="A1:V301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2026-10-01 12:08:17</t>
+          <t>2026-10-01 12:08:10</t>
         </is>
       </c>
       <c r="L255" t="n">
@@ -17519,11 +17519,11 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>00:35:25</t>
+          <t>00:35:18</t>
         </is>
       </c>
       <c r="R255" t="n">
-        <v>0.5903</v>
+        <v>0.5883</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -20191,47 +20191,23 @@
       <c r="J296" t="n">
         <v>13.81900024</v>
       </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>2026-10-01 12:08:21</t>
-        </is>
-      </c>
-      <c r="L296" t="n">
-        <v>24.8912197</v>
-      </c>
-      <c r="M296" t="n">
-        <v>67.0807547</v>
-      </c>
-      <c r="N296" t="n">
-        <v>27.69599914550781</v>
-      </c>
-      <c r="O296" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P296" t="inlineStr">
-        <is>
-          <t>Almost Same</t>
-        </is>
-      </c>
-      <c r="Q296" t="inlineStr">
-        <is>
-          <t>00:05:17</t>
-        </is>
-      </c>
-      <c r="R296" t="n">
-        <v>0.0881</v>
-      </c>
+      <c r="K296" t="inlineStr"/>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr"/>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
+      <c r="R296" t="inlineStr"/>
       <c r="S296" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="T296" t="n">
         <v>4.8</v>
       </c>
-      <c r="U296" t="n">
-        <v>5.8</v>
-      </c>
+      <c r="U296" t="inlineStr"/>
       <c r="V296" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -20570,76 +20546,8 @@
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>VIS-20261001120822-9463F3</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>5071</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>Muhammad Shahzaib</t>
-        </is>
-      </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>101704</t>
-        </is>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>MOON STAR SER.STATIONS</t>
-        </is>
-      </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>2026-10-01 12:08:22</t>
-        </is>
-      </c>
-      <c r="H302" t="n">
-        <v>24.8515921</v>
-      </c>
-      <c r="I302" t="n">
-        <v>67.18264189999999</v>
-      </c>
-      <c r="J302" t="n">
-        <v>20</v>
-      </c>
-      <c r="K302" t="inlineStr"/>
-      <c r="L302" t="inlineStr"/>
-      <c r="M302" t="inlineStr"/>
-      <c r="N302" t="inlineStr"/>
-      <c r="O302" t="inlineStr"/>
-      <c r="P302" t="inlineStr"/>
-      <c r="Q302" t="inlineStr"/>
-      <c r="R302" t="inlineStr"/>
-      <c r="S302" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="T302" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="U302" t="inlineStr"/>
-      <c r="V302" t="inlineStr">
-        <is>
-          <t>Within 1.5 km</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V302"/>
+  <autoFilter ref="A1:V301"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$308</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V301"/>
+  <dimension ref="A1:V308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,13 +437,13 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -16843,7 +16843,7 @@
         <v>67.0329515</v>
       </c>
       <c r="N245" t="n">
-        <v>16.41600036621094</v>
+        <v>16.41600037</v>
       </c>
       <c r="O245" t="n">
         <v>7.8</v>
@@ -16855,7 +16855,7 @@
       </c>
       <c r="Q245" t="inlineStr">
         <is>
-          <t>00:46:13</t>
+          <t>0:46:13</t>
         </is>
       </c>
       <c r="R245" t="n">
@@ -17497,7 +17497,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2026-10-01 12:08:10</t>
+          <t>2026-10-01 12:08:17</t>
         </is>
       </c>
       <c r="L255" t="n">
@@ -17507,7 +17507,7 @@
         <v>67.032931</v>
       </c>
       <c r="N255" t="n">
-        <v>17.29500007629395</v>
+        <v>17.29500008</v>
       </c>
       <c r="O255" t="n">
         <v>6.9</v>
@@ -17519,11 +17519,11 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>00:35:18</t>
+          <t>0:35:25</t>
         </is>
       </c>
       <c r="R255" t="n">
-        <v>0.5883</v>
+        <v>0.5903</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -19807,23 +19807,47 @@
       <c r="J290" t="n">
         <v>14.44799995</v>
       </c>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
-      <c r="N290" t="inlineStr"/>
-      <c r="O290" t="inlineStr"/>
-      <c r="P290" t="inlineStr"/>
-      <c r="Q290" t="inlineStr"/>
-      <c r="R290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:12:09</t>
+        </is>
+      </c>
+      <c r="L290" t="n">
+        <v>24.8912206</v>
+      </c>
+      <c r="M290" t="n">
+        <v>67.08077780000001</v>
+      </c>
+      <c r="N290" t="n">
+        <v>14.38199997</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>0:10:00</t>
+        </is>
+      </c>
+      <c r="R290" t="n">
+        <v>0.1667</v>
+      </c>
       <c r="S290" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T290" t="n">
         <v>6.1</v>
       </c>
-      <c r="U290" t="inlineStr"/>
+      <c r="U290" t="n">
+        <v>5.5</v>
+      </c>
       <c r="V290" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -20127,23 +20151,47 @@
       <c r="J295" t="n">
         <v>17.37999916</v>
       </c>
-      <c r="K295" t="inlineStr"/>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr"/>
-      <c r="N295" t="inlineStr"/>
-      <c r="O295" t="inlineStr"/>
-      <c r="P295" t="inlineStr"/>
-      <c r="Q295" t="inlineStr"/>
-      <c r="R295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:48</t>
+        </is>
+      </c>
+      <c r="L295" t="n">
+        <v>24.9249904</v>
+      </c>
+      <c r="M295" t="n">
+        <v>67.03093029999999</v>
+      </c>
+      <c r="N295" t="n">
+        <v>27.375</v>
+      </c>
+      <c r="O295" t="n">
+        <v>2</v>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>0:05:49</t>
+        </is>
+      </c>
+      <c r="R295" t="n">
+        <v>0.0969</v>
+      </c>
       <c r="S295" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T295" t="n">
         <v>16.9</v>
       </c>
-      <c r="U295" t="inlineStr"/>
+      <c r="U295" t="n">
+        <v>15.1</v>
+      </c>
       <c r="V295" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -20191,23 +20239,47 @@
       <c r="J296" t="n">
         <v>13.81900024</v>
       </c>
-      <c r="K296" t="inlineStr"/>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
-      <c r="N296" t="inlineStr"/>
-      <c r="O296" t="inlineStr"/>
-      <c r="P296" t="inlineStr"/>
-      <c r="Q296" t="inlineStr"/>
-      <c r="R296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:21</t>
+        </is>
+      </c>
+      <c r="L296" t="n">
+        <v>24.8912197</v>
+      </c>
+      <c r="M296" t="n">
+        <v>67.0807547</v>
+      </c>
+      <c r="N296" t="n">
+        <v>27.69599915</v>
+      </c>
+      <c r="O296" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>0:05:17</t>
+        </is>
+      </c>
+      <c r="R296" t="n">
+        <v>0.0881</v>
+      </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T296" t="n">
         <v>4.8</v>
       </c>
-      <c r="U296" t="inlineStr"/>
+      <c r="U296" t="n">
+        <v>5.8</v>
+      </c>
       <c r="V296" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -20353,20 +20425,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>4897</t>
-        </is>
+      <c r="C299" t="n">
+        <v>4897</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
           <t>Amjad Ashraf</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>114944</t>
-        </is>
+      <c r="E299" t="n">
+        <v>114944</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -20385,7 +20453,7 @@
         <v>67.0863461</v>
       </c>
       <c r="J299" t="n">
-        <v>7.926000118255615</v>
+        <v>7.926000118</v>
       </c>
       <c r="K299" t="inlineStr"/>
       <c r="L299" t="inlineStr"/>
@@ -20421,20 +20489,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>4287</t>
-        </is>
+      <c r="C300" t="n">
+        <v>4287</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
           <t>sajid ahmed</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>101545</t>
-        </is>
+      <c r="E300" t="n">
+        <v>101545</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -20453,7 +20517,7 @@
         <v>67.0291797</v>
       </c>
       <c r="J300" t="n">
-        <v>26.7180004119873</v>
+        <v>26.71800041</v>
       </c>
       <c r="K300" t="inlineStr"/>
       <c r="L300" t="inlineStr"/>
@@ -20489,20 +20553,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
+      <c r="C301" t="n">
+        <v>1810</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
           <t>M khalid Khan lodhi</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>114944</t>
-        </is>
+      <c r="E301" t="n">
+        <v>114944</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -20515,10 +20575,10 @@
         </is>
       </c>
       <c r="H301" t="n">
-        <v>24.99099099099099</v>
+        <v>24.99099099</v>
       </c>
       <c r="I301" t="n">
-        <v>67.0916901822235</v>
+        <v>67.09169018</v>
       </c>
       <c r="J301" t="n">
         <v>2000</v>
@@ -20546,8 +20606,460 @@
         </is>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>VIS-20261001120822-9463F3</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>5071</v>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Muhammad Shahzaib</t>
+        </is>
+      </c>
+      <c r="E302" t="n">
+        <v>101704</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>MOON STAR SER.STATIONS</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:22</t>
+        </is>
+      </c>
+      <c r="H302" t="n">
+        <v>24.8515921</v>
+      </c>
+      <c r="I302" t="n">
+        <v>67.18264189999999</v>
+      </c>
+      <c r="J302" t="n">
+        <v>20</v>
+      </c>
+      <c r="K302" t="inlineStr"/>
+      <c r="L302" t="inlineStr"/>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr"/>
+      <c r="O302" t="inlineStr"/>
+      <c r="P302" t="inlineStr"/>
+      <c r="Q302" t="inlineStr"/>
+      <c r="R302" t="inlineStr"/>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T302" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="U302" t="inlineStr"/>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>VIS-20261001120828-6293E6</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>5073</v>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Syed Talha Qamar</t>
+        </is>
+      </c>
+      <c r="E303" t="n">
+        <v>120293</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>KISWA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:08:28</t>
+        </is>
+      </c>
+      <c r="H303" t="n">
+        <v>24.9332115</v>
+      </c>
+      <c r="I303" t="n">
+        <v>67.1551116</v>
+      </c>
+      <c r="J303" t="n">
+        <v>12.67399979</v>
+      </c>
+      <c r="K303" t="inlineStr"/>
+      <c r="L303" t="inlineStr"/>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr"/>
+      <c r="O303" t="inlineStr"/>
+      <c r="P303" t="inlineStr"/>
+      <c r="Q303" t="inlineStr"/>
+      <c r="R303" t="inlineStr"/>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T303" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="U303" t="inlineStr"/>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>VIS-20261001121222-3E55B3</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>4991</v>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Muhammad Hafeez Ur Rehman</t>
+        </is>
+      </c>
+      <c r="E304" t="n">
+        <v>117965</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>SAM PETROLEUM 2</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:12:22</t>
+        </is>
+      </c>
+      <c r="H304" t="n">
+        <v>24.8388618</v>
+      </c>
+      <c r="I304" t="n">
+        <v>67.25904540000001</v>
+      </c>
+      <c r="J304" t="n">
+        <v>20</v>
+      </c>
+      <c r="K304" t="inlineStr"/>
+      <c r="L304" t="inlineStr"/>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr"/>
+      <c r="O304" t="inlineStr"/>
+      <c r="P304" t="inlineStr"/>
+      <c r="Q304" t="inlineStr"/>
+      <c r="R304" t="inlineStr"/>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T304" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="U304" t="inlineStr"/>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>VIS-20261001121226-FCC2BE</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>5107</v>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Muhammad Azam</t>
+        </is>
+      </c>
+      <c r="E305" t="n">
+        <v>116207</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>AL BADAR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:12:26</t>
+        </is>
+      </c>
+      <c r="H305" t="n">
+        <v>24.8843183</v>
+      </c>
+      <c r="I305" t="n">
+        <v>66.9767583</v>
+      </c>
+      <c r="J305" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K305" t="inlineStr"/>
+      <c r="L305" t="inlineStr"/>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr"/>
+      <c r="O305" t="inlineStr"/>
+      <c r="P305" t="inlineStr"/>
+      <c r="Q305" t="inlineStr"/>
+      <c r="R305" t="inlineStr"/>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T305" t="n">
+        <v>21</v>
+      </c>
+      <c r="U305" t="inlineStr"/>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>VIS-20261001121241-F5613D</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>5104</v>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Muhammad Yasir Iqbal</t>
+        </is>
+      </c>
+      <c r="E306" t="n">
+        <v>119420</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>HAFIZ PS</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:12:41</t>
+        </is>
+      </c>
+      <c r="H306" t="n">
+        <v>24.9454092</v>
+      </c>
+      <c r="I306" t="n">
+        <v>67.10901699999999</v>
+      </c>
+      <c r="J306" t="n">
+        <v>20</v>
+      </c>
+      <c r="K306" t="inlineStr"/>
+      <c r="L306" t="inlineStr"/>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr"/>
+      <c r="O306" t="inlineStr"/>
+      <c r="P306" t="inlineStr"/>
+      <c r="Q306" t="inlineStr"/>
+      <c r="R306" t="inlineStr"/>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T306" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="U306" t="inlineStr"/>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>VIS-20261001121256-9AA165</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>4029</v>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Sohail Ahmed</t>
+        </is>
+      </c>
+      <c r="E307" t="n">
+        <v>101598</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>TRICO SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:12:56</t>
+        </is>
+      </c>
+      <c r="H307" t="n">
+        <v>24.8912184</v>
+      </c>
+      <c r="I307" t="n">
+        <v>67.0807693</v>
+      </c>
+      <c r="J307" t="n">
+        <v>15.21199989</v>
+      </c>
+      <c r="K307" t="inlineStr"/>
+      <c r="L307" t="inlineStr"/>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr"/>
+      <c r="O307" t="inlineStr"/>
+      <c r="P307" t="inlineStr"/>
+      <c r="Q307" t="inlineStr"/>
+      <c r="R307" t="inlineStr"/>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T307" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U307" t="inlineStr"/>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>VIS-20261001121413-7986D6</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>3511</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Muhammad Ishaque</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>101594</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>NAWAZ SERVICE STN</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:14:13</t>
+        </is>
+      </c>
+      <c r="H308" t="n">
+        <v>24.8530818</v>
+      </c>
+      <c r="I308" t="n">
+        <v>66.9940455</v>
+      </c>
+      <c r="J308" t="n">
+        <v>13.25899982452393</v>
+      </c>
+      <c r="K308" t="inlineStr"/>
+      <c r="L308" t="inlineStr"/>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr"/>
+      <c r="O308" t="inlineStr"/>
+      <c r="P308" t="inlineStr"/>
+      <c r="Q308" t="inlineStr"/>
+      <c r="R308" t="inlineStr"/>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T308" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="U308" t="inlineStr"/>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V301"/>
+  <autoFilter ref="A1:V308"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$308</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$318</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V308"/>
+  <dimension ref="A1:V318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,11 @@
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -20711,23 +20711,47 @@
       <c r="J303" t="n">
         <v>12.67399979</v>
       </c>
-      <c r="K303" t="inlineStr"/>
-      <c r="L303" t="inlineStr"/>
-      <c r="M303" t="inlineStr"/>
-      <c r="N303" t="inlineStr"/>
-      <c r="O303" t="inlineStr"/>
-      <c r="P303" t="inlineStr"/>
-      <c r="Q303" t="inlineStr"/>
-      <c r="R303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:20:27</t>
+        </is>
+      </c>
+      <c r="L303" t="n">
+        <v>24.9332136</v>
+      </c>
+      <c r="M303" t="n">
+        <v>67.15510190000001</v>
+      </c>
+      <c r="N303" t="n">
+        <v>17.4069995880127</v>
+      </c>
+      <c r="O303" t="n">
+        <v>1</v>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>00:11:59</t>
+        </is>
+      </c>
+      <c r="R303" t="n">
+        <v>0.1997</v>
+      </c>
       <c r="S303" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T303" t="n">
         <v>15.7</v>
       </c>
-      <c r="U303" t="inlineStr"/>
+      <c r="U303" t="n">
+        <v>16.4</v>
+      </c>
       <c r="V303" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -20967,23 +20991,47 @@
       <c r="J307" t="n">
         <v>15.21199989</v>
       </c>
-      <c r="K307" t="inlineStr"/>
-      <c r="L307" t="inlineStr"/>
-      <c r="M307" t="inlineStr"/>
-      <c r="N307" t="inlineStr"/>
-      <c r="O307" t="inlineStr"/>
-      <c r="P307" t="inlineStr"/>
-      <c r="Q307" t="inlineStr"/>
-      <c r="R307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:14:15</t>
+        </is>
+      </c>
+      <c r="L307" t="n">
+        <v>24.8912882</v>
+      </c>
+      <c r="M307" t="n">
+        <v>67.08076490000001</v>
+      </c>
+      <c r="N307" t="n">
+        <v>21.53300095</v>
+      </c>
+      <c r="O307" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>0:01:19</t>
+        </is>
+      </c>
+      <c r="R307" t="n">
+        <v>0.0219</v>
+      </c>
       <c r="S307" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T307" t="n">
         <v>5.7</v>
       </c>
-      <c r="U307" t="inlineStr"/>
+      <c r="U307" t="n">
+        <v>2.1</v>
+      </c>
       <c r="V307" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -21001,20 +21049,16 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
+      <c r="C308" t="n">
+        <v>3511</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
           <t>Muhammad Ishaque</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>101594</t>
-        </is>
+      <c r="E308" t="n">
+        <v>101594</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -21033,7 +21077,7 @@
         <v>66.9940455</v>
       </c>
       <c r="J308" t="n">
-        <v>13.25899982452393</v>
+        <v>13.25899982</v>
       </c>
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
@@ -21058,8 +21102,696 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>VIS-20261001121419-83FDEA</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>5007</v>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Mehran Munir</t>
+        </is>
+      </c>
+      <c r="E309" t="n">
+        <v>101683</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>JAMSHED S/S</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:14:19</t>
+        </is>
+      </c>
+      <c r="H309" t="n">
+        <v>24.9204286</v>
+      </c>
+      <c r="I309" t="n">
+        <v>67.0314479</v>
+      </c>
+      <c r="J309" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="K309" t="inlineStr"/>
+      <c r="L309" t="inlineStr"/>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr"/>
+      <c r="O309" t="inlineStr"/>
+      <c r="P309" t="inlineStr"/>
+      <c r="Q309" t="inlineStr"/>
+      <c r="R309" t="inlineStr"/>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T309" t="n">
+        <v>3207.7</v>
+      </c>
+      <c r="U309" t="inlineStr"/>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>VIS-20261001121420-EC9CC5</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>5249</v>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Wali Hashmi</t>
+        </is>
+      </c>
+      <c r="E310" t="n">
+        <v>116207</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>AL BADAR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:14:20</t>
+        </is>
+      </c>
+      <c r="H310" t="n">
+        <v>24.884006</v>
+      </c>
+      <c r="I310" t="n">
+        <v>66.97683309999999</v>
+      </c>
+      <c r="J310" t="n">
+        <v>11.73499966</v>
+      </c>
+      <c r="K310" t="inlineStr"/>
+      <c r="L310" t="inlineStr"/>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr"/>
+      <c r="O310" t="inlineStr"/>
+      <c r="P310" t="inlineStr"/>
+      <c r="Q310" t="inlineStr"/>
+      <c r="R310" t="inlineStr"/>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T310" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="U310" t="inlineStr"/>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>VIS-20261001121424-E3F845</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>710005</v>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Farhan Saeed Khalili</t>
+        </is>
+      </c>
+      <c r="E311" t="n">
+        <v>116207</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>AL BADAR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:14:24</t>
+        </is>
+      </c>
+      <c r="H311" t="n">
+        <v>24.88441555</v>
+      </c>
+      <c r="I311" t="n">
+        <v>66.97681871</v>
+      </c>
+      <c r="J311" t="n">
+        <v>24.58197445</v>
+      </c>
+      <c r="K311" t="inlineStr"/>
+      <c r="L311" t="inlineStr"/>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr"/>
+      <c r="O311" t="inlineStr"/>
+      <c r="P311" t="inlineStr"/>
+      <c r="Q311" t="inlineStr"/>
+      <c r="R311" t="inlineStr"/>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T311" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="U311" t="inlineStr"/>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>VIS-20261001121427-21C839</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>5244</v>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Fahad Ali</t>
+        </is>
+      </c>
+      <c r="E312" t="n">
+        <v>101722</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>PSO S/S 7 (A.B GHAZI)</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:14:27</t>
+        </is>
+      </c>
+      <c r="H312" t="n">
+        <v>24.8080945</v>
+      </c>
+      <c r="I312" t="n">
+        <v>67.03691910000001</v>
+      </c>
+      <c r="J312" t="n">
+        <v>7.730000019</v>
+      </c>
+      <c r="K312" t="inlineStr"/>
+      <c r="L312" t="inlineStr"/>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr"/>
+      <c r="O312" t="inlineStr"/>
+      <c r="P312" t="inlineStr"/>
+      <c r="Q312" t="inlineStr"/>
+      <c r="R312" t="inlineStr"/>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T312" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="U312" t="inlineStr"/>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>VIS-20261001121714-30B451</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>3254</v>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Naweed Masood Ali</t>
+        </is>
+      </c>
+      <c r="E313" t="n">
+        <v>116207</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>AL BADAR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:17:14</t>
+        </is>
+      </c>
+      <c r="H313" t="n">
+        <v>24.8845347</v>
+      </c>
+      <c r="I313" t="n">
+        <v>66.9764845</v>
+      </c>
+      <c r="J313" t="n">
+        <v>37.5719986</v>
+      </c>
+      <c r="K313" t="inlineStr"/>
+      <c r="L313" t="inlineStr"/>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr"/>
+      <c r="O313" t="inlineStr"/>
+      <c r="P313" t="inlineStr"/>
+      <c r="Q313" t="inlineStr"/>
+      <c r="R313" t="inlineStr"/>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T313" t="n">
+        <v>57.6</v>
+      </c>
+      <c r="U313" t="inlineStr"/>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>VIS-20261001121717-87CDD9</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>5227</v>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Hassan Ali</t>
+        </is>
+      </c>
+      <c r="E314" t="n">
+        <v>116442</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>SAMCO POL F/S</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:17:17</t>
+        </is>
+      </c>
+      <c r="H314" t="n">
+        <v>33.6340875</v>
+      </c>
+      <c r="I314" t="n">
+        <v>73.0765954</v>
+      </c>
+      <c r="J314" t="n">
+        <v>11.81499958</v>
+      </c>
+      <c r="K314" t="inlineStr"/>
+      <c r="L314" t="inlineStr"/>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr"/>
+      <c r="O314" t="inlineStr"/>
+      <c r="P314" t="inlineStr"/>
+      <c r="Q314" t="inlineStr"/>
+      <c r="R314" t="inlineStr"/>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T314" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="U314" t="inlineStr"/>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>VIS-20261001121722-F7E00B</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>4024</v>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Muhammad Saqib</t>
+        </is>
+      </c>
+      <c r="E315" t="n">
+        <v>120293</v>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>KISWA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:17:22</t>
+        </is>
+      </c>
+      <c r="H315" t="n">
+        <v>24.9332083</v>
+      </c>
+      <c r="I315" t="n">
+        <v>67.1551683</v>
+      </c>
+      <c r="J315" t="n">
+        <v>19.52799988</v>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:18:53</t>
+        </is>
+      </c>
+      <c r="L315" t="n">
+        <v>24.9332122</v>
+      </c>
+      <c r="M315" t="n">
+        <v>67.1551296</v>
+      </c>
+      <c r="N315" t="n">
+        <v>11.51099968</v>
+      </c>
+      <c r="O315" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>0:01:31</t>
+        </is>
+      </c>
+      <c r="R315" t="n">
+        <v>0.0253</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T315" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="U315" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>VIS-20261001121725-A470B7</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>4864</v>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Mohsin Hassan</t>
+        </is>
+      </c>
+      <c r="E316" t="n">
+        <v>117973</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>PSO S/S 76 (SHEERIN)</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:17:25</t>
+        </is>
+      </c>
+      <c r="H316" t="n">
+        <v>24.8191462</v>
+      </c>
+      <c r="I316" t="n">
+        <v>66.9942274</v>
+      </c>
+      <c r="J316" t="n">
+        <v>20</v>
+      </c>
+      <c r="K316" t="inlineStr"/>
+      <c r="L316" t="inlineStr"/>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr"/>
+      <c r="O316" t="inlineStr"/>
+      <c r="P316" t="inlineStr"/>
+      <c r="Q316" t="inlineStr"/>
+      <c r="R316" t="inlineStr"/>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T316" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="U316" t="inlineStr"/>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>VIS-20261001121726-A512B7</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>4472</v>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Ansar Iqbal</t>
+        </is>
+      </c>
+      <c r="E317" t="n">
+        <v>118005</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>KK GASOLINE</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:17:26</t>
+        </is>
+      </c>
+      <c r="H317" t="n">
+        <v>31.8379837</v>
+      </c>
+      <c r="I317" t="n">
+        <v>70.9122507</v>
+      </c>
+      <c r="J317" t="n">
+        <v>33.02500153</v>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:18:53</t>
+        </is>
+      </c>
+      <c r="L317" t="n">
+        <v>31.8377657</v>
+      </c>
+      <c r="M317" t="n">
+        <v>70.91220250000001</v>
+      </c>
+      <c r="N317" t="n">
+        <v>29.64699936</v>
+      </c>
+      <c r="O317" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>0:01:27</t>
+        </is>
+      </c>
+      <c r="R317" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T317" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="U317" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>VIS-20261001121843-9289A8</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>4867</v>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Sayyam Dost</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>118707</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>PSO S/S 28 BHITTAI</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:18:43</t>
+        </is>
+      </c>
+      <c r="H318" t="n">
+        <v>24.8317843</v>
+      </c>
+      <c r="I318" t="n">
+        <v>67.0786335</v>
+      </c>
+      <c r="J318" t="n">
+        <v>13.65699959</v>
+      </c>
+      <c r="K318" t="inlineStr"/>
+      <c r="L318" t="inlineStr"/>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
+      <c r="O318" t="inlineStr"/>
+      <c r="P318" t="inlineStr"/>
+      <c r="Q318" t="inlineStr"/>
+      <c r="R318" t="inlineStr"/>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T318" t="n">
+        <v>7</v>
+      </c>
+      <c r="U318" t="inlineStr"/>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V308"/>
+  <autoFilter ref="A1:V318"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$318</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$338</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V318"/>
+  <dimension ref="A1:V338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -437,13 +437,13 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -20723,7 +20723,7 @@
         <v>67.15510190000001</v>
       </c>
       <c r="N303" t="n">
-        <v>17.4069995880127</v>
+        <v>17.40699959</v>
       </c>
       <c r="O303" t="n">
         <v>1</v>
@@ -20735,7 +20735,7 @@
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>00:11:59</t>
+          <t>0:11:59</t>
         </is>
       </c>
       <c r="R303" t="n">
@@ -21143,23 +21143,47 @@
       <c r="J309" t="n">
         <v>36.5</v>
       </c>
-      <c r="K309" t="inlineStr"/>
-      <c r="L309" t="inlineStr"/>
-      <c r="M309" t="inlineStr"/>
-      <c r="N309" t="inlineStr"/>
-      <c r="O309" t="inlineStr"/>
-      <c r="P309" t="inlineStr"/>
-      <c r="Q309" t="inlineStr"/>
-      <c r="R309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:24:13</t>
+        </is>
+      </c>
+      <c r="L309" t="n">
+        <v>24.881099</v>
+      </c>
+      <c r="M309" t="n">
+        <v>67.03817979999999</v>
+      </c>
+      <c r="N309" t="n">
+        <v>13.06299973</v>
+      </c>
+      <c r="O309" t="n">
+        <v>4425.6</v>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>Big Difference</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>0:09:54</t>
+        </is>
+      </c>
+      <c r="R309" t="n">
+        <v>0.165</v>
+      </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T309" t="n">
         <v>3207.7</v>
       </c>
-      <c r="U309" t="inlineStr"/>
+      <c r="U309" t="n">
+        <v>7625.8</v>
+      </c>
       <c r="V309" t="inlineStr">
         <is>
           <t>Mismatch &gt; 1.5 km</t>
@@ -21790,8 +21814,1324 @@
         </is>
       </c>
     </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>VIS-20261001122041-DC1500</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>4396</v>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Sultan salahuddin isfandyar</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>119420</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>HAFIZ PS</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:20:41</t>
+        </is>
+      </c>
+      <c r="H319" t="n">
+        <v>24.9454056</v>
+      </c>
+      <c r="I319" t="n">
+        <v>67.1090106</v>
+      </c>
+      <c r="J319" t="n">
+        <v>12.5539999</v>
+      </c>
+      <c r="K319" t="inlineStr"/>
+      <c r="L319" t="inlineStr"/>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr"/>
+      <c r="O319" t="inlineStr"/>
+      <c r="P319" t="inlineStr"/>
+      <c r="Q319" t="inlineStr"/>
+      <c r="R319" t="inlineStr"/>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T319" t="n">
+        <v>43</v>
+      </c>
+      <c r="U319" t="inlineStr"/>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>VIS-20261001122047-579C9B</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>501445</v>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Raaziya Majeed</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>118352</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>FAISAL SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:20:47</t>
+        </is>
+      </c>
+      <c r="H320" t="n">
+        <v>24.9282862</v>
+      </c>
+      <c r="I320" t="n">
+        <v>67.0629395</v>
+      </c>
+      <c r="J320" t="n">
+        <v>24.24500084</v>
+      </c>
+      <c r="K320" t="inlineStr"/>
+      <c r="L320" t="inlineStr"/>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr"/>
+      <c r="O320" t="inlineStr"/>
+      <c r="P320" t="inlineStr"/>
+      <c r="Q320" t="inlineStr"/>
+      <c r="R320" t="inlineStr"/>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T320" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="U320" t="inlineStr"/>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>VIS-20261001122051-A0E3B5</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>3932</v>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>DORIS DIAS</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>119962</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>STANDARD SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:20:51</t>
+        </is>
+      </c>
+      <c r="H321" t="n">
+        <v>24.8606348</v>
+      </c>
+      <c r="I321" t="n">
+        <v>67.0663977</v>
+      </c>
+      <c r="J321" t="n">
+        <v>29.39800072</v>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:21:28</t>
+        </is>
+      </c>
+      <c r="L321" t="n">
+        <v>24.8606251</v>
+      </c>
+      <c r="M321" t="n">
+        <v>67.0664161</v>
+      </c>
+      <c r="N321" t="n">
+        <v>25.73699951</v>
+      </c>
+      <c r="O321" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>0:00:37</t>
+        </is>
+      </c>
+      <c r="R321" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T321" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="U321" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>VIS-20261001122052-03F3F0</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>5090</v>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Shamim</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>114944</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>NAFEY FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:20:52</t>
+        </is>
+      </c>
+      <c r="H322" t="n">
+        <v>24.9864986</v>
+      </c>
+      <c r="I322" t="n">
+        <v>67.0852067</v>
+      </c>
+      <c r="J322" t="n">
+        <v>17.42499924</v>
+      </c>
+      <c r="K322" t="inlineStr"/>
+      <c r="L322" t="inlineStr"/>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr"/>
+      <c r="O322" t="inlineStr"/>
+      <c r="P322" t="inlineStr"/>
+      <c r="Q322" t="inlineStr"/>
+      <c r="R322" t="inlineStr"/>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T322" t="n">
+        <v>123.9</v>
+      </c>
+      <c r="U322" t="inlineStr"/>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>VIS-20261001122053-E948BC</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>2938</v>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Ali Husnain</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>110239</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>ALPHA P/S</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:20:53</t>
+        </is>
+      </c>
+      <c r="H323" t="n">
+        <v>24.95864911</v>
+      </c>
+      <c r="I323" t="n">
+        <v>67.07529128</v>
+      </c>
+      <c r="J323" t="n">
+        <v>24.78225318</v>
+      </c>
+      <c r="K323" t="inlineStr"/>
+      <c r="L323" t="inlineStr"/>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr"/>
+      <c r="O323" t="inlineStr"/>
+      <c r="P323" t="inlineStr"/>
+      <c r="Q323" t="inlineStr"/>
+      <c r="R323" t="inlineStr"/>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T323" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="U323" t="inlineStr"/>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>VIS-20261001122055-D6D031</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>4027</v>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Ifraheem Ullah Khan Lodhi</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>119574</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>KAARSAZ PETROLEUM SERVICES</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:20:55</t>
+        </is>
+      </c>
+      <c r="H324" t="n">
+        <v>24.8740655</v>
+      </c>
+      <c r="I324" t="n">
+        <v>67.09501109999999</v>
+      </c>
+      <c r="J324" t="n">
+        <v>12.46500015</v>
+      </c>
+      <c r="K324" t="inlineStr"/>
+      <c r="L324" t="inlineStr"/>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr"/>
+      <c r="O324" t="inlineStr"/>
+      <c r="P324" t="inlineStr"/>
+      <c r="Q324" t="inlineStr"/>
+      <c r="R324" t="inlineStr"/>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T324" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="U324" t="inlineStr"/>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>VIS-20261001122056-C38424</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>4596</v>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Zahid Iqbal</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>115764</v>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>NOOR FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:20:56</t>
+        </is>
+      </c>
+      <c r="H325" t="n">
+        <v>32.9712207</v>
+      </c>
+      <c r="I325" t="n">
+        <v>73.69094370000001</v>
+      </c>
+      <c r="J325" t="n">
+        <v>25.26399994</v>
+      </c>
+      <c r="K325" t="inlineStr"/>
+      <c r="L325" t="inlineStr"/>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr"/>
+      <c r="O325" t="inlineStr"/>
+      <c r="P325" t="inlineStr"/>
+      <c r="Q325" t="inlineStr"/>
+      <c r="R325" t="inlineStr"/>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T325" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U325" t="inlineStr"/>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>VIS-20261001122106-2B7711</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>5265</v>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Ali Hassan</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>111578</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>MM II PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:21:06</t>
+        </is>
+      </c>
+      <c r="H326" t="n">
+        <v>24.78672351</v>
+      </c>
+      <c r="I326" t="n">
+        <v>67.34523704</v>
+      </c>
+      <c r="J326" t="n">
+        <v>38.94321906</v>
+      </c>
+      <c r="K326" t="inlineStr"/>
+      <c r="L326" t="inlineStr"/>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr"/>
+      <c r="O326" t="inlineStr"/>
+      <c r="P326" t="inlineStr"/>
+      <c r="Q326" t="inlineStr"/>
+      <c r="R326" t="inlineStr"/>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T326" t="n">
+        <v>11</v>
+      </c>
+      <c r="U326" t="inlineStr"/>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>VIS-20261001122108-887CDD</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>4370</v>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Fawad Ahmad Pirzada</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>118319</v>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>SHAH RUKAN -E-ALAM G/S</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:21:08</t>
+        </is>
+      </c>
+      <c r="H327" t="n">
+        <v>30.18018018</v>
+      </c>
+      <c r="I327" t="n">
+        <v>71.51357374</v>
+      </c>
+      <c r="J327" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K327" t="inlineStr"/>
+      <c r="L327" t="inlineStr"/>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr"/>
+      <c r="O327" t="inlineStr"/>
+      <c r="P327" t="inlineStr"/>
+      <c r="Q327" t="inlineStr"/>
+      <c r="R327" t="inlineStr"/>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T327" t="n">
+        <v>769.5</v>
+      </c>
+      <c r="U327" t="inlineStr"/>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>VIS-20261001122123-960F71</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>3969</v>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Syed Muhammad Ali Shah</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>119962</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>STANDARD SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:21:23</t>
+        </is>
+      </c>
+      <c r="H328" t="n">
+        <v>24.8606384</v>
+      </c>
+      <c r="I328" t="n">
+        <v>67.0664136</v>
+      </c>
+      <c r="J328" t="n">
+        <v>24.25099945</v>
+      </c>
+      <c r="K328" t="inlineStr"/>
+      <c r="L328" t="inlineStr"/>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr"/>
+      <c r="O328" t="inlineStr"/>
+      <c r="P328" t="inlineStr"/>
+      <c r="Q328" t="inlineStr"/>
+      <c r="R328" t="inlineStr"/>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T328" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="U328" t="inlineStr"/>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>VIS-20261001122303-1E0F6A</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>4939</v>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Muhammad Zubair</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>101660</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>SADIQ GASOLINE</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:23:03</t>
+        </is>
+      </c>
+      <c r="H329" t="n">
+        <v>24.935945</v>
+      </c>
+      <c r="I329" t="n">
+        <v>67.07559759999999</v>
+      </c>
+      <c r="J329" t="n">
+        <v>16.5909996</v>
+      </c>
+      <c r="K329" t="inlineStr"/>
+      <c r="L329" t="inlineStr"/>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr"/>
+      <c r="O329" t="inlineStr"/>
+      <c r="P329" t="inlineStr"/>
+      <c r="Q329" t="inlineStr"/>
+      <c r="R329" t="inlineStr"/>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T329" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="U329" t="inlineStr"/>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>VIS-20261001122435-43CCBB</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>3247</v>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Hafiz Manzoor Ahmad</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>118319</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>SHAH RUKAN -E-ALAM G/S</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:24:35</t>
+        </is>
+      </c>
+      <c r="H330" t="n">
+        <v>30.1852214</v>
+      </c>
+      <c r="I330" t="n">
+        <v>71.5112695</v>
+      </c>
+      <c r="J330" t="n">
+        <v>20</v>
+      </c>
+      <c r="K330" t="inlineStr"/>
+      <c r="L330" t="inlineStr"/>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr"/>
+      <c r="O330" t="inlineStr"/>
+      <c r="P330" t="inlineStr"/>
+      <c r="Q330" t="inlineStr"/>
+      <c r="R330" t="inlineStr"/>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T330" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="U330" t="inlineStr"/>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>VIS-20261001122451-BF4752</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>4550</v>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Rizwan Ahmed</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>119261</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>PSO S/S 85 (EASTERN</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:24:51</t>
+        </is>
+      </c>
+      <c r="H331" t="n">
+        <v>24.9193154</v>
+      </c>
+      <c r="I331" t="n">
+        <v>67.00356840000001</v>
+      </c>
+      <c r="J331" t="n">
+        <v>20</v>
+      </c>
+      <c r="K331" t="inlineStr"/>
+      <c r="L331" t="inlineStr"/>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr"/>
+      <c r="O331" t="inlineStr"/>
+      <c r="P331" t="inlineStr"/>
+      <c r="Q331" t="inlineStr"/>
+      <c r="R331" t="inlineStr"/>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T331" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="U331" t="inlineStr"/>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>VIS-20261001122511-F3FD37</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>4207</v>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Fahim Ahmed Bughio</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>101722</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>PSO S/S 7 (A.B GHAZI)</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:25:11</t>
+        </is>
+      </c>
+      <c r="H332" t="n">
+        <v>24.80801097</v>
+      </c>
+      <c r="I332" t="n">
+        <v>67.03689642000001</v>
+      </c>
+      <c r="J332" t="n">
+        <v>9.756512257000001</v>
+      </c>
+      <c r="K332" t="inlineStr"/>
+      <c r="L332" t="inlineStr"/>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr"/>
+      <c r="O332" t="inlineStr"/>
+      <c r="P332" t="inlineStr"/>
+      <c r="Q332" t="inlineStr"/>
+      <c r="R332" t="inlineStr"/>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T332" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="U332" t="inlineStr"/>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>VIS-20261001122512-8C24F6</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>11412</v>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Khizer Ahmed Khan</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>118707</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>PSO S/S 28 BHITTAI</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:25:12</t>
+        </is>
+      </c>
+      <c r="H333" t="n">
+        <v>24.83173896</v>
+      </c>
+      <c r="I333" t="n">
+        <v>67.07851483</v>
+      </c>
+      <c r="J333" t="n">
+        <v>12.78669893</v>
+      </c>
+      <c r="K333" t="inlineStr"/>
+      <c r="L333" t="inlineStr"/>
+      <c r="M333" t="inlineStr"/>
+      <c r="N333" t="inlineStr"/>
+      <c r="O333" t="inlineStr"/>
+      <c r="P333" t="inlineStr"/>
+      <c r="Q333" t="inlineStr"/>
+      <c r="R333" t="inlineStr"/>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T333" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="U333" t="inlineStr"/>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>VIS-20261001122513-28283F</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>2750</v>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Faisal Mehmood Abbasi</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>112126</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>BOSTAN PETROLEUM</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:25:13</t>
+        </is>
+      </c>
+      <c r="H334" t="n">
+        <v>33.5684574</v>
+      </c>
+      <c r="I334" t="n">
+        <v>73.1555711</v>
+      </c>
+      <c r="J334" t="n">
+        <v>16.32699966</v>
+      </c>
+      <c r="K334" t="inlineStr"/>
+      <c r="L334" t="inlineStr"/>
+      <c r="M334" t="inlineStr"/>
+      <c r="N334" t="inlineStr"/>
+      <c r="O334" t="inlineStr"/>
+      <c r="P334" t="inlineStr"/>
+      <c r="Q334" t="inlineStr"/>
+      <c r="R334" t="inlineStr"/>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T334" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="U334" t="inlineStr"/>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>VIS-20261001122521-63740D</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>4585</v>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Syed Asim Abbas</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>118277</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>KHAWAJA ZAFAR P/S</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:25:21</t>
+        </is>
+      </c>
+      <c r="H335" t="n">
+        <v>31.5019678</v>
+      </c>
+      <c r="I335" t="n">
+        <v>74.28108279999999</v>
+      </c>
+      <c r="J335" t="n">
+        <v>21.7859993</v>
+      </c>
+      <c r="K335" t="inlineStr"/>
+      <c r="L335" t="inlineStr"/>
+      <c r="M335" t="inlineStr"/>
+      <c r="N335" t="inlineStr"/>
+      <c r="O335" t="inlineStr"/>
+      <c r="P335" t="inlineStr"/>
+      <c r="Q335" t="inlineStr"/>
+      <c r="R335" t="inlineStr"/>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T335" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U335" t="inlineStr"/>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>VIS-20261001122746-7AAE04</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>501428</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Haseeb effendi</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>117793</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Q.STAR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:27:46</t>
+        </is>
+      </c>
+      <c r="H336" t="n">
+        <v>24.85293122266564</v>
+      </c>
+      <c r="I336" t="n">
+        <v>67.05273690380395</v>
+      </c>
+      <c r="J336" t="n">
+        <v>32.75284808940749</v>
+      </c>
+      <c r="K336" t="inlineStr"/>
+      <c r="L336" t="inlineStr"/>
+      <c r="M336" t="inlineStr"/>
+      <c r="N336" t="inlineStr"/>
+      <c r="O336" t="inlineStr"/>
+      <c r="P336" t="inlineStr"/>
+      <c r="Q336" t="inlineStr"/>
+      <c r="R336" t="inlineStr"/>
+      <c r="S336" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T336" t="n">
+        <v>36</v>
+      </c>
+      <c r="U336" t="inlineStr"/>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>VIS-20261001122746-A5F0F3</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>5051</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Muhammad Arslan</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>102943</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>KHURRAM PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:27:46</t>
+        </is>
+      </c>
+      <c r="H337" t="n">
+        <v>29.3812863</v>
+      </c>
+      <c r="I337" t="n">
+        <v>71.73543119999999</v>
+      </c>
+      <c r="J337" t="n">
+        <v>19.9689998626709</v>
+      </c>
+      <c r="K337" t="inlineStr"/>
+      <c r="L337" t="inlineStr"/>
+      <c r="M337" t="inlineStr"/>
+      <c r="N337" t="inlineStr"/>
+      <c r="O337" t="inlineStr"/>
+      <c r="P337" t="inlineStr"/>
+      <c r="Q337" t="inlineStr"/>
+      <c r="R337" t="inlineStr"/>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T337" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="U337" t="inlineStr"/>
+      <c r="V337" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>VIS-20261001122748-5F0385</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>501444</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Husnain Azhar</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>119574</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>KAARSAZ PETROLEUM SERVICES</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:27:48</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>24.8740586</v>
+      </c>
+      <c r="I338" t="n">
+        <v>67.0950204</v>
+      </c>
+      <c r="J338" t="n">
+        <v>41.13199996948242</v>
+      </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr"/>
+      <c r="P338" t="inlineStr"/>
+      <c r="Q338" t="inlineStr"/>
+      <c r="R338" t="inlineStr"/>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T338" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="U338" t="inlineStr"/>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V318"/>
+  <autoFilter ref="A1:V338"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$338</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$337</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V338"/>
+  <dimension ref="A1:V337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -23062,76 +23062,8 @@
         </is>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>VIS-20261001122748-5F0385</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>501444</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>Husnain Azhar</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>119574</t>
-        </is>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>KAARSAZ PETROLEUM SERVICES</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>2026-10-01 12:27:48</t>
-        </is>
-      </c>
-      <c r="H338" t="n">
-        <v>24.8740586</v>
-      </c>
-      <c r="I338" t="n">
-        <v>67.0950204</v>
-      </c>
-      <c r="J338" t="n">
-        <v>41.13199996948242</v>
-      </c>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
-      <c r="M338" t="inlineStr"/>
-      <c r="N338" t="inlineStr"/>
-      <c r="O338" t="inlineStr"/>
-      <c r="P338" t="inlineStr"/>
-      <c r="Q338" t="inlineStr"/>
-      <c r="R338" t="inlineStr"/>
-      <c r="S338" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="T338" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="U338" t="inlineStr"/>
-      <c r="V338" t="inlineStr">
-        <is>
-          <t>Within 1.5 km</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:V338"/>
+  <autoFilter ref="A1:V337"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$337</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$379</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V337"/>
+  <dimension ref="A1:V379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -441,9 +441,9 @@
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="17" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -4743,23 +4743,47 @@
       <c r="J61" t="n">
         <v>20</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:33</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>30.1728246</v>
+      </c>
+      <c r="M61" t="n">
+        <v>71.5072943</v>
+      </c>
+      <c r="N61" t="n">
+        <v>100</v>
+      </c>
+      <c r="O61" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>01:44:27</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>1.7408</v>
+      </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T61" t="n">
         <v>22.8</v>
       </c>
-      <c r="U61" t="inlineStr"/>
+      <c r="U61" t="n">
+        <v>66.7</v>
+      </c>
       <c r="V61" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -12111,23 +12135,47 @@
       <c r="J172" t="n">
         <v>42.89699936</v>
       </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:09</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>24.867585</v>
+      </c>
+      <c r="M172" t="n">
+        <v>67.08357650000001</v>
+      </c>
+      <c r="N172" t="n">
+        <v>28.26600074768066</v>
+      </c>
+      <c r="O172" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>01:29:10</t>
+        </is>
+      </c>
+      <c r="R172" t="n">
+        <v>1.4861</v>
+      </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T172" t="n">
         <v>178.8</v>
       </c>
-      <c r="U172" t="inlineStr"/>
+      <c r="U172" t="n">
+        <v>207.8</v>
+      </c>
       <c r="V172" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -12559,23 +12607,47 @@
       <c r="J179" t="n">
         <v>20</v>
       </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:12</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>24.8670867</v>
+      </c>
+      <c r="M179" t="n">
+        <v>67.0838129</v>
+      </c>
+      <c r="N179" t="n">
+        <v>16.76600074768066</v>
+      </c>
+      <c r="O179" t="n">
+        <v>3</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>01:29:32</t>
+        </is>
+      </c>
+      <c r="R179" t="n">
+        <v>1.4922</v>
+      </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T179" t="n">
         <v>175.3</v>
       </c>
-      <c r="U179" t="inlineStr"/>
+      <c r="U179" t="n">
+        <v>176</v>
+      </c>
       <c r="V179" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -12815,23 +12887,47 @@
       <c r="J183" t="n">
         <v>10.42599964</v>
       </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:37</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>24.86708</v>
+      </c>
+      <c r="M183" t="n">
+        <v>67.08382</v>
+      </c>
+      <c r="N183" t="n">
+        <v>17.19700050354004</v>
+      </c>
+      <c r="O183" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>01:28:28</t>
+        </is>
+      </c>
+      <c r="R183" t="n">
+        <v>1.4744</v>
+      </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T183" t="n">
         <v>179.4</v>
       </c>
-      <c r="U183" t="inlineStr"/>
+      <c r="U183" t="n">
+        <v>175.2</v>
+      </c>
       <c r="V183" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -13135,23 +13231,47 @@
       <c r="J188" t="n">
         <v>13.1619997</v>
       </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:17</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>31.437799</v>
+      </c>
+      <c r="M188" t="n">
+        <v>73.0914537</v>
+      </c>
+      <c r="N188" t="n">
+        <v>15.41199970245361</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>01:27:32</t>
+        </is>
+      </c>
+      <c r="R188" t="n">
+        <v>1.4589</v>
+      </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T188" t="n">
         <v>27.8</v>
       </c>
-      <c r="U188" t="inlineStr"/>
+      <c r="U188" t="n">
+        <v>28.1</v>
+      </c>
       <c r="V188" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -13391,23 +13511,47 @@
       <c r="J192" t="n">
         <v>9.31400013</v>
       </c>
-      <c r="K192" t="inlineStr"/>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32:00</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>31.4378072</v>
+      </c>
+      <c r="M192" t="n">
+        <v>73.09144929999999</v>
+      </c>
+      <c r="N192" t="n">
+        <v>14.22700023651123</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>01:28:09</t>
+        </is>
+      </c>
+      <c r="R192" t="n">
+        <v>1.4692</v>
+      </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T192" t="n">
         <v>27</v>
       </c>
-      <c r="U192" t="inlineStr"/>
+      <c r="U192" t="n">
+        <v>27.5</v>
+      </c>
       <c r="V192" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -19487,23 +19631,47 @@
       <c r="J285" t="n">
         <v>11.90600014</v>
       </c>
-      <c r="K285" t="inlineStr"/>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
-      <c r="N285" t="inlineStr"/>
-      <c r="O285" t="inlineStr"/>
-      <c r="P285" t="inlineStr"/>
-      <c r="Q285" t="inlineStr"/>
-      <c r="R285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:12</t>
+        </is>
+      </c>
+      <c r="L285" t="n">
+        <v>30.2205081</v>
+      </c>
+      <c r="M285" t="n">
+        <v>71.5156928</v>
+      </c>
+      <c r="N285" t="n">
+        <v>11.54399967193604</v>
+      </c>
+      <c r="O285" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>00:32:20</t>
+        </is>
+      </c>
+      <c r="R285" t="n">
+        <v>0.5389</v>
+      </c>
       <c r="S285" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T285" t="n">
         <v>12.7</v>
       </c>
-      <c r="U285" t="inlineStr"/>
+      <c r="U285" t="n">
+        <v>14.1</v>
+      </c>
       <c r="V285" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -22327,23 +22495,47 @@
       <c r="J326" t="n">
         <v>38.94321906</v>
       </c>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
-      <c r="M326" t="inlineStr"/>
-      <c r="N326" t="inlineStr"/>
-      <c r="O326" t="inlineStr"/>
-      <c r="P326" t="inlineStr"/>
-      <c r="Q326" t="inlineStr"/>
-      <c r="R326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:02</t>
+        </is>
+      </c>
+      <c r="L326" t="n">
+        <v>24.78672318975915</v>
+      </c>
+      <c r="M326" t="n">
+        <v>67.34525773723347</v>
+      </c>
+      <c r="N326" t="n">
+        <v>29.94402033400452</v>
+      </c>
+      <c r="O326" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>00:06:56</t>
+        </is>
+      </c>
+      <c r="R326" t="n">
+        <v>0.1156</v>
+      </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T326" t="n">
         <v>11</v>
       </c>
-      <c r="U326" t="inlineStr"/>
+      <c r="U326" t="n">
+        <v>9.699999999999999</v>
+      </c>
       <c r="V326" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -22391,23 +22583,47 @@
       <c r="J327" t="n">
         <v>2000</v>
       </c>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr"/>
-      <c r="N327" t="inlineStr"/>
-      <c r="O327" t="inlineStr"/>
-      <c r="P327" t="inlineStr"/>
-      <c r="Q327" t="inlineStr"/>
-      <c r="R327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:29</t>
+        </is>
+      </c>
+      <c r="L327" t="n">
+        <v>30.18018018018018</v>
+      </c>
+      <c r="M327" t="n">
+        <v>71.51357374207015</v>
+      </c>
+      <c r="N327" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O327" t="n">
+        <v>0</v>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>00:08:21</t>
+        </is>
+      </c>
+      <c r="R327" t="n">
+        <v>0.1392</v>
+      </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T327" t="n">
         <v>769.5</v>
       </c>
-      <c r="U327" t="inlineStr"/>
+      <c r="U327" t="n">
+        <v>769.5</v>
+      </c>
       <c r="V327" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -22903,23 +23119,47 @@
       <c r="J335" t="n">
         <v>21.7859993</v>
       </c>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" t="inlineStr"/>
-      <c r="N335" t="inlineStr"/>
-      <c r="O335" t="inlineStr"/>
-      <c r="P335" t="inlineStr"/>
-      <c r="Q335" t="inlineStr"/>
-      <c r="R335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:48</t>
+        </is>
+      </c>
+      <c r="L335" t="n">
+        <v>31.5019634</v>
+      </c>
+      <c r="M335" t="n">
+        <v>74.2810956</v>
+      </c>
+      <c r="N335" t="n">
+        <v>27.18499946594238</v>
+      </c>
+      <c r="O335" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>00:03:27</t>
+        </is>
+      </c>
+      <c r="R335" t="n">
+        <v>0.0575</v>
+      </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T335" t="n">
         <v>3.9</v>
       </c>
-      <c r="U335" t="inlineStr"/>
+      <c r="U335" t="n">
+        <v>2.8</v>
+      </c>
       <c r="V335" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -23039,31 +23279,3151 @@
       <c r="J337" t="n">
         <v>19.9689998626709</v>
       </c>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
-      <c r="M337" t="inlineStr"/>
-      <c r="N337" t="inlineStr"/>
-      <c r="O337" t="inlineStr"/>
-      <c r="P337" t="inlineStr"/>
-      <c r="Q337" t="inlineStr"/>
-      <c r="R337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:27</t>
+        </is>
+      </c>
+      <c r="L337" t="n">
+        <v>29.3812986</v>
+      </c>
+      <c r="M337" t="n">
+        <v>71.7354531</v>
+      </c>
+      <c r="N337" t="n">
+        <v>15.48999977111816</v>
+      </c>
+      <c r="O337" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>00:00:41</t>
+        </is>
+      </c>
+      <c r="R337" t="n">
+        <v>0.0114</v>
+      </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T337" t="n">
         <v>16.6</v>
       </c>
-      <c r="U337" t="inlineStr"/>
+      <c r="U337" t="n">
+        <v>19.1</v>
+      </c>
       <c r="V337" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
         </is>
       </c>
     </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>VIS-20261001122748-5F0385</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>501444</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Husnain Azhar</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>119574</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>KAARSAZ PETROLEUM SERVICES</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:27:48</t>
+        </is>
+      </c>
+      <c r="H338" t="n">
+        <v>24.8740586</v>
+      </c>
+      <c r="I338" t="n">
+        <v>67.0950204</v>
+      </c>
+      <c r="J338" t="n">
+        <v>41.13199996948242</v>
+      </c>
+      <c r="K338" t="inlineStr"/>
+      <c r="L338" t="inlineStr"/>
+      <c r="M338" t="inlineStr"/>
+      <c r="N338" t="inlineStr"/>
+      <c r="O338" t="inlineStr"/>
+      <c r="P338" t="inlineStr"/>
+      <c r="Q338" t="inlineStr"/>
+      <c r="R338" t="inlineStr"/>
+      <c r="S338" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T338" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="U338" t="inlineStr"/>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>VIS-20261001122810-B8F7F1</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>3637</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Abdul Mannan</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>115569</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>MIAN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:10</t>
+        </is>
+      </c>
+      <c r="H339" t="n">
+        <v>33.7640148</v>
+      </c>
+      <c r="I339" t="n">
+        <v>72.7251801</v>
+      </c>
+      <c r="J339" t="n">
+        <v>20</v>
+      </c>
+      <c r="K339" t="inlineStr"/>
+      <c r="L339" t="inlineStr"/>
+      <c r="M339" t="inlineStr"/>
+      <c r="N339" t="inlineStr"/>
+      <c r="O339" t="inlineStr"/>
+      <c r="P339" t="inlineStr"/>
+      <c r="Q339" t="inlineStr"/>
+      <c r="R339" t="inlineStr"/>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T339" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="U339" t="inlineStr"/>
+      <c r="V339" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>VIS-20261001122812-CA9C1E</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>501427</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Muhammad Hassan Shirazi</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>116973</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>PINE FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:12</t>
+        </is>
+      </c>
+      <c r="H340" t="n">
+        <v>31.4095548</v>
+      </c>
+      <c r="I340" t="n">
+        <v>74.2492142</v>
+      </c>
+      <c r="J340" t="n">
+        <v>11.84700012207031</v>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:24</t>
+        </is>
+      </c>
+      <c r="L340" t="n">
+        <v>31.4095424</v>
+      </c>
+      <c r="M340" t="n">
+        <v>74.24925570000001</v>
+      </c>
+      <c r="N340" t="n">
+        <v>11.63599967956543</v>
+      </c>
+      <c r="O340" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>00:00:12</t>
+        </is>
+      </c>
+      <c r="R340" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="S340" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T340" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U340" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>VIS-20261001122815-22C438</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>4139</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Muhammad Amir Shabbir</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>117538</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>REHMAN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:15</t>
+        </is>
+      </c>
+      <c r="H341" t="n">
+        <v>31.6000838</v>
+      </c>
+      <c r="I341" t="n">
+        <v>74.2996083</v>
+      </c>
+      <c r="J341" t="n">
+        <v>36.97800064086914</v>
+      </c>
+      <c r="K341" t="inlineStr"/>
+      <c r="L341" t="inlineStr"/>
+      <c r="M341" t="inlineStr"/>
+      <c r="N341" t="inlineStr"/>
+      <c r="O341" t="inlineStr"/>
+      <c r="P341" t="inlineStr"/>
+      <c r="Q341" t="inlineStr"/>
+      <c r="R341" t="inlineStr"/>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T341" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="U341" t="inlineStr"/>
+      <c r="V341" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>VIS-20261001122819-1737E3</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>4768</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Toseef Alam</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>103148</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>KASHIF FILL. STATION</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:19</t>
+        </is>
+      </c>
+      <c r="H342" t="n">
+        <v>31.5215775</v>
+      </c>
+      <c r="I342" t="n">
+        <v>73.11132739999999</v>
+      </c>
+      <c r="J342" t="n">
+        <v>9</v>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:58</t>
+        </is>
+      </c>
+      <c r="L342" t="n">
+        <v>31.5215364</v>
+      </c>
+      <c r="M342" t="n">
+        <v>73.1114104</v>
+      </c>
+      <c r="N342" t="n">
+        <v>35</v>
+      </c>
+      <c r="O342" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>00:00:39</t>
+        </is>
+      </c>
+      <c r="R342" t="n">
+        <v>0.0108</v>
+      </c>
+      <c r="S342" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T342" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="U342" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>VIS-20261001122822-DB22A4</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>501451</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Naveed ullah</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>101704</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>MOON STAR SER.STATIONS</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:22</t>
+        </is>
+      </c>
+      <c r="H343" t="n">
+        <v>24.8515899</v>
+      </c>
+      <c r="I343" t="n">
+        <v>67.18262679999999</v>
+      </c>
+      <c r="J343" t="n">
+        <v>19.85400009155273</v>
+      </c>
+      <c r="K343" t="inlineStr"/>
+      <c r="L343" t="inlineStr"/>
+      <c r="M343" t="inlineStr"/>
+      <c r="N343" t="inlineStr"/>
+      <c r="O343" t="inlineStr"/>
+      <c r="P343" t="inlineStr"/>
+      <c r="Q343" t="inlineStr"/>
+      <c r="R343" t="inlineStr"/>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T343" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="U343" t="inlineStr"/>
+      <c r="V343" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>VIS-20261001122831-481162</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>3666</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Muhammad Faizan Ejaz</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>118118</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>A. K FUEL</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:31</t>
+        </is>
+      </c>
+      <c r="H344" t="n">
+        <v>31.525759</v>
+      </c>
+      <c r="I344" t="n">
+        <v>74.284853</v>
+      </c>
+      <c r="J344" t="n">
+        <v>14.88199996948242</v>
+      </c>
+      <c r="K344" t="inlineStr"/>
+      <c r="L344" t="inlineStr"/>
+      <c r="M344" t="inlineStr"/>
+      <c r="N344" t="inlineStr"/>
+      <c r="O344" t="inlineStr"/>
+      <c r="P344" t="inlineStr"/>
+      <c r="Q344" t="inlineStr"/>
+      <c r="R344" t="inlineStr"/>
+      <c r="S344" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T344" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="U344" t="inlineStr"/>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>VIS-20261001122836-E3AA2C</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Deedar Ali</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>109868</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>GHOUSIA F/S</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:36</t>
+        </is>
+      </c>
+      <c r="H345" t="n">
+        <v>27.8544003</v>
+      </c>
+      <c r="I345" t="n">
+        <v>69.10695629999999</v>
+      </c>
+      <c r="J345" t="n">
+        <v>18.21599960327148</v>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:52</t>
+        </is>
+      </c>
+      <c r="L345" t="n">
+        <v>27.8543947</v>
+      </c>
+      <c r="M345" t="n">
+        <v>69.1069416</v>
+      </c>
+      <c r="N345" t="n">
+        <v>18.1870002746582</v>
+      </c>
+      <c r="O345" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>00:00:16</t>
+        </is>
+      </c>
+      <c r="R345" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T345" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U345" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V345" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>VIS-20261001122856-1DED3E</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>4391</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Mushaf Badar</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>101722</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>PSO S/S 7 (A.B GHAZI)</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:28:56</t>
+        </is>
+      </c>
+      <c r="H346" t="n">
+        <v>24.8081349</v>
+      </c>
+      <c r="I346" t="n">
+        <v>67.03701340000001</v>
+      </c>
+      <c r="J346" t="n">
+        <v>19.16900062561035</v>
+      </c>
+      <c r="K346" t="inlineStr"/>
+      <c r="L346" t="inlineStr"/>
+      <c r="M346" t="inlineStr"/>
+      <c r="N346" t="inlineStr"/>
+      <c r="O346" t="inlineStr"/>
+      <c r="P346" t="inlineStr"/>
+      <c r="Q346" t="inlineStr"/>
+      <c r="R346" t="inlineStr"/>
+      <c r="S346" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T346" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="U346" t="inlineStr"/>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>VIS-20261001122902-63564C</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>5231</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Muhammad Saad</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>111578</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>MM II PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:02</t>
+        </is>
+      </c>
+      <c r="H347" t="n">
+        <v>24.7866468</v>
+      </c>
+      <c r="I347" t="n">
+        <v>67.34521549999999</v>
+      </c>
+      <c r="J347" t="n">
+        <v>16.98299980163574</v>
+      </c>
+      <c r="K347" t="inlineStr"/>
+      <c r="L347" t="inlineStr"/>
+      <c r="M347" t="inlineStr"/>
+      <c r="N347" t="inlineStr"/>
+      <c r="O347" t="inlineStr"/>
+      <c r="P347" t="inlineStr"/>
+      <c r="Q347" t="inlineStr"/>
+      <c r="R347" t="inlineStr"/>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T347" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="U347" t="inlineStr"/>
+      <c r="V347" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>VIS-20261001122916-DDF411</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>720011</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Shehzad khan</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>119506</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>HUR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:16</t>
+        </is>
+      </c>
+      <c r="H348" t="n">
+        <v>24.8199743</v>
+      </c>
+      <c r="I348" t="n">
+        <v>67.1510847</v>
+      </c>
+      <c r="J348" t="n">
+        <v>17.43000030517578</v>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:59</t>
+        </is>
+      </c>
+      <c r="L348" t="n">
+        <v>24.8199753</v>
+      </c>
+      <c r="M348" t="n">
+        <v>67.15109699999999</v>
+      </c>
+      <c r="N348" t="n">
+        <v>11.81400012969971</v>
+      </c>
+      <c r="O348" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>00:00:43</t>
+        </is>
+      </c>
+      <c r="R348" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="S348" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T348" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="U348" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>VIS-20261001122929-0CCCCF</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Tanveer Abbas Khan</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>118005</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>KK GASOLINE</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:29</t>
+        </is>
+      </c>
+      <c r="H349" t="n">
+        <v>31.8377461</v>
+      </c>
+      <c r="I349" t="n">
+        <v>70.9122022</v>
+      </c>
+      <c r="J349" t="n">
+        <v>26.5049991607666</v>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:36</t>
+        </is>
+      </c>
+      <c r="L349" t="n">
+        <v>31.8377552</v>
+      </c>
+      <c r="M349" t="n">
+        <v>70.9121986</v>
+      </c>
+      <c r="N349" t="n">
+        <v>44.2760009765625</v>
+      </c>
+      <c r="O349" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>00:00:07</t>
+        </is>
+      </c>
+      <c r="R349" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T349" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="U349" t="n">
+        <v>26</v>
+      </c>
+      <c r="V349" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>VIS-20261001122931-55F1D0</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>5262</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Fahad Pervaiz</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>103241</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>KHAN BROS.F/STN.</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:31</t>
+        </is>
+      </c>
+      <c r="H350" t="n">
+        <v>31.3906652550173</v>
+      </c>
+      <c r="I350" t="n">
+        <v>74.26105872214579</v>
+      </c>
+      <c r="J350" t="n">
+        <v>21.99960956186194</v>
+      </c>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="M350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
+      <c r="O350" t="inlineStr"/>
+      <c r="P350" t="inlineStr"/>
+      <c r="Q350" t="inlineStr"/>
+      <c r="R350" t="inlineStr"/>
+      <c r="S350" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T350" t="n">
+        <v>46.2</v>
+      </c>
+      <c r="U350" t="inlineStr"/>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>VIS-20261001122933-B29429</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>5172</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Raza</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>110523</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>SAFA ENTERPRISES</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:33</t>
+        </is>
+      </c>
+      <c r="H351" t="n">
+        <v>24.84069720370643</v>
+      </c>
+      <c r="I351" t="n">
+        <v>67.09821811713095</v>
+      </c>
+      <c r="J351" t="n">
+        <v>18.52443093848551</v>
+      </c>
+      <c r="K351" t="inlineStr"/>
+      <c r="L351" t="inlineStr"/>
+      <c r="M351" t="inlineStr"/>
+      <c r="N351" t="inlineStr"/>
+      <c r="O351" t="inlineStr"/>
+      <c r="P351" t="inlineStr"/>
+      <c r="Q351" t="inlineStr"/>
+      <c r="R351" t="inlineStr"/>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T351" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="U351" t="inlineStr"/>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>VIS-20261001122936-AEDD57</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Osama Sabir</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>118707</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>PSO S/S 28 BHITTAI</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:36</t>
+        </is>
+      </c>
+      <c r="H352" t="n">
+        <v>24.83173590584631</v>
+      </c>
+      <c r="I352" t="n">
+        <v>67.07852028685659</v>
+      </c>
+      <c r="J352" t="n">
+        <v>13.35765884278658</v>
+      </c>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr"/>
+      <c r="M352" t="inlineStr"/>
+      <c r="N352" t="inlineStr"/>
+      <c r="O352" t="inlineStr"/>
+      <c r="P352" t="inlineStr"/>
+      <c r="Q352" t="inlineStr"/>
+      <c r="R352" t="inlineStr"/>
+      <c r="S352" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T352" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="U352" t="inlineStr"/>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>VIS-20261001122936-5F8EF6</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>501406</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Sarmad Malik</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>119664</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>PSO S/S 52</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:36</t>
+        </is>
+      </c>
+      <c r="H353" t="n">
+        <v>31.490117</v>
+      </c>
+      <c r="I353" t="n">
+        <v>74.3116733</v>
+      </c>
+      <c r="J353" t="n">
+        <v>13.17599964141846</v>
+      </c>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr"/>
+      <c r="M353" t="inlineStr"/>
+      <c r="N353" t="inlineStr"/>
+      <c r="O353" t="inlineStr"/>
+      <c r="P353" t="inlineStr"/>
+      <c r="Q353" t="inlineStr"/>
+      <c r="R353" t="inlineStr"/>
+      <c r="S353" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T353" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="U353" t="inlineStr"/>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>VIS-20261001122947-D215B2</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>2366</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>RAJA M faisal</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>119136</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>SUN FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:47</t>
+        </is>
+      </c>
+      <c r="H354" t="n">
+        <v>31.61070897722099</v>
+      </c>
+      <c r="I354" t="n">
+        <v>74.42373966997791</v>
+      </c>
+      <c r="J354" t="n">
+        <v>28.27318116056879</v>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:56</t>
+        </is>
+      </c>
+      <c r="L354" t="n">
+        <v>31.61070900557002</v>
+      </c>
+      <c r="M354" t="n">
+        <v>74.42373980733447</v>
+      </c>
+      <c r="N354" t="n">
+        <v>28.22180989374531</v>
+      </c>
+      <c r="O354" t="n">
+        <v>0</v>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>00:00:09</t>
+        </is>
+      </c>
+      <c r="R354" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T354" t="n">
+        <v>31887.3</v>
+      </c>
+      <c r="U354" t="n">
+        <v>31887.3</v>
+      </c>
+      <c r="V354" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>VIS-20261001122951-ECC07E</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>2864</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Danish Obaid</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>112839</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>SHAHEEN SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:51</t>
+        </is>
+      </c>
+      <c r="H355" t="n">
+        <v>24.88695204274522</v>
+      </c>
+      <c r="I355" t="n">
+        <v>67.145825334677</v>
+      </c>
+      <c r="J355" t="n">
+        <v>11.42702029651687</v>
+      </c>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr"/>
+      <c r="M355" t="inlineStr"/>
+      <c r="N355" t="inlineStr"/>
+      <c r="O355" t="inlineStr"/>
+      <c r="P355" t="inlineStr"/>
+      <c r="Q355" t="inlineStr"/>
+      <c r="R355" t="inlineStr"/>
+      <c r="S355" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T355" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="U355" t="inlineStr"/>
+      <c r="V355" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>VIS-20261001122952-A5CD16</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>5215</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Sheraz Sabir</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>113862</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>KHYBER SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:52</t>
+        </is>
+      </c>
+      <c r="H356" t="n">
+        <v>24.8552807</v>
+      </c>
+      <c r="I356" t="n">
+        <v>67.2294186</v>
+      </c>
+      <c r="J356" t="n">
+        <v>21.48500061035156</v>
+      </c>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr"/>
+      <c r="M356" t="inlineStr"/>
+      <c r="N356" t="inlineStr"/>
+      <c r="O356" t="inlineStr"/>
+      <c r="P356" t="inlineStr"/>
+      <c r="Q356" t="inlineStr"/>
+      <c r="R356" t="inlineStr"/>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T356" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="U356" t="inlineStr"/>
+      <c r="V356" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>VIS-20261001122953-C4108E</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>501429</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Wajahat Hussain</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>111578</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>MM II PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:53</t>
+        </is>
+      </c>
+      <c r="H357" t="n">
+        <v>24.786636</v>
+      </c>
+      <c r="I357" t="n">
+        <v>67.3451963</v>
+      </c>
+      <c r="J357" t="n">
+        <v>18.56999969482422</v>
+      </c>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr"/>
+      <c r="M357" t="inlineStr"/>
+      <c r="N357" t="inlineStr"/>
+      <c r="O357" t="inlineStr"/>
+      <c r="P357" t="inlineStr"/>
+      <c r="Q357" t="inlineStr"/>
+      <c r="R357" t="inlineStr"/>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T357" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="U357" t="inlineStr"/>
+      <c r="V357" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>VIS-20261001122955-AD89BB</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>2626</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Zubair A Khan</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>113884</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>TIPU PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:29:55</t>
+        </is>
+      </c>
+      <c r="H358" t="n">
+        <v>24.9303892</v>
+      </c>
+      <c r="I358" t="n">
+        <v>67.0669924</v>
+      </c>
+      <c r="J358" t="n">
+        <v>13.01500034332275</v>
+      </c>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr"/>
+      <c r="M358" t="inlineStr"/>
+      <c r="N358" t="inlineStr"/>
+      <c r="O358" t="inlineStr"/>
+      <c r="P358" t="inlineStr"/>
+      <c r="Q358" t="inlineStr"/>
+      <c r="R358" t="inlineStr"/>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T358" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="U358" t="inlineStr"/>
+      <c r="V358" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>VIS-20261001123005-EC3B96</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Kashif Karim</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>104265</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>MURREE FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:05</t>
+        </is>
+      </c>
+      <c r="H359" t="n">
+        <v>33.9169781</v>
+      </c>
+      <c r="I359" t="n">
+        <v>73.39382790000001</v>
+      </c>
+      <c r="J359" t="n">
+        <v>24.42000007629395</v>
+      </c>
+      <c r="K359" t="inlineStr"/>
+      <c r="L359" t="inlineStr"/>
+      <c r="M359" t="inlineStr"/>
+      <c r="N359" t="inlineStr"/>
+      <c r="O359" t="inlineStr"/>
+      <c r="P359" t="inlineStr"/>
+      <c r="Q359" t="inlineStr"/>
+      <c r="R359" t="inlineStr"/>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T359" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="U359" t="inlineStr"/>
+      <c r="V359" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>VIS-20261001123015-9E1F4B</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>3286</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Zulfiqar Nabi Malik</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>102649</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>QAIS MUNIM P/S</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:15</t>
+        </is>
+      </c>
+      <c r="H360" t="n">
+        <v>31.61382596709355</v>
+      </c>
+      <c r="I360" t="n">
+        <v>74.29076594302452</v>
+      </c>
+      <c r="J360" t="n">
+        <v>39.70845486859545</v>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr"/>
+      <c r="M360" t="inlineStr"/>
+      <c r="N360" t="inlineStr"/>
+      <c r="O360" t="inlineStr"/>
+      <c r="P360" t="inlineStr"/>
+      <c r="Q360" t="inlineStr"/>
+      <c r="R360" t="inlineStr"/>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T360" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="U360" t="inlineStr"/>
+      <c r="V360" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>VIS-20261001123018-7F6DC9</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Syed Asim Abbas</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>118277</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>KHAWAJA ZAFAR P/S</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:18</t>
+        </is>
+      </c>
+      <c r="H361" t="n">
+        <v>31.5019815</v>
+      </c>
+      <c r="I361" t="n">
+        <v>74.281097</v>
+      </c>
+      <c r="J361" t="n">
+        <v>24.59799957275391</v>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr"/>
+      <c r="M361" t="inlineStr"/>
+      <c r="N361" t="inlineStr"/>
+      <c r="O361" t="inlineStr"/>
+      <c r="P361" t="inlineStr"/>
+      <c r="Q361" t="inlineStr"/>
+      <c r="R361" t="inlineStr"/>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T361" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="U361" t="inlineStr"/>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>VIS-20261001123033-E319BA</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Tahwer hussain</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>113862</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>KHYBER SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:33</t>
+        </is>
+      </c>
+      <c r="H362" t="n">
+        <v>24.8552902</v>
+      </c>
+      <c r="I362" t="n">
+        <v>67.2293669</v>
+      </c>
+      <c r="J362" t="n">
+        <v>31.77000045776367</v>
+      </c>
+      <c r="K362" t="inlineStr"/>
+      <c r="L362" t="inlineStr"/>
+      <c r="M362" t="inlineStr"/>
+      <c r="N362" t="inlineStr"/>
+      <c r="O362" t="inlineStr"/>
+      <c r="P362" t="inlineStr"/>
+      <c r="Q362" t="inlineStr"/>
+      <c r="R362" t="inlineStr"/>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T362" t="n">
+        <v>50.7</v>
+      </c>
+      <c r="U362" t="inlineStr"/>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>VIS-20261001123034-95EC4A</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>3633</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Jehanzeb Abbasi</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>104303</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>KOHSAR GAS STATION</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:34</t>
+        </is>
+      </c>
+      <c r="H363" t="n">
+        <v>33.91411643353397</v>
+      </c>
+      <c r="I363" t="n">
+        <v>73.39180315142532</v>
+      </c>
+      <c r="J363" t="n">
+        <v>15.93841688452017</v>
+      </c>
+      <c r="K363" t="inlineStr"/>
+      <c r="L363" t="inlineStr"/>
+      <c r="M363" t="inlineStr"/>
+      <c r="N363" t="inlineStr"/>
+      <c r="O363" t="inlineStr"/>
+      <c r="P363" t="inlineStr"/>
+      <c r="Q363" t="inlineStr"/>
+      <c r="R363" t="inlineStr"/>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T363" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="U363" t="inlineStr"/>
+      <c r="V363" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>VIS-20261001123037-AB35D7</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>2918</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Ghulam Ahmed</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>117438</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>CHOWRANGI SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:37</t>
+        </is>
+      </c>
+      <c r="H364" t="n">
+        <v>24.9025154</v>
+      </c>
+      <c r="I364" t="n">
+        <v>67.03089629999999</v>
+      </c>
+      <c r="J364" t="n">
+        <v>23.84600067138672</v>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr"/>
+      <c r="M364" t="inlineStr"/>
+      <c r="N364" t="inlineStr"/>
+      <c r="O364" t="inlineStr"/>
+      <c r="P364" t="inlineStr"/>
+      <c r="Q364" t="inlineStr"/>
+      <c r="R364" t="inlineStr"/>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T364" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U364" t="inlineStr"/>
+      <c r="V364" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>VIS-20261001123041-0FFFA2</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>3310</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Imtiaz</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>101728</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>NASEER GASOLINE</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:41</t>
+        </is>
+      </c>
+      <c r="H365" t="n">
+        <v>24.8611984</v>
+      </c>
+      <c r="I365" t="n">
+        <v>67.0014795</v>
+      </c>
+      <c r="J365" t="n">
+        <v>28.10000038146973</v>
+      </c>
+      <c r="K365" t="inlineStr"/>
+      <c r="L365" t="inlineStr"/>
+      <c r="M365" t="inlineStr"/>
+      <c r="N365" t="inlineStr"/>
+      <c r="O365" t="inlineStr"/>
+      <c r="P365" t="inlineStr"/>
+      <c r="Q365" t="inlineStr"/>
+      <c r="R365" t="inlineStr"/>
+      <c r="S365" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T365" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="U365" t="inlineStr"/>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>VIS-20261001123042-59405D</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>4367</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Asad R shah</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>109868</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>GHOUSIA F/S</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:42</t>
+        </is>
+      </c>
+      <c r="H366" t="n">
+        <v>27.8544103</v>
+      </c>
+      <c r="I366" t="n">
+        <v>69.1069351</v>
+      </c>
+      <c r="J366" t="n">
+        <v>20.17200088500977</v>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:12</t>
+        </is>
+      </c>
+      <c r="L366" t="n">
+        <v>27.8543961</v>
+      </c>
+      <c r="M366" t="n">
+        <v>69.10694479999999</v>
+      </c>
+      <c r="N366" t="n">
+        <v>14.97200012207031</v>
+      </c>
+      <c r="O366" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>00:00:30</t>
+        </is>
+      </c>
+      <c r="R366" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="S366" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T366" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="U366" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="V366" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>VIS-20261001123050-161926</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>4919</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Amna Irfan Memon</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>120290</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>SKY BLUE SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:30:50</t>
+        </is>
+      </c>
+      <c r="H367" t="n">
+        <v>24.91830868865613</v>
+      </c>
+      <c r="I367" t="n">
+        <v>67.05305661269725</v>
+      </c>
+      <c r="J367" t="n">
+        <v>30.84762270339107</v>
+      </c>
+      <c r="K367" t="inlineStr"/>
+      <c r="L367" t="inlineStr"/>
+      <c r="M367" t="inlineStr"/>
+      <c r="N367" t="inlineStr"/>
+      <c r="O367" t="inlineStr"/>
+      <c r="P367" t="inlineStr"/>
+      <c r="Q367" t="inlineStr"/>
+      <c r="R367" t="inlineStr"/>
+      <c r="S367" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T367" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="U367" t="inlineStr"/>
+      <c r="V367" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>VIS-20261001123117-E1C925</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>3147</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Saleem Ahmed Khan</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>101704</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>MOON STAR SER.STATIONS</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:17</t>
+        </is>
+      </c>
+      <c r="H368" t="n">
+        <v>24.8515944</v>
+      </c>
+      <c r="I368" t="n">
+        <v>67.1826317</v>
+      </c>
+      <c r="J368" t="n">
+        <v>14.09500026702881</v>
+      </c>
+      <c r="K368" t="inlineStr"/>
+      <c r="L368" t="inlineStr"/>
+      <c r="M368" t="inlineStr"/>
+      <c r="N368" t="inlineStr"/>
+      <c r="O368" t="inlineStr"/>
+      <c r="P368" t="inlineStr"/>
+      <c r="Q368" t="inlineStr"/>
+      <c r="R368" t="inlineStr"/>
+      <c r="S368" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T368" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="U368" t="inlineStr"/>
+      <c r="V368" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>VIS-20261001123123-0500FB</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>4948</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Rana Muhammad Bilal Shahid</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>116003</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>AL-FAISAL P/S</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:23</t>
+        </is>
+      </c>
+      <c r="H369" t="n">
+        <v>24.8728332</v>
+      </c>
+      <c r="I369" t="n">
+        <v>67.1713894</v>
+      </c>
+      <c r="J369" t="n">
+        <v>12.46100044250488</v>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:46</t>
+        </is>
+      </c>
+      <c r="L369" t="n">
+        <v>24.8728239</v>
+      </c>
+      <c r="M369" t="n">
+        <v>67.17139570000001</v>
+      </c>
+      <c r="N369" t="n">
+        <v>16.64800071716309</v>
+      </c>
+      <c r="O369" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>00:00:23</t>
+        </is>
+      </c>
+      <c r="R369" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="S369" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T369" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="U369" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="V369" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>VIS-20261001123124-F9A444</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>3299</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Fazal Elahi</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>116024</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>NIAZ A GHAFOOR P/S</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:24</t>
+        </is>
+      </c>
+      <c r="H370" t="n">
+        <v>29.3946018</v>
+      </c>
+      <c r="I370" t="n">
+        <v>71.6861887</v>
+      </c>
+      <c r="J370" t="n">
+        <v>20.8080005645752</v>
+      </c>
+      <c r="K370" t="inlineStr"/>
+      <c r="L370" t="inlineStr"/>
+      <c r="M370" t="inlineStr"/>
+      <c r="N370" t="inlineStr"/>
+      <c r="O370" t="inlineStr"/>
+      <c r="P370" t="inlineStr"/>
+      <c r="Q370" t="inlineStr"/>
+      <c r="R370" t="inlineStr"/>
+      <c r="S370" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T370" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="U370" t="inlineStr"/>
+      <c r="V370" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>VIS-20261001123136-93CBD4</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>1763</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>M Sohail  Mujtaba</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>102649</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>QAIS MUNIM P/S</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:36</t>
+        </is>
+      </c>
+      <c r="H371" t="n">
+        <v>31.6036036036036</v>
+      </c>
+      <c r="I371" t="n">
+        <v>74.29916302446395</v>
+      </c>
+      <c r="J371" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr"/>
+      <c r="M371" t="inlineStr"/>
+      <c r="N371" t="inlineStr"/>
+      <c r="O371" t="inlineStr"/>
+      <c r="P371" t="inlineStr"/>
+      <c r="Q371" t="inlineStr"/>
+      <c r="R371" t="inlineStr"/>
+      <c r="S371" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T371" t="n">
+        <v>1377.9</v>
+      </c>
+      <c r="U371" t="inlineStr"/>
+      <c r="V371" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>VIS-20261001123138-ADB5CB</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>119080</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>GULSHAN AND COMPANY</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:38</t>
+        </is>
+      </c>
+      <c r="H372" t="n">
+        <v>24.911895</v>
+      </c>
+      <c r="I372" t="n">
+        <v>67.0138383</v>
+      </c>
+      <c r="J372" t="n">
+        <v>17.44099998474121</v>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:50</t>
+        </is>
+      </c>
+      <c r="L372" t="n">
+        <v>24.9118614</v>
+      </c>
+      <c r="M372" t="n">
+        <v>67.0138378</v>
+      </c>
+      <c r="N372" t="n">
+        <v>17.70899963378906</v>
+      </c>
+      <c r="O372" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>00:00:12</t>
+        </is>
+      </c>
+      <c r="R372" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="S372" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T372" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="U372" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="V372" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>VIS-20261001123148-CA0894</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>4879</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Manesh</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>113884</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>TIPU PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:31:48</t>
+        </is>
+      </c>
+      <c r="H373" t="n">
+        <v>24.9304117</v>
+      </c>
+      <c r="I373" t="n">
+        <v>67.066945</v>
+      </c>
+      <c r="J373" t="n">
+        <v>41.93999862670898</v>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr"/>
+      <c r="M373" t="inlineStr"/>
+      <c r="N373" t="inlineStr"/>
+      <c r="O373" t="inlineStr"/>
+      <c r="P373" t="inlineStr"/>
+      <c r="Q373" t="inlineStr"/>
+      <c r="R373" t="inlineStr"/>
+      <c r="S373" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T373" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="U373" t="inlineStr"/>
+      <c r="V373" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>VIS-20261001123205-C58463</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>501419</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Umer Abid</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>120342</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>AAA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32:05</t>
+        </is>
+      </c>
+      <c r="H374" t="n">
+        <v>31.4012907601871</v>
+      </c>
+      <c r="I374" t="n">
+        <v>74.1572650432458</v>
+      </c>
+      <c r="J374" t="n">
+        <v>3.216975644401034</v>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr"/>
+      <c r="M374" t="inlineStr"/>
+      <c r="N374" t="inlineStr"/>
+      <c r="O374" t="inlineStr"/>
+      <c r="P374" t="inlineStr"/>
+      <c r="Q374" t="inlineStr"/>
+      <c r="R374" t="inlineStr"/>
+      <c r="S374" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T374" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="U374" t="inlineStr"/>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>VIS-20261001123205-DCB737</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>4534</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Abdul karim</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>119769</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>AAI PETROLEUM</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32:05</t>
+        </is>
+      </c>
+      <c r="H375" t="n">
+        <v>31.5060334</v>
+      </c>
+      <c r="I375" t="n">
+        <v>74.38496309999999</v>
+      </c>
+      <c r="J375" t="n">
+        <v>18.40800094604492</v>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr"/>
+      <c r="M375" t="inlineStr"/>
+      <c r="N375" t="inlineStr"/>
+      <c r="O375" t="inlineStr"/>
+      <c r="P375" t="inlineStr"/>
+      <c r="Q375" t="inlineStr"/>
+      <c r="R375" t="inlineStr"/>
+      <c r="S375" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T375" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="U375" t="inlineStr"/>
+      <c r="V375" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>VIS-20261001123215-83C3D0</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>4277</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Fahad Ahmed Siddiqui</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>118465</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>A.G SS</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32:15</t>
+        </is>
+      </c>
+      <c r="H376" t="n">
+        <v>24.9668216</v>
+      </c>
+      <c r="I376" t="n">
+        <v>67.0675255</v>
+      </c>
+      <c r="J376" t="n">
+        <v>16.03800010681152</v>
+      </c>
+      <c r="K376" t="inlineStr"/>
+      <c r="L376" t="inlineStr"/>
+      <c r="M376" t="inlineStr"/>
+      <c r="N376" t="inlineStr"/>
+      <c r="O376" t="inlineStr"/>
+      <c r="P376" t="inlineStr"/>
+      <c r="Q376" t="inlineStr"/>
+      <c r="R376" t="inlineStr"/>
+      <c r="S376" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T376" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U376" t="inlineStr"/>
+      <c r="V376" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>VIS-20261001123231-59EC29</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>4987</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Muhammad Qasim Malik</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>119840</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>TAJ - 8 F/S</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32:31</t>
+        </is>
+      </c>
+      <c r="H377" t="n">
+        <v>31.4378006</v>
+      </c>
+      <c r="I377" t="n">
+        <v>73.09145359999999</v>
+      </c>
+      <c r="J377" t="n">
+        <v>12.69299983978271</v>
+      </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32:45</t>
+        </is>
+      </c>
+      <c r="L377" t="n">
+        <v>31.4377975</v>
+      </c>
+      <c r="M377" t="n">
+        <v>73.0914573</v>
+      </c>
+      <c r="N377" t="n">
+        <v>13.33199977874756</v>
+      </c>
+      <c r="O377" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>00:00:14</t>
+        </is>
+      </c>
+      <c r="R377" t="n">
+        <v>0.0039</v>
+      </c>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T377" t="n">
+        <v>28</v>
+      </c>
+      <c r="U377" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="V377" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>VIS-20261001123245-95763E</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>501440</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Abdul Qadir</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>102943</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>KHURRAM PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32:45</t>
+        </is>
+      </c>
+      <c r="H378" t="n">
+        <v>29.3815196</v>
+      </c>
+      <c r="I378" t="n">
+        <v>71.73533999999999</v>
+      </c>
+      <c r="J378" t="n">
+        <v>27.22999954223633</v>
+      </c>
+      <c r="K378" t="inlineStr"/>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
+      <c r="N378" t="inlineStr"/>
+      <c r="O378" t="inlineStr"/>
+      <c r="P378" t="inlineStr"/>
+      <c r="Q378" t="inlineStr"/>
+      <c r="R378" t="inlineStr"/>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T378" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="U378" t="inlineStr"/>
+      <c r="V378" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>VIS-20261001123257-002826</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>5119</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Syed Danyal Zahid</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>115746</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>MAURPIUR FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:32:57</t>
+        </is>
+      </c>
+      <c r="H379" t="n">
+        <v>24.8657631</v>
+      </c>
+      <c r="I379" t="n">
+        <v>66.9853674</v>
+      </c>
+      <c r="J379" t="n">
+        <v>26.79500007629395</v>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr"/>
+      <c r="M379" t="inlineStr"/>
+      <c r="N379" t="inlineStr"/>
+      <c r="O379" t="inlineStr"/>
+      <c r="P379" t="inlineStr"/>
+      <c r="Q379" t="inlineStr"/>
+      <c r="R379" t="inlineStr"/>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T379" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="U379" t="inlineStr"/>
+      <c r="V379" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V337"/>
+  <autoFilter ref="A1:V379"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$379</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$404</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V379"/>
+  <dimension ref="A1:V404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -3647,23 +3647,47 @@
       <c r="J45" t="n">
         <v>20</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:35:17</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>33.6680262</v>
+      </c>
+      <c r="M45" t="n">
+        <v>73.0774598</v>
+      </c>
+      <c r="N45" t="n">
+        <v>7.105999946594238</v>
+      </c>
+      <c r="O45" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>01:54:37</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>1.9103</v>
+      </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T45" t="n">
         <v>18.7</v>
       </c>
-      <c r="U45" t="inlineStr"/>
+      <c r="U45" t="n">
+        <v>14.3</v>
+      </c>
       <c r="V45" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -4615,23 +4639,47 @@
       <c r="J59" t="n">
         <v>28.26199913</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:35:15</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>33.66793</v>
+      </c>
+      <c r="M59" t="n">
+        <v>73.07744630000001</v>
+      </c>
+      <c r="N59" t="n">
+        <v>16.71100044250488</v>
+      </c>
+      <c r="O59" t="n">
+        <v>35</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>01:50:39</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>1.8442</v>
+      </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T59" t="n">
         <v>16.8</v>
       </c>
-      <c r="U59" t="inlineStr"/>
+      <c r="U59" t="n">
+        <v>18.3</v>
+      </c>
       <c r="V59" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -17191,23 +17239,47 @@
       <c r="J248" t="n">
         <v>11.96500015</v>
       </c>
-      <c r="K248" t="inlineStr"/>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr"/>
-      <c r="Q248" t="inlineStr"/>
-      <c r="R248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:33:56</t>
+        </is>
+      </c>
+      <c r="L248" t="n">
+        <v>24.9378066</v>
+      </c>
+      <c r="M248" t="n">
+        <v>67.0764448</v>
+      </c>
+      <c r="N248" t="n">
+        <v>12.10799980163574</v>
+      </c>
+      <c r="O248" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>01:09:41</t>
+        </is>
+      </c>
+      <c r="R248" t="n">
+        <v>1.1614</v>
+      </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T248" t="n">
         <v>4.5</v>
       </c>
-      <c r="U248" t="inlineStr"/>
+      <c r="U248" t="n">
+        <v>3.2</v>
+      </c>
       <c r="V248" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -24807,23 +24879,47 @@
       <c r="J357" t="n">
         <v>18.56999969482422</v>
       </c>
-      <c r="K357" t="inlineStr"/>
-      <c r="L357" t="inlineStr"/>
-      <c r="M357" t="inlineStr"/>
-      <c r="N357" t="inlineStr"/>
-      <c r="O357" t="inlineStr"/>
-      <c r="P357" t="inlineStr"/>
-      <c r="Q357" t="inlineStr"/>
-      <c r="R357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:34:42</t>
+        </is>
+      </c>
+      <c r="L357" t="n">
+        <v>24.7866289</v>
+      </c>
+      <c r="M357" t="n">
+        <v>67.34521479999999</v>
+      </c>
+      <c r="N357" t="n">
+        <v>21.60000038146973</v>
+      </c>
+      <c r="O357" t="n">
+        <v>2</v>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>00:04:49</t>
+        </is>
+      </c>
+      <c r="R357" t="n">
+        <v>0.0803</v>
+      </c>
       <c r="S357" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T357" t="n">
         <v>11.6</v>
       </c>
-      <c r="U357" t="inlineStr"/>
+      <c r="U357" t="n">
+        <v>9.9</v>
+      </c>
       <c r="V357" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -26331,23 +26427,47 @@
       <c r="J378" t="n">
         <v>27.22999954223633</v>
       </c>
-      <c r="K378" t="inlineStr"/>
-      <c r="L378" t="inlineStr"/>
-      <c r="M378" t="inlineStr"/>
-      <c r="N378" t="inlineStr"/>
-      <c r="O378" t="inlineStr"/>
-      <c r="P378" t="inlineStr"/>
-      <c r="Q378" t="inlineStr"/>
-      <c r="R378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:34:19</t>
+        </is>
+      </c>
+      <c r="L378" t="n">
+        <v>29.3815581</v>
+      </c>
+      <c r="M378" t="n">
+        <v>71.7354751</v>
+      </c>
+      <c r="N378" t="n">
+        <v>30.10499954223633</v>
+      </c>
+      <c r="O378" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>00:01:34</t>
+        </is>
+      </c>
+      <c r="R378" t="n">
+        <v>0.0261</v>
+      </c>
       <c r="S378" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T378" t="n">
         <v>37.3</v>
       </c>
-      <c r="U378" t="inlineStr"/>
+      <c r="U378" t="n">
+        <v>44.6</v>
+      </c>
       <c r="V378" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -26422,8 +26542,1852 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>VIS-20261001123329-FFA998</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>3405</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Ali murad khan</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>110114</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>MAZHAR ALI F/S</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:33:29</t>
+        </is>
+      </c>
+      <c r="H380" t="n">
+        <v>32.7997765</v>
+      </c>
+      <c r="I380" t="n">
+        <v>73.8729797</v>
+      </c>
+      <c r="J380" t="n">
+        <v>14.97900009155273</v>
+      </c>
+      <c r="K380" t="inlineStr"/>
+      <c r="L380" t="inlineStr"/>
+      <c r="M380" t="inlineStr"/>
+      <c r="N380" t="inlineStr"/>
+      <c r="O380" t="inlineStr"/>
+      <c r="P380" t="inlineStr"/>
+      <c r="Q380" t="inlineStr"/>
+      <c r="R380" t="inlineStr"/>
+      <c r="S380" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T380" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="U380" t="inlineStr"/>
+      <c r="V380" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>VIS-20261001123333-0584E3</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Abdul Qudoos Qureshi</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>118850</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>MEHDI PETROLEUM SER</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:33:33</t>
+        </is>
+      </c>
+      <c r="H381" t="n">
+        <v>24.9018675</v>
+      </c>
+      <c r="I381" t="n">
+        <v>67.20258389999999</v>
+      </c>
+      <c r="J381" t="n">
+        <v>20.45599937438965</v>
+      </c>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr"/>
+      <c r="M381" t="inlineStr"/>
+      <c r="N381" t="inlineStr"/>
+      <c r="O381" t="inlineStr"/>
+      <c r="P381" t="inlineStr"/>
+      <c r="Q381" t="inlineStr"/>
+      <c r="R381" t="inlineStr"/>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T381" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="U381" t="inlineStr"/>
+      <c r="V381" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>VIS-20261001123334-BF6793</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>4430</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Muhammad Ahmed Siddiqui</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>117973</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>PSO S/S 76 (SHEERIN)</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:33:34</t>
+        </is>
+      </c>
+      <c r="H382" t="n">
+        <v>24.8191335</v>
+      </c>
+      <c r="I382" t="n">
+        <v>66.9942205</v>
+      </c>
+      <c r="J382" t="n">
+        <v>48.90000152587891</v>
+      </c>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr"/>
+      <c r="M382" t="inlineStr"/>
+      <c r="N382" t="inlineStr"/>
+      <c r="O382" t="inlineStr"/>
+      <c r="P382" t="inlineStr"/>
+      <c r="Q382" t="inlineStr"/>
+      <c r="R382" t="inlineStr"/>
+      <c r="S382" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T382" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U382" t="inlineStr"/>
+      <c r="V382" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>VIS-20261001123343-A9D9E8</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>4948</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Rana Muhammad Bilal Shahid</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>116003</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>AL-FAISAL P/S</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:33:43</t>
+        </is>
+      </c>
+      <c r="H383" t="n">
+        <v>24.8728214</v>
+      </c>
+      <c r="I383" t="n">
+        <v>67.171385</v>
+      </c>
+      <c r="J383" t="n">
+        <v>20.40800094604492</v>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:33:52</t>
+        </is>
+      </c>
+      <c r="L383" t="n">
+        <v>24.8728288</v>
+      </c>
+      <c r="M383" t="n">
+        <v>67.1713891</v>
+      </c>
+      <c r="N383" t="n">
+        <v>9.166999816894531</v>
+      </c>
+      <c r="O383" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>00:00:09</t>
+        </is>
+      </c>
+      <c r="R383" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S383" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T383" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="U383" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="V383" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>VIS-20261001123403-1262F6</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Usman Ali Qadri</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>120342</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>AAA FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:34:03</t>
+        </is>
+      </c>
+      <c r="H384" t="n">
+        <v>31.4012621</v>
+      </c>
+      <c r="I384" t="n">
+        <v>74.1571321</v>
+      </c>
+      <c r="J384" t="n">
+        <v>18.30599975585938</v>
+      </c>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr"/>
+      <c r="M384" t="inlineStr"/>
+      <c r="N384" t="inlineStr"/>
+      <c r="O384" t="inlineStr"/>
+      <c r="P384" t="inlineStr"/>
+      <c r="Q384" t="inlineStr"/>
+      <c r="R384" t="inlineStr"/>
+      <c r="S384" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T384" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="U384" t="inlineStr"/>
+      <c r="V384" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>VIS-20261001123413-2EC2C6</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Imran Hussain</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>118465</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>A.G SS</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:34:13</t>
+        </is>
+      </c>
+      <c r="H385" t="n">
+        <v>24.9668143</v>
+      </c>
+      <c r="I385" t="n">
+        <v>67.0675239</v>
+      </c>
+      <c r="J385" t="n">
+        <v>14.27700042724609</v>
+      </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr"/>
+      <c r="M385" t="inlineStr"/>
+      <c r="N385" t="inlineStr"/>
+      <c r="O385" t="inlineStr"/>
+      <c r="P385" t="inlineStr"/>
+      <c r="Q385" t="inlineStr"/>
+      <c r="R385" t="inlineStr"/>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T385" t="n">
+        <v>3</v>
+      </c>
+      <c r="U385" t="inlineStr"/>
+      <c r="V385" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>VIS-20261001123427-FF060A</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>4628</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Muhammad Yahya Zamir</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>120605</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>A &amp; S P/S</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:34:27</t>
+        </is>
+      </c>
+      <c r="H386" t="n">
+        <v>24.88288288288288</v>
+      </c>
+      <c r="I386" t="n">
+        <v>67.1725841613777</v>
+      </c>
+      <c r="J386" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr"/>
+      <c r="M386" t="inlineStr"/>
+      <c r="N386" t="inlineStr"/>
+      <c r="O386" t="inlineStr"/>
+      <c r="P386" t="inlineStr"/>
+      <c r="Q386" t="inlineStr"/>
+      <c r="R386" t="inlineStr"/>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T386" t="n">
+        <v>282.6</v>
+      </c>
+      <c r="U386" t="inlineStr"/>
+      <c r="V386" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>VIS-20261001123443-B1B9C3</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>2995</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Asif Raza khan</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>102943</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>KHURRAM PET SERVICE</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:34:43</t>
+        </is>
+      </c>
+      <c r="H387" t="n">
+        <v>29.381315</v>
+      </c>
+      <c r="I387" t="n">
+        <v>71.7354414</v>
+      </c>
+      <c r="J387" t="n">
+        <v>14.07999992370605</v>
+      </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:35:14</t>
+        </is>
+      </c>
+      <c r="L387" t="n">
+        <v>29.3813053</v>
+      </c>
+      <c r="M387" t="n">
+        <v>71.73545470000001</v>
+      </c>
+      <c r="N387" t="n">
+        <v>20.63100051879883</v>
+      </c>
+      <c r="O387" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>00:00:31</t>
+        </is>
+      </c>
+      <c r="R387" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T387" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="U387" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="V387" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>VIS-20261001123451-EB5075</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>1414</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Syed Zahid yaqoob</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>119769</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>AAI PETROLEUM</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:34:51</t>
+        </is>
+      </c>
+      <c r="H388" t="n">
+        <v>31.5060108</v>
+      </c>
+      <c r="I388" t="n">
+        <v>74.3849653</v>
+      </c>
+      <c r="J388" t="n">
+        <v>18.0319995880127</v>
+      </c>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr"/>
+      <c r="M388" t="inlineStr"/>
+      <c r="N388" t="inlineStr"/>
+      <c r="O388" t="inlineStr"/>
+      <c r="P388" t="inlineStr"/>
+      <c r="Q388" t="inlineStr"/>
+      <c r="R388" t="inlineStr"/>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T388" t="n">
+        <v>119</v>
+      </c>
+      <c r="U388" t="inlineStr"/>
+      <c r="V388" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>VIS-20261001123506-14145B</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>5077</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Col R Rao Hameed ur Rehman</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>112126</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>BOSTAN PETROLEUM</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:35:06</t>
+        </is>
+      </c>
+      <c r="H389" t="n">
+        <v>33.56887429848847</v>
+      </c>
+      <c r="I389" t="n">
+        <v>73.15647070293137</v>
+      </c>
+      <c r="J389" t="n">
+        <v>68.09123124221786</v>
+      </c>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr"/>
+      <c r="M389" t="inlineStr"/>
+      <c r="N389" t="inlineStr"/>
+      <c r="O389" t="inlineStr"/>
+      <c r="P389" t="inlineStr"/>
+      <c r="Q389" t="inlineStr"/>
+      <c r="R389" t="inlineStr"/>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T389" t="n">
+        <v>35.9</v>
+      </c>
+      <c r="U389" t="inlineStr"/>
+      <c r="V389" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>VIS-20261001123521-26EBDD</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Muhammad zubair</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>116912</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>AL-HARAM FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:35:21</t>
+        </is>
+      </c>
+      <c r="H390" t="n">
+        <v>30.6554787</v>
+      </c>
+      <c r="I390" t="n">
+        <v>73.1147481</v>
+      </c>
+      <c r="J390" t="n">
+        <v>32.98300170898438</v>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:37:31</t>
+        </is>
+      </c>
+      <c r="L390" t="n">
+        <v>30.6555202</v>
+      </c>
+      <c r="M390" t="n">
+        <v>73.1147395</v>
+      </c>
+      <c r="N390" t="n">
+        <v>37.43199920654297</v>
+      </c>
+      <c r="O390" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>00:02:10</t>
+        </is>
+      </c>
+      <c r="R390" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T390" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="U390" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V390" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>VIS-20261001123524-14E96F</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>3257</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Mohammad Hafiz shah</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>115746</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>MAURPIUR FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:35:24</t>
+        </is>
+      </c>
+      <c r="H391" t="n">
+        <v>24.86486486486486</v>
+      </c>
+      <c r="I391" t="n">
+        <v>66.98406106279202</v>
+      </c>
+      <c r="J391" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K391" t="inlineStr"/>
+      <c r="L391" t="inlineStr"/>
+      <c r="M391" t="inlineStr"/>
+      <c r="N391" t="inlineStr"/>
+      <c r="O391" t="inlineStr"/>
+      <c r="P391" t="inlineStr"/>
+      <c r="Q391" t="inlineStr"/>
+      <c r="R391" t="inlineStr"/>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T391" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="U391" t="inlineStr"/>
+      <c r="V391" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>VIS-20261001123532-8F3D3E</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>4442</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>M Masood</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>118277</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>KHAWAJA ZAFAR P/S</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:35:32</t>
+        </is>
+      </c>
+      <c r="H392" t="n">
+        <v>31.5019687</v>
+      </c>
+      <c r="I392" t="n">
+        <v>74.2810812</v>
+      </c>
+      <c r="J392" t="n">
+        <v>19.34900093078613</v>
+      </c>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr"/>
+      <c r="M392" t="inlineStr"/>
+      <c r="N392" t="inlineStr"/>
+      <c r="O392" t="inlineStr"/>
+      <c r="P392" t="inlineStr"/>
+      <c r="Q392" t="inlineStr"/>
+      <c r="R392" t="inlineStr"/>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T392" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U392" t="inlineStr"/>
+      <c r="V392" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>VIS-20261001123559-49315F</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>2175</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Zulfiqar Ali Baloch</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>101737</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>AL-MADINA T/S</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:35:59</t>
+        </is>
+      </c>
+      <c r="H393" t="n">
+        <v>25.6067075</v>
+      </c>
+      <c r="I393" t="n">
+        <v>68.4347245</v>
+      </c>
+      <c r="J393" t="n">
+        <v>300</v>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:36:22</t>
+        </is>
+      </c>
+      <c r="L393" t="n">
+        <v>25.6460082</v>
+      </c>
+      <c r="M393" t="n">
+        <v>68.30028280000001</v>
+      </c>
+      <c r="N393" t="n">
+        <v>42.81700134277344</v>
+      </c>
+      <c r="O393" t="n">
+        <v>14169.5</v>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>Big Difference</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>00:00:23</t>
+        </is>
+      </c>
+      <c r="R393" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T393" t="n">
+        <v>14155.4</v>
+      </c>
+      <c r="U393" t="n">
+        <v>20</v>
+      </c>
+      <c r="V393" t="inlineStr">
+        <is>
+          <t>Mismatch &gt; 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>VIS-20261001123600-C5E36B</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>3141</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Raees Shaikh</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>116628</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>METRO SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:36:00</t>
+        </is>
+      </c>
+      <c r="H394" t="n">
+        <v>25.3759978</v>
+      </c>
+      <c r="I394" t="n">
+        <v>68.3574351</v>
+      </c>
+      <c r="J394" t="n">
+        <v>32.70600128173828</v>
+      </c>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr"/>
+      <c r="M394" t="inlineStr"/>
+      <c r="N394" t="inlineStr"/>
+      <c r="O394" t="inlineStr"/>
+      <c r="P394" t="inlineStr"/>
+      <c r="Q394" t="inlineStr"/>
+      <c r="R394" t="inlineStr"/>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T394" t="n">
+        <v>1392</v>
+      </c>
+      <c r="U394" t="inlineStr"/>
+      <c r="V394" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>VIS-20261001123603-FEAD92</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>4801</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Naseer Khan</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>110612</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>SCOUT WELFARE F/S</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:36:03</t>
+        </is>
+      </c>
+      <c r="H395" t="n">
+        <v>34.0151801</v>
+      </c>
+      <c r="I395" t="n">
+        <v>71.5987265</v>
+      </c>
+      <c r="J395" t="n">
+        <v>14.08800029754639</v>
+      </c>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr"/>
+      <c r="M395" t="inlineStr"/>
+      <c r="N395" t="inlineStr"/>
+      <c r="O395" t="inlineStr"/>
+      <c r="P395" t="inlineStr"/>
+      <c r="Q395" t="inlineStr"/>
+      <c r="R395" t="inlineStr"/>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T395" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="U395" t="inlineStr"/>
+      <c r="V395" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>VIS-20261001123610-C006C4</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>3241</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Mirza Aamir baig</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>112326</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>AWAMI FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:36:10</t>
+        </is>
+      </c>
+      <c r="H396" t="n">
+        <v>24.93693693693694</v>
+      </c>
+      <c r="I396" t="n">
+        <v>67.12253827027016</v>
+      </c>
+      <c r="J396" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:38:05</t>
+        </is>
+      </c>
+      <c r="L396" t="n">
+        <v>24.93693693693694</v>
+      </c>
+      <c r="M396" t="n">
+        <v>67.12253827027016</v>
+      </c>
+      <c r="N396" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O396" t="n">
+        <v>0</v>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>00:01:55</t>
+        </is>
+      </c>
+      <c r="R396" t="n">
+        <v>0.0319</v>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T396" t="n">
+        <v>711.5</v>
+      </c>
+      <c r="U396" t="n">
+        <v>711.5</v>
+      </c>
+      <c r="V396" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>VIS-20261001123619-A32FB9</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>4349</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Fahad chishti</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>112326</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>AWAMI FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:36:19</t>
+        </is>
+      </c>
+      <c r="H397" t="n">
+        <v>24.9342411</v>
+      </c>
+      <c r="I397" t="n">
+        <v>67.1288357</v>
+      </c>
+      <c r="J397" t="n">
+        <v>10.76599979400635</v>
+      </c>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr"/>
+      <c r="M397" t="inlineStr"/>
+      <c r="N397" t="inlineStr"/>
+      <c r="O397" t="inlineStr"/>
+      <c r="P397" t="inlineStr"/>
+      <c r="Q397" t="inlineStr"/>
+      <c r="R397" t="inlineStr"/>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T397" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="U397" t="inlineStr"/>
+      <c r="V397" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>VIS-20261001123641-0ACD67</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>501441</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Sajeed ur Rahman</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>116023</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>DIAMOND F/S</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:36:41</t>
+        </is>
+      </c>
+      <c r="H398" t="n">
+        <v>34.0040743</v>
+      </c>
+      <c r="I398" t="n">
+        <v>71.5044663</v>
+      </c>
+      <c r="J398" t="n">
+        <v>14.02299976348877</v>
+      </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:37:42</t>
+        </is>
+      </c>
+      <c r="L398" t="n">
+        <v>34.004072</v>
+      </c>
+      <c r="M398" t="n">
+        <v>71.5044606</v>
+      </c>
+      <c r="N398" t="n">
+        <v>11.80700016021729</v>
+      </c>
+      <c r="O398" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>00:01:01</t>
+        </is>
+      </c>
+      <c r="R398" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T398" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="U398" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="V398" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>VIS-20261001123642-2A621C</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>2525</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Sami Undre</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>114723</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>STADIUM SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:36:42</t>
+        </is>
+      </c>
+      <c r="H399" t="n">
+        <v>24.8913491</v>
+      </c>
+      <c r="I399" t="n">
+        <v>67.07714230000001</v>
+      </c>
+      <c r="J399" t="n">
+        <v>11.50300025939941</v>
+      </c>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr"/>
+      <c r="M399" t="inlineStr"/>
+      <c r="N399" t="inlineStr"/>
+      <c r="O399" t="inlineStr"/>
+      <c r="P399" t="inlineStr"/>
+      <c r="Q399" t="inlineStr"/>
+      <c r="R399" t="inlineStr"/>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T399" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="U399" t="inlineStr"/>
+      <c r="V399" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>VIS-20261001123729-BA34EC</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>4970</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Adnan Afzaal Siddiqui</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>113884</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>TIPU PETROLEUM SERVICE</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:37:29</t>
+        </is>
+      </c>
+      <c r="H400" t="n">
+        <v>24.9303529</v>
+      </c>
+      <c r="I400" t="n">
+        <v>67.0669382</v>
+      </c>
+      <c r="J400" t="n">
+        <v>18.9330005645752</v>
+      </c>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr"/>
+      <c r="M400" t="inlineStr"/>
+      <c r="N400" t="inlineStr"/>
+      <c r="O400" t="inlineStr"/>
+      <c r="P400" t="inlineStr"/>
+      <c r="Q400" t="inlineStr"/>
+      <c r="R400" t="inlineStr"/>
+      <c r="S400" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T400" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="U400" t="inlineStr"/>
+      <c r="V400" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>VIS-20261001123741-618C66</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>4552</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Muhammad ismail</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>110612</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>SCOUT WELFARE F/S</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:37:41</t>
+        </is>
+      </c>
+      <c r="H401" t="n">
+        <v>34.0152074</v>
+      </c>
+      <c r="I401" t="n">
+        <v>71.5987327</v>
+      </c>
+      <c r="J401" t="n">
+        <v>10.47299957275391</v>
+      </c>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr"/>
+      <c r="M401" t="inlineStr"/>
+      <c r="N401" t="inlineStr"/>
+      <c r="O401" t="inlineStr"/>
+      <c r="P401" t="inlineStr"/>
+      <c r="Q401" t="inlineStr"/>
+      <c r="R401" t="inlineStr"/>
+      <c r="S401" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T401" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="U401" t="inlineStr"/>
+      <c r="V401" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>VIS-20261001123754-71A468</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>3477</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Imran Naeem Khan</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>118158</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>PSO S/S 79 (EMERALD FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:37:54</t>
+        </is>
+      </c>
+      <c r="H402" t="n">
+        <v>31.50115195771338</v>
+      </c>
+      <c r="I402" t="n">
+        <v>74.32135191455836</v>
+      </c>
+      <c r="J402" t="n">
+        <v>18.17658003856427</v>
+      </c>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr"/>
+      <c r="M402" t="inlineStr"/>
+      <c r="N402" t="inlineStr"/>
+      <c r="O402" t="inlineStr"/>
+      <c r="P402" t="inlineStr"/>
+      <c r="Q402" t="inlineStr"/>
+      <c r="R402" t="inlineStr"/>
+      <c r="S402" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T402" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="U402" t="inlineStr"/>
+      <c r="V402" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>VIS-20261001123758-1CFFF6</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>501441</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Sajeed ur Rahman</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>116023</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>DIAMOND F/S</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:37:58</t>
+        </is>
+      </c>
+      <c r="H403" t="n">
+        <v>34.0040724</v>
+      </c>
+      <c r="I403" t="n">
+        <v>71.504465</v>
+      </c>
+      <c r="J403" t="n">
+        <v>12.86400032043457</v>
+      </c>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr"/>
+      <c r="M403" t="inlineStr"/>
+      <c r="N403" t="inlineStr"/>
+      <c r="O403" t="inlineStr"/>
+      <c r="P403" t="inlineStr"/>
+      <c r="Q403" t="inlineStr"/>
+      <c r="R403" t="inlineStr"/>
+      <c r="S403" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T403" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="U403" t="inlineStr"/>
+      <c r="V403" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>VIS-20261001123806-370659</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>3315</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Bismillah Khan</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>104101</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>PSO S/S 2 (FARIDIA)</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:38:06</t>
+        </is>
+      </c>
+      <c r="H404" t="n">
+        <v>30.2006769</v>
+      </c>
+      <c r="I404" t="n">
+        <v>71.4538034</v>
+      </c>
+      <c r="J404" t="n">
+        <v>20.05500030517578</v>
+      </c>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr"/>
+      <c r="M404" t="inlineStr"/>
+      <c r="N404" t="inlineStr"/>
+      <c r="O404" t="inlineStr"/>
+      <c r="P404" t="inlineStr"/>
+      <c r="Q404" t="inlineStr"/>
+      <c r="R404" t="inlineStr"/>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T404" t="n">
+        <v>1029</v>
+      </c>
+      <c r="U404" t="inlineStr"/>
+      <c r="V404" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V379"/>
+  <autoFilter ref="A1:V404"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -27771,47 +27771,23 @@
       <c r="J396" t="n">
         <v>2000</v>
       </c>
-      <c r="K396" t="inlineStr">
-        <is>
-          <t>2026-10-01 12:38:05</t>
-        </is>
-      </c>
-      <c r="L396" t="n">
-        <v>24.93693693693694</v>
-      </c>
-      <c r="M396" t="n">
-        <v>67.12253827027016</v>
-      </c>
-      <c r="N396" t="n">
-        <v>2000</v>
-      </c>
-      <c r="O396" t="n">
-        <v>0</v>
-      </c>
-      <c r="P396" t="inlineStr">
-        <is>
-          <t>Almost Same</t>
-        </is>
-      </c>
-      <c r="Q396" t="inlineStr">
-        <is>
-          <t>00:01:55</t>
-        </is>
-      </c>
-      <c r="R396" t="n">
-        <v>0.0319</v>
-      </c>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr"/>
+      <c r="M396" t="inlineStr"/>
+      <c r="N396" t="inlineStr"/>
+      <c r="O396" t="inlineStr"/>
+      <c r="P396" t="inlineStr"/>
+      <c r="Q396" t="inlineStr"/>
+      <c r="R396" t="inlineStr"/>
       <c r="S396" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="T396" t="n">
         <v>711.5</v>
       </c>
-      <c r="U396" t="n">
-        <v>711.5</v>
-      </c>
+      <c r="U396" t="inlineStr"/>
       <c r="V396" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>

--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Visits" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$404</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Visits'!$A$1:$V$431</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V404"/>
+  <dimension ref="A1:V431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -8975,23 +8975,47 @@
       <c r="J123" t="n">
         <v>4</v>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:41:58</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>33.704199</v>
+      </c>
+      <c r="M123" t="n">
+        <v>73.0718574</v>
+      </c>
+      <c r="N123" t="n">
+        <v>16.52899932861328</v>
+      </c>
+      <c r="O123" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>01:46:54</t>
+        </is>
+      </c>
+      <c r="R123" t="n">
+        <v>1.7817</v>
+      </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T123" t="n">
         <v>21.4</v>
       </c>
-      <c r="U123" t="inlineStr"/>
+      <c r="U123" t="n">
+        <v>21</v>
+      </c>
       <c r="V123" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -13775,26 +13799,50 @@
       <c r="J195" t="n">
         <v>12.72999954</v>
       </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:18</t>
+        </is>
+      </c>
+      <c r="L195" t="n">
+        <v>24.8368493</v>
+      </c>
+      <c r="M195" t="n">
+        <v>67.03373329999999</v>
+      </c>
+      <c r="N195" t="n">
+        <v>16.24200057983398</v>
+      </c>
+      <c r="O195" t="n">
+        <v>2873.3</v>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Big Difference</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>01:37:59</t>
+        </is>
+      </c>
+      <c r="R195" t="n">
+        <v>1.6331</v>
+      </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T195" t="n">
         <v>21.6</v>
       </c>
-      <c r="U195" t="inlineStr"/>
+      <c r="U195" t="n">
+        <v>2894.8</v>
+      </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>Within 1.5 km</t>
+          <t>Mismatch &gt; 1.5 km</t>
         </is>
       </c>
     </row>
@@ -27771,23 +27819,47 @@
       <c r="J396" t="n">
         <v>2000</v>
       </c>
-      <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
-      <c r="M396" t="inlineStr"/>
-      <c r="N396" t="inlineStr"/>
-      <c r="O396" t="inlineStr"/>
-      <c r="P396" t="inlineStr"/>
-      <c r="Q396" t="inlineStr"/>
-      <c r="R396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:38:07</t>
+        </is>
+      </c>
+      <c r="L396" t="n">
+        <v>24.93693693693694</v>
+      </c>
+      <c r="M396" t="n">
+        <v>67.12253827027016</v>
+      </c>
+      <c r="N396" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O396" t="n">
+        <v>0</v>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>00:01:57</t>
+        </is>
+      </c>
+      <c r="R396" t="n">
+        <v>0.0325</v>
+      </c>
       <c r="S396" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T396" t="n">
         <v>711.5</v>
       </c>
-      <c r="U396" t="inlineStr"/>
+      <c r="U396" t="n">
+        <v>711.5</v>
+      </c>
       <c r="V396" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -27839,23 +27911,47 @@
       <c r="J397" t="n">
         <v>10.76599979400635</v>
       </c>
-      <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
-      <c r="M397" t="inlineStr"/>
-      <c r="N397" t="inlineStr"/>
-      <c r="O397" t="inlineStr"/>
-      <c r="P397" t="inlineStr"/>
-      <c r="Q397" t="inlineStr"/>
-      <c r="R397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:38:14</t>
+        </is>
+      </c>
+      <c r="L397" t="n">
+        <v>24.9342491</v>
+      </c>
+      <c r="M397" t="n">
+        <v>67.12887600000001</v>
+      </c>
+      <c r="N397" t="n">
+        <v>10.72500038146973</v>
+      </c>
+      <c r="O397" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>00:01:55</t>
+        </is>
+      </c>
+      <c r="R397" t="n">
+        <v>0.0319</v>
+      </c>
       <c r="S397" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T397" t="n">
         <v>11.5</v>
       </c>
-      <c r="U397" t="inlineStr"/>
+      <c r="U397" t="n">
+        <v>11.1</v>
+      </c>
       <c r="V397" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -28271,23 +28367,47 @@
       <c r="J403" t="n">
         <v>12.86400032043457</v>
       </c>
-      <c r="K403" t="inlineStr"/>
-      <c r="L403" t="inlineStr"/>
-      <c r="M403" t="inlineStr"/>
-      <c r="N403" t="inlineStr"/>
-      <c r="O403" t="inlineStr"/>
-      <c r="P403" t="inlineStr"/>
-      <c r="Q403" t="inlineStr"/>
-      <c r="R403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:41:40</t>
+        </is>
+      </c>
+      <c r="L403" t="n">
+        <v>34.0040737</v>
+      </c>
+      <c r="M403" t="n">
+        <v>71.5044506</v>
+      </c>
+      <c r="N403" t="n">
+        <v>17.90800094604492</v>
+      </c>
+      <c r="O403" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>00:03:42</t>
+        </is>
+      </c>
+      <c r="R403" t="n">
+        <v>0.0617</v>
+      </c>
       <c r="S403" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T403" t="n">
         <v>32.7</v>
       </c>
-      <c r="U403" t="inlineStr"/>
+      <c r="U403" t="n">
+        <v>34.1</v>
+      </c>
       <c r="V403" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
@@ -28362,8 +28482,2060 @@
         </is>
       </c>
     </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>VIS-20261001123856-A97056</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>3241</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Mirza Aamir baig</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>112326</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>AWAMI FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:38:56</t>
+        </is>
+      </c>
+      <c r="H405" t="n">
+        <v>24.93693693693694</v>
+      </c>
+      <c r="I405" t="n">
+        <v>67.12253827027016</v>
+      </c>
+      <c r="J405" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:39:57</t>
+        </is>
+      </c>
+      <c r="L405" t="n">
+        <v>24.93693693693694</v>
+      </c>
+      <c r="M405" t="n">
+        <v>67.12253827027016</v>
+      </c>
+      <c r="N405" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O405" t="n">
+        <v>0</v>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>00:01:01</t>
+        </is>
+      </c>
+      <c r="R405" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T405" t="n">
+        <v>711.5</v>
+      </c>
+      <c r="U405" t="n">
+        <v>711.5</v>
+      </c>
+      <c r="V405" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>VIS-20261001123859-16774B</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>2512</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Arika Fazail</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>118352</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>FAISAL SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:38:59</t>
+        </is>
+      </c>
+      <c r="H406" t="n">
+        <v>24.9282675</v>
+      </c>
+      <c r="I406" t="n">
+        <v>67.0629215</v>
+      </c>
+      <c r="J406" t="n">
+        <v>21.61000061035156</v>
+      </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:39:11</t>
+        </is>
+      </c>
+      <c r="L406" t="n">
+        <v>24.9282697</v>
+      </c>
+      <c r="M406" t="n">
+        <v>67.0629277</v>
+      </c>
+      <c r="N406" t="n">
+        <v>24.89999961853027</v>
+      </c>
+      <c r="O406" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>00:00:12</t>
+        </is>
+      </c>
+      <c r="R406" t="n">
+        <v>0.0033</v>
+      </c>
+      <c r="S406" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T406" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="U406" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="V406" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>VIS-20261001123900-688A51</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>4684</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>SYED YOUSUF RAZA ZAIDI</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>104303</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>KOHSAR GAS STATION</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:39:00</t>
+        </is>
+      </c>
+      <c r="H407" t="n">
+        <v>33.9140155</v>
+      </c>
+      <c r="I407" t="n">
+        <v>73.3917622</v>
+      </c>
+      <c r="J407" t="n">
+        <v>20</v>
+      </c>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr"/>
+      <c r="M407" t="inlineStr"/>
+      <c r="N407" t="inlineStr"/>
+      <c r="O407" t="inlineStr"/>
+      <c r="P407" t="inlineStr"/>
+      <c r="Q407" t="inlineStr"/>
+      <c r="R407" t="inlineStr"/>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T407" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="U407" t="inlineStr"/>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>VIS-20261001123922-B1DBAB</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>2204</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Shah Nawaz Magsi</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>118465</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>A.G SS</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:39:22</t>
+        </is>
+      </c>
+      <c r="H408" t="n">
+        <v>24.96698196782002</v>
+      </c>
+      <c r="I408" t="n">
+        <v>67.06762715032367</v>
+      </c>
+      <c r="J408" t="n">
+        <v>21.79574753731167</v>
+      </c>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr"/>
+      <c r="M408" t="inlineStr"/>
+      <c r="N408" t="inlineStr"/>
+      <c r="O408" t="inlineStr"/>
+      <c r="P408" t="inlineStr"/>
+      <c r="Q408" t="inlineStr"/>
+      <c r="R408" t="inlineStr"/>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T408" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="U408" t="inlineStr"/>
+      <c r="V408" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>VIS-20261001123944-09FB0E</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>4713</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Zohaib Shafi</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>115746</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>MAURPIUR FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:39:44</t>
+        </is>
+      </c>
+      <c r="H409" t="n">
+        <v>24.8658919</v>
+      </c>
+      <c r="I409" t="n">
+        <v>66.9857574</v>
+      </c>
+      <c r="J409" t="n">
+        <v>34.67800140380859</v>
+      </c>
+      <c r="K409" t="inlineStr"/>
+      <c r="L409" t="inlineStr"/>
+      <c r="M409" t="inlineStr"/>
+      <c r="N409" t="inlineStr"/>
+      <c r="O409" t="inlineStr"/>
+      <c r="P409" t="inlineStr"/>
+      <c r="Q409" t="inlineStr"/>
+      <c r="R409" t="inlineStr"/>
+      <c r="S409" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T409" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="U409" t="inlineStr"/>
+      <c r="V409" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>VIS-20261001124003-2F3D6C</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Izan Islam Uddin</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>114723</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>STADIUM SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:03</t>
+        </is>
+      </c>
+      <c r="H410" t="n">
+        <v>24.8913015</v>
+      </c>
+      <c r="I410" t="n">
+        <v>67.0771144</v>
+      </c>
+      <c r="J410" t="n">
+        <v>14.90900039672852</v>
+      </c>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr"/>
+      <c r="M410" t="inlineStr"/>
+      <c r="N410" t="inlineStr"/>
+      <c r="O410" t="inlineStr"/>
+      <c r="P410" t="inlineStr"/>
+      <c r="Q410" t="inlineStr"/>
+      <c r="R410" t="inlineStr"/>
+      <c r="S410" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T410" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="U410" t="inlineStr"/>
+      <c r="V410" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>VIS-20261001124010-6A17C2</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>4557</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Khurram Shahzad</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>119328</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>SAFE FUEL</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:10</t>
+        </is>
+      </c>
+      <c r="H411" t="n">
+        <v>31.6089508</v>
+      </c>
+      <c r="I411" t="n">
+        <v>74.36417539999999</v>
+      </c>
+      <c r="J411" t="n">
+        <v>7.813000202178955</v>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:33</t>
+        </is>
+      </c>
+      <c r="L411" t="n">
+        <v>31.6089391</v>
+      </c>
+      <c r="M411" t="n">
+        <v>74.3641758</v>
+      </c>
+      <c r="N411" t="n">
+        <v>8.279000282287598</v>
+      </c>
+      <c r="O411" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>00:00:23</t>
+        </is>
+      </c>
+      <c r="R411" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T411" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U411" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="V411" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>VIS-20261001124018-FBACDD</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>501114</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Arham Hameed</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>115746</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>MAURPIUR FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:18</t>
+        </is>
+      </c>
+      <c r="H412" t="n">
+        <v>24.8656913</v>
+      </c>
+      <c r="I412" t="n">
+        <v>66.9854095</v>
+      </c>
+      <c r="J412" t="n">
+        <v>27.39100074768066</v>
+      </c>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr"/>
+      <c r="M412" t="inlineStr"/>
+      <c r="N412" t="inlineStr"/>
+      <c r="O412" t="inlineStr"/>
+      <c r="P412" t="inlineStr"/>
+      <c r="Q412" t="inlineStr"/>
+      <c r="R412" t="inlineStr"/>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T412" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="U412" t="inlineStr"/>
+      <c r="V412" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>VIS-20261001124031-87C1D3</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>3928</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Muhammad Almas</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>103808</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>MIAN &amp; CO</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:31</t>
+        </is>
+      </c>
+      <c r="H413" t="n">
+        <v>31.4113716</v>
+      </c>
+      <c r="I413" t="n">
+        <v>73.0626977</v>
+      </c>
+      <c r="J413" t="n">
+        <v>92.90000152587891</v>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:41:30</t>
+        </is>
+      </c>
+      <c r="L413" t="n">
+        <v>31.4117847</v>
+      </c>
+      <c r="M413" t="n">
+        <v>73.06237520000001</v>
+      </c>
+      <c r="N413" t="n">
+        <v>45.62599945068359</v>
+      </c>
+      <c r="O413" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>00:00:59</t>
+        </is>
+      </c>
+      <c r="R413" t="n">
+        <v>0.0164</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T413" t="n">
+        <v>51.9</v>
+      </c>
+      <c r="U413" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="V413" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>VIS-20261001124033-B37D38</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Adnan Ali Syed</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>103808</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>MIAN &amp; CO</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:33</t>
+        </is>
+      </c>
+      <c r="H414" t="n">
+        <v>31.41164822933146</v>
+      </c>
+      <c r="I414" t="n">
+        <v>73.06275031363904</v>
+      </c>
+      <c r="J414" t="n">
+        <v>35.95190348694207</v>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:41:15</t>
+        </is>
+      </c>
+      <c r="L414" t="n">
+        <v>31.41169787100448</v>
+      </c>
+      <c r="M414" t="n">
+        <v>73.06284604870589</v>
+      </c>
+      <c r="N414" t="n">
+        <v>33.98388097391314</v>
+      </c>
+      <c r="O414" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>00:00:42</t>
+        </is>
+      </c>
+      <c r="R414" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T414" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="U414" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>VIS-20261001124046-C9C580</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>3166</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Imran Sabir</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>118118</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>A. K FUEL</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:46</t>
+        </is>
+      </c>
+      <c r="H415" t="n">
+        <v>31.5257523</v>
+      </c>
+      <c r="I415" t="n">
+        <v>74.2848494</v>
+      </c>
+      <c r="J415" t="n">
+        <v>12.68400001525879</v>
+      </c>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr"/>
+      <c r="M415" t="inlineStr"/>
+      <c r="N415" t="inlineStr"/>
+      <c r="O415" t="inlineStr"/>
+      <c r="P415" t="inlineStr"/>
+      <c r="Q415" t="inlineStr"/>
+      <c r="R415" t="inlineStr"/>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T415" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="U415" t="inlineStr"/>
+      <c r="V415" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>VIS-20261001124055-C3E55B</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>3317</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Syed Muhammad Hassan</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>115746</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>MAURPIUR FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:55</t>
+        </is>
+      </c>
+      <c r="H416" t="n">
+        <v>24.8657771</v>
+      </c>
+      <c r="I416" t="n">
+        <v>66.98539700000001</v>
+      </c>
+      <c r="J416" t="n">
+        <v>30.63800048828125</v>
+      </c>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr"/>
+      <c r="M416" t="inlineStr"/>
+      <c r="N416" t="inlineStr"/>
+      <c r="O416" t="inlineStr"/>
+      <c r="P416" t="inlineStr"/>
+      <c r="Q416" t="inlineStr"/>
+      <c r="R416" t="inlineStr"/>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T416" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="U416" t="inlineStr"/>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>VIS-20261001124056-ADA831</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>4583</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>shafi ullah</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>116023</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>DIAMOND F/S</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:56</t>
+        </is>
+      </c>
+      <c r="H417" t="n">
+        <v>34.0040716</v>
+      </c>
+      <c r="I417" t="n">
+        <v>71.504441</v>
+      </c>
+      <c r="J417" t="n">
+        <v>20</v>
+      </c>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr"/>
+      <c r="M417" t="inlineStr"/>
+      <c r="N417" t="inlineStr"/>
+      <c r="O417" t="inlineStr"/>
+      <c r="P417" t="inlineStr"/>
+      <c r="Q417" t="inlineStr"/>
+      <c r="R417" t="inlineStr"/>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T417" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="U417" t="inlineStr"/>
+      <c r="V417" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>VIS-20261001124059-35DE03</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>5058</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Asma Zameer</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>102296</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>IQBAL &amp; CO</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:40:59</t>
+        </is>
+      </c>
+      <c r="H418" t="n">
+        <v>28.0241367</v>
+      </c>
+      <c r="I418" t="n">
+        <v>69.54239</v>
+      </c>
+      <c r="J418" t="n">
+        <v>9.600000381469727</v>
+      </c>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr"/>
+      <c r="M418" t="inlineStr"/>
+      <c r="N418" t="inlineStr"/>
+      <c r="O418" t="inlineStr"/>
+      <c r="P418" t="inlineStr"/>
+      <c r="Q418" t="inlineStr"/>
+      <c r="R418" t="inlineStr"/>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T418" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="U418" t="inlineStr"/>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>VIS-20261001124101-1F5E64</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>501453</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Haseeb hussain</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>119574</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>KAARSAZ PETROLEUM SERVICES</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:41:01</t>
+        </is>
+      </c>
+      <c r="H419" t="n">
+        <v>24.8740641</v>
+      </c>
+      <c r="I419" t="n">
+        <v>67.0950035</v>
+      </c>
+      <c r="J419" t="n">
+        <v>12.05000019073486</v>
+      </c>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr"/>
+      <c r="M419" t="inlineStr"/>
+      <c r="N419" t="inlineStr"/>
+      <c r="O419" t="inlineStr"/>
+      <c r="P419" t="inlineStr"/>
+      <c r="Q419" t="inlineStr"/>
+      <c r="R419" t="inlineStr"/>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T419" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="U419" t="inlineStr"/>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>VIS-20261001124125-FF0D5E</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>3237</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Mujtaba Jalal Qasim</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>118986</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>PREMIER FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:41:25</t>
+        </is>
+      </c>
+      <c r="H420" t="n">
+        <v>31.5031587</v>
+      </c>
+      <c r="I420" t="n">
+        <v>74.3476802</v>
+      </c>
+      <c r="J420" t="n">
+        <v>32.69200134277344</v>
+      </c>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr"/>
+      <c r="M420" t="inlineStr"/>
+      <c r="N420" t="inlineStr"/>
+      <c r="O420" t="inlineStr"/>
+      <c r="P420" t="inlineStr"/>
+      <c r="Q420" t="inlineStr"/>
+      <c r="R420" t="inlineStr"/>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T420" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="U420" t="inlineStr"/>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>VIS-20261001124143-4C7475</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>4557</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Khurram Shahzad</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>119328</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>SAFE FUEL</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:41:43</t>
+        </is>
+      </c>
+      <c r="H421" t="n">
+        <v>31.6089329</v>
+      </c>
+      <c r="I421" t="n">
+        <v>74.3641733</v>
+      </c>
+      <c r="J421" t="n">
+        <v>6.428999900817871</v>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:10</t>
+        </is>
+      </c>
+      <c r="L421" t="n">
+        <v>31.6089317</v>
+      </c>
+      <c r="M421" t="n">
+        <v>74.36417609999999</v>
+      </c>
+      <c r="N421" t="n">
+        <v>6.682000160217285</v>
+      </c>
+      <c r="O421" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>00:00:27</t>
+        </is>
+      </c>
+      <c r="R421" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T421" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="U421" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>VIS-20261001124146-829BB3</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>3145</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Muhammad zubair</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>116912</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>AL-HARAM FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:41:46</t>
+        </is>
+      </c>
+      <c r="H422" t="n">
+        <v>30.6553831</v>
+      </c>
+      <c r="I422" t="n">
+        <v>73.11468669999999</v>
+      </c>
+      <c r="J422" t="n">
+        <v>16.29999923706055</v>
+      </c>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr"/>
+      <c r="M422" t="inlineStr"/>
+      <c r="N422" t="inlineStr"/>
+      <c r="O422" t="inlineStr"/>
+      <c r="P422" t="inlineStr"/>
+      <c r="Q422" t="inlineStr"/>
+      <c r="R422" t="inlineStr"/>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T422" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U422" t="inlineStr"/>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>VIS-20261001124215-2BF61B</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Adil Ahmed</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>110571</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>AJMEER P/S</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:15</t>
+        </is>
+      </c>
+      <c r="H423" t="n">
+        <v>24.9845969</v>
+      </c>
+      <c r="I423" t="n">
+        <v>67.0518646</v>
+      </c>
+      <c r="J423" t="n">
+        <v>17.86499977111816</v>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:46</t>
+        </is>
+      </c>
+      <c r="L423" t="n">
+        <v>24.9846043</v>
+      </c>
+      <c r="M423" t="n">
+        <v>67.0518768</v>
+      </c>
+      <c r="N423" t="n">
+        <v>13.19400024414062</v>
+      </c>
+      <c r="O423" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>00:00:31</t>
+        </is>
+      </c>
+      <c r="R423" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T423" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="U423" t="n">
+        <v>200.7</v>
+      </c>
+      <c r="V423" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>VIS-20261001124218-F27C1B</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>3264</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Zameer Illahi Pitafi</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>102296</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>IQBAL &amp; CO</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:18</t>
+        </is>
+      </c>
+      <c r="H424" t="n">
+        <v>28.0241285</v>
+      </c>
+      <c r="I424" t="n">
+        <v>69.5422877</v>
+      </c>
+      <c r="J424" t="n">
+        <v>27.38800048828125</v>
+      </c>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr"/>
+      <c r="M424" t="inlineStr"/>
+      <c r="N424" t="inlineStr"/>
+      <c r="O424" t="inlineStr"/>
+      <c r="P424" t="inlineStr"/>
+      <c r="Q424" t="inlineStr"/>
+      <c r="R424" t="inlineStr"/>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T424" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="U424" t="inlineStr"/>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>VIS-20261001124241-C4BA51</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>119080</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>GULSHAN AND COMPANY</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:41</t>
+        </is>
+      </c>
+      <c r="H425" t="n">
+        <v>24.9118267</v>
+      </c>
+      <c r="I425" t="n">
+        <v>67.01394999999999</v>
+      </c>
+      <c r="J425" t="n">
+        <v>4.400000095367432</v>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:51</t>
+        </is>
+      </c>
+      <c r="L425" t="n">
+        <v>24.9118257</v>
+      </c>
+      <c r="M425" t="n">
+        <v>67.0139494</v>
+      </c>
+      <c r="N425" t="n">
+        <v>7.735000133514404</v>
+      </c>
+      <c r="O425" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>00:00:10</t>
+        </is>
+      </c>
+      <c r="R425" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T425" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="U425" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>VIS-20261001124243-B11A09</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Ahmed Pasha</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>103087</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>KAMOKA FILL STATION</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:43</t>
+        </is>
+      </c>
+      <c r="H426" t="n">
+        <v>31.3841729</v>
+      </c>
+      <c r="I426" t="n">
+        <v>73.2003704</v>
+      </c>
+      <c r="J426" t="n">
+        <v>28.59099960327148</v>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:58</t>
+        </is>
+      </c>
+      <c r="L426" t="n">
+        <v>31.3841682</v>
+      </c>
+      <c r="M426" t="n">
+        <v>73.2003678</v>
+      </c>
+      <c r="N426" t="n">
+        <v>21.91300010681152</v>
+      </c>
+      <c r="O426" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>00:00:15</t>
+        </is>
+      </c>
+      <c r="R426" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="T426" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="U426" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>VIS-20261001124243-9EE529</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>4655</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Raheel Shaikh</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>116152</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>KARACHI GASOLINE</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:43</t>
+        </is>
+      </c>
+      <c r="H427" t="n">
+        <v>24.8710114</v>
+      </c>
+      <c r="I427" t="n">
+        <v>67.1981226</v>
+      </c>
+      <c r="J427" t="n">
+        <v>25.64800071716309</v>
+      </c>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr"/>
+      <c r="M427" t="inlineStr"/>
+      <c r="N427" t="inlineStr"/>
+      <c r="O427" t="inlineStr"/>
+      <c r="P427" t="inlineStr"/>
+      <c r="Q427" t="inlineStr"/>
+      <c r="R427" t="inlineStr"/>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T427" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="U427" t="inlineStr"/>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>VIS-20261001124258-E53392</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2152</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Muhammad Faraz Khalili</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>115584</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>JANNAT FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:42:58</t>
+        </is>
+      </c>
+      <c r="H428" t="n">
+        <v>24.8467759</v>
+      </c>
+      <c r="I428" t="n">
+        <v>67.2132076</v>
+      </c>
+      <c r="J428" t="n">
+        <v>37.83200073242188</v>
+      </c>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr"/>
+      <c r="M428" t="inlineStr"/>
+      <c r="N428" t="inlineStr"/>
+      <c r="O428" t="inlineStr"/>
+      <c r="P428" t="inlineStr"/>
+      <c r="Q428" t="inlineStr"/>
+      <c r="R428" t="inlineStr"/>
+      <c r="S428" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T428" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="U428" t="inlineStr"/>
+      <c r="V428" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>VIS-20261001124331-AC2B13</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>501399</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Abdul Basit Siddiqui</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>116152</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>KARACHI GASOLINE</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:43:31</t>
+        </is>
+      </c>
+      <c r="H429" t="n">
+        <v>24.8708267</v>
+      </c>
+      <c r="I429" t="n">
+        <v>67.198185</v>
+      </c>
+      <c r="J429" t="n">
+        <v>5</v>
+      </c>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr"/>
+      <c r="M429" t="inlineStr"/>
+      <c r="N429" t="inlineStr"/>
+      <c r="O429" t="inlineStr"/>
+      <c r="P429" t="inlineStr"/>
+      <c r="Q429" t="inlineStr"/>
+      <c r="R429" t="inlineStr"/>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T429" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="U429" t="inlineStr"/>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>VIS-20261001124337-33FE8B</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>5003</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Sabeel Sirat Ur Rehman</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>115584</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>JANNAT FILLING STATION</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:43:37</t>
+        </is>
+      </c>
+      <c r="H430" t="n">
+        <v>24.8468542</v>
+      </c>
+      <c r="I430" t="n">
+        <v>67.2136738</v>
+      </c>
+      <c r="J430" t="n">
+        <v>30.43499946594238</v>
+      </c>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr"/>
+      <c r="M430" t="inlineStr"/>
+      <c r="N430" t="inlineStr"/>
+      <c r="O430" t="inlineStr"/>
+      <c r="P430" t="inlineStr"/>
+      <c r="Q430" t="inlineStr"/>
+      <c r="R430" t="inlineStr"/>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T430" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="U430" t="inlineStr"/>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>VIS-20261001124341-F5045A</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>3624</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Manoj Kumar</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>119506</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>HUR SERVICE STATION</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:43:41</t>
+        </is>
+      </c>
+      <c r="H431" t="n">
+        <v>24.8199969</v>
+      </c>
+      <c r="I431" t="n">
+        <v>67.1510956</v>
+      </c>
+      <c r="J431" t="n">
+        <v>11.48099994659424</v>
+      </c>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="inlineStr"/>
+      <c r="O431" t="inlineStr"/>
+      <c r="P431" t="inlineStr"/>
+      <c r="Q431" t="inlineStr"/>
+      <c r="R431" t="inlineStr"/>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="T431" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="U431" t="inlineStr"/>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>Within 1.5 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:V404"/>
+  <autoFilter ref="A1:V431"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/visits/Visits_2026-10-01.xlsx
+++ b/data/visits/Visits_2026-10-01.xlsx
@@ -18791,23 +18791,47 @@
       <c r="J270" t="n">
         <v>7.731999874</v>
       </c>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
-      <c r="N270" t="inlineStr"/>
-      <c r="O270" t="inlineStr"/>
-      <c r="P270" t="inlineStr"/>
-      <c r="Q270" t="inlineStr"/>
-      <c r="R270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>2026-10-01 12:43:42</t>
+        </is>
+      </c>
+      <c r="L270" t="n">
+        <v>24.8392894</v>
+      </c>
+      <c r="M270" t="n">
+        <v>67.1196673</v>
+      </c>
+      <c r="N270" t="n">
+        <v>20</v>
+      </c>
+      <c r="O270" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Almost Same</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>00:54:29</t>
+        </is>
+      </c>
+      <c r="R270" t="n">
+        <v>0.9081</v>
+      </c>
       <c r="S270" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="T270" t="n">
         <v>42</v>
       </c>
-      <c r="U270" t="inlineStr"/>
+      <c r="U270" t="n">
+        <v>39.1</v>
+      </c>
       <c r="V270" t="inlineStr">
         <is>
           <t>Within 1.5 km</t>
